--- a/data/Integracao Armazem.xlsx
+++ b/data/Integracao Armazem.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{193BE12A-49A2-458D-AB65-CF2C79963047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1127318-420D-40A6-90E0-8F1252AF5ECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{422D47E6-8DC3-4B25-BD50-E675C15B05CB}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7954" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8299" uniqueCount="672">
   <si>
     <t>Selecione o EPI que NÃO é obrigatório durante o processo de montagem de paletes</t>
   </si>
@@ -2010,6 +2010,171 @@
   </si>
   <si>
     <t>14:04</t>
+  </si>
+  <si>
+    <t>Anderson Santos Silva</t>
+  </si>
+  <si>
+    <t>556.238.928-25</t>
+  </si>
+  <si>
+    <t>13/04/2026</t>
+  </si>
+  <si>
+    <t>14/04/2026</t>
+  </si>
+  <si>
+    <t>14:56</t>
+  </si>
+  <si>
+    <t>Rodrigo melo Ribeiro</t>
+  </si>
+  <si>
+    <t>33345194813</t>
+  </si>
+  <si>
+    <t>12:18</t>
+  </si>
+  <si>
+    <t>LUCAS EDUARDO ROCINI</t>
+  </si>
+  <si>
+    <t>01395043973</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>Ygor. Genivaldo Silva de Jesus</t>
+  </si>
+  <si>
+    <t>46455046811</t>
+  </si>
+  <si>
+    <t>12:08</t>
+  </si>
+  <si>
+    <t>Bruno Sauza Simois</t>
+  </si>
+  <si>
+    <t>40369558880</t>
+  </si>
+  <si>
+    <t>Devemos realizar a movimentação de garrafas com no máximo 2 unidades por mão</t>
+  </si>
+  <si>
+    <t>11:58</t>
+  </si>
+  <si>
+    <t>Bruno Souza Simões</t>
+  </si>
+  <si>
+    <t>15/04/2026</t>
+  </si>
+  <si>
+    <t>17:58</t>
+  </si>
+  <si>
+    <t>Ygor Genivaldo Silva de Jesus</t>
+  </si>
+  <si>
+    <t>15:07</t>
+  </si>
+  <si>
+    <t>O Picking é a área que é utilizada para armazenagem de paletes fechados do estoque</t>
+  </si>
+  <si>
+    <t>15:02</t>
+  </si>
+  <si>
+    <t>Bruno Souza simoes</t>
+  </si>
+  <si>
+    <t>Bruno Souza Simois</t>
+  </si>
+  <si>
+    <t>14:53</t>
+  </si>
+  <si>
+    <t>Bruno Souza</t>
+  </si>
+  <si>
+    <t>Curva A: "Alto giro"; Curva B: "Baixo giro"; Curva C: "Zero giro"</t>
+  </si>
+  <si>
+    <t>14:49</t>
+  </si>
+  <si>
+    <t>14:48</t>
+  </si>
+  <si>
+    <t>12:14</t>
+  </si>
+  <si>
+    <t>18:02</t>
+  </si>
+  <si>
+    <t>40 369 558880</t>
+  </si>
+  <si>
+    <t>Os produtos diversos podem ser posicionados na parte interna do palete</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>Ygor genivaldo Silva de Jesus</t>
+  </si>
+  <si>
+    <t>14:51</t>
+  </si>
+  <si>
+    <t>14:47</t>
+  </si>
+  <si>
+    <t>18:04</t>
+  </si>
+  <si>
+    <t>10:11</t>
+  </si>
+  <si>
+    <t>Para adiantar a separação, podemos pegar o produto correto porém embalagem diferente</t>
+  </si>
+  <si>
+    <t>15:12</t>
+  </si>
+  <si>
+    <t>Associar palete, abrir a lista de produtos, separar todo o palete sem conferência e confirmar todos os produtos</t>
+  </si>
+  <si>
+    <t>15:11</t>
+  </si>
+  <si>
+    <t>15:06</t>
+  </si>
+  <si>
+    <t>18:07</t>
+  </si>
+  <si>
+    <t>10:14</t>
+  </si>
+  <si>
+    <t>15:17</t>
+  </si>
+  <si>
+    <t>15:16</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>15:14</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>10:16</t>
   </si>
 </sst>
 </file>
@@ -2399,7 +2564,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D8EC4C0-DEF5-4A13-83D8-46C06041A7DF}">
-  <dimension ref="A1:S256"/>
+  <dimension ref="A1:S262"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="19" width="14.109375" customWidth="1"/>
@@ -14449,6 +14614,306 @@
         <v>612</v>
       </c>
     </row>
+    <row r="257" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A257" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="B257" s="8" t="s">
+        <v>618</v>
+      </c>
+      <c r="C257" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D257" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E257" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F257" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G257" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H257" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I257" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J257" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K257" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="L257" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M257" s="8">
+        <v>80</v>
+      </c>
+      <c r="N257" s="8"/>
+      <c r="O257" s="8"/>
+      <c r="P257" s="10"/>
+      <c r="Q257" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="R257" s="11" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="258" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A258" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="B258" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="C258" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D258" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E258" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F258" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="G258" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H258" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I258" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J258" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K258" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="L258" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="M258" s="8">
+        <v>60</v>
+      </c>
+      <c r="N258" s="8"/>
+      <c r="O258" s="8"/>
+      <c r="P258" s="10"/>
+      <c r="Q258" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="R258" s="11" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="259" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A259" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="B259" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="C259" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D259" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E259" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F259" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G259" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H259" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I259" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J259" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="K259" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L259" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M259" s="8">
+        <v>80</v>
+      </c>
+      <c r="N259" s="8"/>
+      <c r="O259" s="8"/>
+      <c r="P259" s="10"/>
+      <c r="Q259" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="R259" s="11" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="260" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A260" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="B260" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="C260" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D260" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E260" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F260" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G260" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H260" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I260" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="J260" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K260" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="L260" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M260" s="8">
+        <v>70</v>
+      </c>
+      <c r="N260" s="8"/>
+      <c r="O260" s="8"/>
+      <c r="P260" s="10"/>
+      <c r="Q260" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="R260" s="11" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="261" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A261" s="8" t="s">
+        <v>631</v>
+      </c>
+      <c r="B261" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="C261" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D261" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E261" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F261" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G261" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="H261" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="I261" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J261" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K261" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="L261" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="M261" s="8">
+        <v>40</v>
+      </c>
+      <c r="N261" s="8"/>
+      <c r="O261" s="8"/>
+      <c r="P261" s="10"/>
+      <c r="Q261" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="R261" s="11" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="262" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A262" s="8" t="s">
+        <v>635</v>
+      </c>
+      <c r="B262" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="C262" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D262" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E262" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F262" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G262" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H262" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I262" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J262" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K262" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L262" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="M262" s="8">
+        <v>80</v>
+      </c>
+      <c r="N262" s="8"/>
+      <c r="O262" s="8"/>
+      <c r="P262" s="10"/>
+      <c r="Q262" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="R262" s="11" t="s">
+        <v>637</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -14457,7 +14922,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9848E97-FB23-44B1-9CE3-C616F78A0A8B}">
-  <dimension ref="A1:S250"/>
+  <dimension ref="A1:S258"/>
   <sheetFormatPr defaultColWidth="15.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -22496,6 +22961,286 @@
       </c>
       <c r="M250" s="11" t="s">
         <v>582</v>
+      </c>
+    </row>
+    <row r="251" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A251" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="B251" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="C251" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D251" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="E251" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="F251" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G251" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H251" s="8">
+        <v>20</v>
+      </c>
+      <c r="I251" s="8"/>
+      <c r="J251" s="8"/>
+      <c r="K251" s="10"/>
+      <c r="L251" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="M251" s="11" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="252" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A252" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="B252" s="8" t="s">
+        <v>618</v>
+      </c>
+      <c r="C252" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D252" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="E252" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="F252" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="G252" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H252" s="8">
+        <v>10</v>
+      </c>
+      <c r="I252" s="8"/>
+      <c r="J252" s="8"/>
+      <c r="K252" s="10"/>
+      <c r="L252" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="M252" s="11" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="253" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A253" s="8" t="s">
+        <v>642</v>
+      </c>
+      <c r="B253" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="C253" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D253" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E253" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="F253" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G253" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H253" s="8">
+        <v>30</v>
+      </c>
+      <c r="I253" s="8"/>
+      <c r="J253" s="8"/>
+      <c r="K253" s="10"/>
+      <c r="L253" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="M253" s="11" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="254" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A254" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="B254" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="C254" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D254" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="E254" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="F254" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G254" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H254" s="8">
+        <v>20</v>
+      </c>
+      <c r="I254" s="8"/>
+      <c r="J254" s="8"/>
+      <c r="K254" s="10"/>
+      <c r="L254" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="M254" s="11" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="255" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A255" s="8" t="s">
+        <v>645</v>
+      </c>
+      <c r="B255" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="C255" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D255" s="8" t="s">
+        <v>646</v>
+      </c>
+      <c r="E255" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="F255" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G255" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="H255" s="8">
+        <v>10</v>
+      </c>
+      <c r="I255" s="8"/>
+      <c r="J255" s="8"/>
+      <c r="K255" s="10"/>
+      <c r="L255" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="M255" s="11" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="256" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A256" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="B256" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="C256" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D256" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="E256" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="F256" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="G256" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H256" s="8">
+        <v>10</v>
+      </c>
+      <c r="I256" s="8"/>
+      <c r="J256" s="8"/>
+      <c r="K256" s="10"/>
+      <c r="L256" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="M256" s="11" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="257" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A257" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="B257" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="C257" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D257" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E257" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="F257" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G257" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H257" s="8">
+        <v>30</v>
+      </c>
+      <c r="I257" s="8"/>
+      <c r="J257" s="8"/>
+      <c r="K257" s="10"/>
+      <c r="L257" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="M257" s="11" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="258" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A258" s="8" t="s">
+        <v>635</v>
+      </c>
+      <c r="B258" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="C258" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D258" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="E258" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F258" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="G258" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H258" s="8">
+        <v>20</v>
+      </c>
+      <c r="I258" s="8"/>
+      <c r="J258" s="8"/>
+      <c r="K258" s="10"/>
+      <c r="L258" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="M258" s="11" t="s">
+        <v>650</v>
       </c>
     </row>
   </sheetData>
@@ -22505,7 +23250,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E795EE60-EBCD-4B19-B884-654D5F927670}">
-  <dimension ref="A1:S248"/>
+  <dimension ref="A1:S255"/>
   <sheetFormatPr defaultColWidth="16.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -30480,6 +31225,251 @@
       </c>
       <c r="M248" s="11" t="s">
         <v>597</v>
+      </c>
+    </row>
+    <row r="249" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A249" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="B249" s="8" t="s">
+        <v>618</v>
+      </c>
+      <c r="C249" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D249" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E249" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="F249" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G249" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H249" s="8">
+        <v>30</v>
+      </c>
+      <c r="I249" s="8"/>
+      <c r="J249" s="8"/>
+      <c r="K249" s="10"/>
+      <c r="L249" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="M249" s="11" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="250" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A250" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="B250" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="C250" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D250" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E250" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="F250" s="8" t="s">
+        <v>652</v>
+      </c>
+      <c r="G250" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H250" s="8">
+        <v>20</v>
+      </c>
+      <c r="I250" s="8"/>
+      <c r="J250" s="8"/>
+      <c r="K250" s="10"/>
+      <c r="L250" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="M250" s="11" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="251" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A251" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="B251" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="C251" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D251" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E251" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="F251" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G251" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H251" s="8">
+        <v>30</v>
+      </c>
+      <c r="I251" s="8"/>
+      <c r="J251" s="8"/>
+      <c r="K251" s="10"/>
+      <c r="L251" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="M251" s="11" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="252" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A252" s="8" t="s">
+        <v>654</v>
+      </c>
+      <c r="B252" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="C252" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D252" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E252" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="F252" s="8" t="s">
+        <v>652</v>
+      </c>
+      <c r="G252" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H252" s="8">
+        <v>20</v>
+      </c>
+      <c r="I252" s="8"/>
+      <c r="J252" s="8"/>
+      <c r="K252" s="10"/>
+      <c r="L252" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="M252" s="11" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="253" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A253" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="B253" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="C253" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D253" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E253" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="F253" s="8" t="s">
+        <v>652</v>
+      </c>
+      <c r="G253" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H253" s="8">
+        <v>20</v>
+      </c>
+      <c r="I253" s="8"/>
+      <c r="J253" s="8"/>
+      <c r="K253" s="10"/>
+      <c r="L253" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="M253" s="11" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="254" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A254" s="8" t="s">
+        <v>635</v>
+      </c>
+      <c r="B254" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="C254" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D254" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E254" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="F254" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G254" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="H254" s="8">
+        <v>20</v>
+      </c>
+      <c r="I254" s="8"/>
+      <c r="J254" s="8"/>
+      <c r="K254" s="10"/>
+      <c r="L254" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="M254" s="11" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="255" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A255" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="B255" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="C255" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D255" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E255" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F255" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G255" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H255" s="8">
+        <v>40</v>
+      </c>
+      <c r="I255" s="8"/>
+      <c r="J255" s="8"/>
+      <c r="K255" s="10"/>
+      <c r="L255" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="M255" s="11" t="s">
+        <v>658</v>
       </c>
     </row>
   </sheetData>
@@ -30489,7 +31479,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41BB7886-C4B6-45DF-87F2-53652B8B0BB3}">
-  <dimension ref="A1:S245"/>
+  <dimension ref="A1:S252"/>
   <sheetFormatPr defaultColWidth="12.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -38368,6 +39358,251 @@
       </c>
       <c r="M245" s="11" t="s">
         <v>615</v>
+      </c>
+    </row>
+    <row r="246" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A246" s="8" t="s">
+        <v>642</v>
+      </c>
+      <c r="B246" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="C246" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D246" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E246" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="F246" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="G246" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H246" s="8">
+        <v>20</v>
+      </c>
+      <c r="I246" s="8"/>
+      <c r="J246" s="8"/>
+      <c r="K246" s="10"/>
+      <c r="L246" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="M246" s="11" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="247" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A247" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="B247" s="8" t="s">
+        <v>618</v>
+      </c>
+      <c r="C247" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D247" s="8" t="s">
+        <v>519</v>
+      </c>
+      <c r="E247" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="F247" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G247" s="8" t="s">
+        <v>661</v>
+      </c>
+      <c r="H247" s="8">
+        <v>10</v>
+      </c>
+      <c r="I247" s="8"/>
+      <c r="J247" s="8"/>
+      <c r="K247" s="10"/>
+      <c r="L247" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="M247" s="11" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="248" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A248" s="8" t="s">
+        <v>642</v>
+      </c>
+      <c r="B248" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="C248" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D248" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E248" s="8" t="s">
+        <v>520</v>
+      </c>
+      <c r="F248" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="G248" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H248" s="8">
+        <v>20</v>
+      </c>
+      <c r="I248" s="8"/>
+      <c r="J248" s="8"/>
+      <c r="K248" s="10"/>
+      <c r="L248" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="M248" s="11" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="249" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A249" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="B249" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="C249" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D249" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E249" s="8" t="s">
+        <v>520</v>
+      </c>
+      <c r="F249" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="G249" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H249" s="8">
+        <v>20</v>
+      </c>
+      <c r="I249" s="8"/>
+      <c r="J249" s="8"/>
+      <c r="K249" s="10"/>
+      <c r="L249" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="M249" s="11" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="250" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A250" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="B250" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="C250" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D250" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E250" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="F250" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G250" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H250" s="8">
+        <v>30</v>
+      </c>
+      <c r="I250" s="8"/>
+      <c r="J250" s="8"/>
+      <c r="K250" s="10"/>
+      <c r="L250" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="M250" s="11" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="251" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A251" s="8" t="s">
+        <v>635</v>
+      </c>
+      <c r="B251" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="C251" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D251" s="8" t="s">
+        <v>519</v>
+      </c>
+      <c r="E251" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="F251" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G251" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H251" s="8">
+        <v>20</v>
+      </c>
+      <c r="I251" s="8"/>
+      <c r="J251" s="8"/>
+      <c r="K251" s="10"/>
+      <c r="L251" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="M251" s="11" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="252" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A252" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="B252" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="C252" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D252" s="8" t="s">
+        <v>519</v>
+      </c>
+      <c r="E252" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F252" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G252" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H252" s="8">
+        <v>30</v>
+      </c>
+      <c r="I252" s="8"/>
+      <c r="J252" s="8"/>
+      <c r="K252" s="10"/>
+      <c r="L252" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="M252" s="11" t="s">
+        <v>665</v>
       </c>
     </row>
   </sheetData>
@@ -38377,7 +39612,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{083B2BF1-723B-4775-8297-318920D3FD0C}">
-  <dimension ref="A1:S245"/>
+  <dimension ref="A1:S252"/>
   <sheetFormatPr defaultColWidth="13.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -46258,6 +47493,251 @@
         <v>616</v>
       </c>
     </row>
+    <row r="246" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A246" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="B246" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="C246" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D246" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="E246" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F246" s="8" t="s">
+        <v>556</v>
+      </c>
+      <c r="G246" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H246" s="8">
+        <v>20</v>
+      </c>
+      <c r="I246" s="8"/>
+      <c r="J246" s="8"/>
+      <c r="K246" s="10"/>
+      <c r="L246" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="M246" s="11" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="247" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A247" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="B247" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="C247" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D247" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="E247" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F247" s="8" t="s">
+        <v>552</v>
+      </c>
+      <c r="G247" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H247" s="8">
+        <v>20</v>
+      </c>
+      <c r="I247" s="8"/>
+      <c r="J247" s="8"/>
+      <c r="K247" s="10"/>
+      <c r="L247" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="M247" s="11" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="248" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A248" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="B248" s="8" t="s">
+        <v>618</v>
+      </c>
+      <c r="C248" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D248" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E248" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F248" s="8" t="s">
+        <v>556</v>
+      </c>
+      <c r="G248" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="H248" s="8">
+        <v>20</v>
+      </c>
+      <c r="I248" s="8"/>
+      <c r="J248" s="8"/>
+      <c r="K248" s="10"/>
+      <c r="L248" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="M248" s="11" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="249" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A249" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="B249" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="C249" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D249" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="E249" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F249" s="8" t="s">
+        <v>552</v>
+      </c>
+      <c r="G249" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H249" s="8">
+        <v>20</v>
+      </c>
+      <c r="I249" s="8"/>
+      <c r="J249" s="8"/>
+      <c r="K249" s="10"/>
+      <c r="L249" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="M249" s="11" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="250" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A250" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="B250" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="C250" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D250" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="E250" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F250" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="G250" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H250" s="8">
+        <v>20</v>
+      </c>
+      <c r="I250" s="8"/>
+      <c r="J250" s="8"/>
+      <c r="K250" s="10"/>
+      <c r="L250" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="M250" s="11" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="251" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A251" s="8" t="s">
+        <v>635</v>
+      </c>
+      <c r="B251" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="C251" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D251" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E251" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F251" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="G251" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H251" s="8">
+        <v>40</v>
+      </c>
+      <c r="I251" s="8"/>
+      <c r="J251" s="8"/>
+      <c r="K251" s="10"/>
+      <c r="L251" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="M251" s="11" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="252" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A252" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="B252" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="C252" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D252" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E252" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F252" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="G252" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H252" s="8">
+        <v>40</v>
+      </c>
+      <c r="I252" s="8"/>
+      <c r="J252" s="8"/>
+      <c r="K252" s="10"/>
+      <c r="L252" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="M252" s="11" t="s">
+        <v>671</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/data/Integracao Armazem.xlsx
+++ b/data/Integracao Armazem.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1127318-420D-40A6-90E0-8F1252AF5ECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92874FB0-981C-4A60-9BAC-CE5F53EC1631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{422D47E6-8DC3-4B25-BD50-E675C15B05CB}"/>
   </bookViews>

--- a/data/Integracao Armazem.xlsx
+++ b/data/Integracao Armazem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92874FB0-981C-4A60-9BAC-CE5F53EC1631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31FCACFB-78E5-4BAF-A54D-2D5E31709AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{422D47E6-8DC3-4B25-BD50-E675C15B05CB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{422D47E6-8DC3-4B25-BD50-E675C15B05CB}"/>
   </bookViews>
   <sheets>
     <sheet name="M1" sheetId="1" r:id="rId1"/>

--- a/data/Integracao Armazem.xlsx
+++ b/data/Integracao Armazem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31FCACFB-78E5-4BAF-A54D-2D5E31709AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58DE67F7-4FBA-4A9E-B6E3-AECE1E5EB479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{422D47E6-8DC3-4B25-BD50-E675C15B05CB}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="4" xr2:uid="{422D47E6-8DC3-4B25-BD50-E675C15B05CB}"/>
   </bookViews>
   <sheets>
     <sheet name="M1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8299" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8999" uniqueCount="762">
   <si>
     <t>Selecione o EPI que NÃO é obrigatório durante o processo de montagem de paletes</t>
   </si>
@@ -2175,6 +2175,276 @@
   </si>
   <si>
     <t>10:16</t>
+  </si>
+  <si>
+    <t>ROBERTO DA SILVA GROTZ</t>
+  </si>
+  <si>
+    <t>16305844798</t>
+  </si>
+  <si>
+    <t>28/04/2026</t>
+  </si>
+  <si>
+    <t>30/04/2026</t>
+  </si>
+  <si>
+    <t>10:43</t>
+  </si>
+  <si>
+    <t>PEDRO AUGUSTO SILVA JUSTINO</t>
+  </si>
+  <si>
+    <t>16570738747</t>
+  </si>
+  <si>
+    <t>09:59</t>
+  </si>
+  <si>
+    <t>Guilherme de Souza Santos</t>
+  </si>
+  <si>
+    <t>58922698845</t>
+  </si>
+  <si>
+    <t>29/04/2026</t>
+  </si>
+  <si>
+    <t>Validar a condição do palete e realizar a separação mesmo em más condições</t>
+  </si>
+  <si>
+    <t>10:33</t>
+  </si>
+  <si>
+    <t>Renan Presciliano Jorge</t>
+  </si>
+  <si>
+    <t>49473669828</t>
+  </si>
+  <si>
+    <t>10:32</t>
+  </si>
+  <si>
+    <t>Lucas de lima Freitas</t>
+  </si>
+  <si>
+    <t>71579959482</t>
+  </si>
+  <si>
+    <t>Guilherme Oliveira da silva</t>
+  </si>
+  <si>
+    <t>45572311871</t>
+  </si>
+  <si>
+    <t>10/03/2008</t>
+  </si>
+  <si>
+    <t>Anderson Gomes Ribeiro</t>
+  </si>
+  <si>
+    <t>09631565513</t>
+  </si>
+  <si>
+    <t>23/04/2026</t>
+  </si>
+  <si>
+    <t>DAVI MARLON MOREIRA RODRIGUES</t>
+  </si>
+  <si>
+    <t>087.156.495-55</t>
+  </si>
+  <si>
+    <t>27/04/2026</t>
+  </si>
+  <si>
+    <t>14:43</t>
+  </si>
+  <si>
+    <t>ITAMAR DOS SANTOS</t>
+  </si>
+  <si>
+    <t>061.435.565-63</t>
+  </si>
+  <si>
+    <t>14:40</t>
+  </si>
+  <si>
+    <t>RIANDERSON DOS ANJOS SOUZA</t>
+  </si>
+  <si>
+    <t>092.410.285-30</t>
+  </si>
+  <si>
+    <t>Deve-se garantir apenas a área seca livre de presença de poças</t>
+  </si>
+  <si>
+    <t>14:39</t>
+  </si>
+  <si>
+    <t>ALEX DE OLIVEIRA MOURA</t>
+  </si>
+  <si>
+    <t>06267570533</t>
+  </si>
+  <si>
+    <t>14:29</t>
+  </si>
+  <si>
+    <t>Benicio Silva de Matos</t>
+  </si>
+  <si>
+    <t>05429917567</t>
+  </si>
+  <si>
+    <t>14:26</t>
+  </si>
+  <si>
+    <t>Danillo Paulo dos Santos</t>
+  </si>
+  <si>
+    <t>08297449599</t>
+  </si>
+  <si>
+    <t>04/05/2026</t>
+  </si>
+  <si>
+    <t>07/05/2026</t>
+  </si>
+  <si>
+    <t>11:08</t>
+  </si>
+  <si>
+    <t>João Victor dos Santos</t>
+  </si>
+  <si>
+    <t>093.323.489-74</t>
+  </si>
+  <si>
+    <t>11:07</t>
+  </si>
+  <si>
+    <t>062.675.705-33</t>
+  </si>
+  <si>
+    <t>BENICIO SILVA DE MATOS</t>
+  </si>
+  <si>
+    <t>054.299.175-67</t>
+  </si>
+  <si>
+    <t>10:44</t>
+  </si>
+  <si>
+    <t>10:42</t>
+  </si>
+  <si>
+    <t>10:01</t>
+  </si>
+  <si>
+    <t>096.323.489-74</t>
+  </si>
+  <si>
+    <t>11:19</t>
+  </si>
+  <si>
+    <t>11:18</t>
+  </si>
+  <si>
+    <t>17:29</t>
+  </si>
+  <si>
+    <t>Itamar dos Santos</t>
+  </si>
+  <si>
+    <t>Alex de Oliveira Moura</t>
+  </si>
+  <si>
+    <t>17:28</t>
+  </si>
+  <si>
+    <t>Rianderson dos Anjos Souza</t>
+  </si>
+  <si>
+    <t>17:27</t>
+  </si>
+  <si>
+    <t>Davi Marlon Moreira Rodrigues</t>
+  </si>
+  <si>
+    <t>17:23</t>
+  </si>
+  <si>
+    <t>10:55</t>
+  </si>
+  <si>
+    <t>10:54</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>10:37</t>
+  </si>
+  <si>
+    <t>11:32</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>17:34</t>
+  </si>
+  <si>
+    <t>17:33</t>
+  </si>
+  <si>
+    <t>17:32</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>O endereço dentro do Picking do produto é mostrada no WMS</t>
+  </si>
+  <si>
+    <t>11:43</t>
+  </si>
+  <si>
+    <t>17:57</t>
+  </si>
+  <si>
+    <t>17:56</t>
+  </si>
+  <si>
+    <t>17:54</t>
+  </si>
+  <si>
+    <t>17:53</t>
+  </si>
+  <si>
+    <t>11:22</t>
+  </si>
+  <si>
+    <t>11:21</t>
+  </si>
+  <si>
+    <t>10:46</t>
+  </si>
+  <si>
+    <t>10:41</t>
+  </si>
+  <si>
+    <t>João  Victor dos Santos</t>
+  </si>
+  <si>
+    <t>11:52</t>
+  </si>
+  <si>
+    <t>Dan</t>
+  </si>
+  <si>
+    <t>11:50</t>
   </si>
 </sst>
 </file>
@@ -2564,7 +2834,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D8EC4C0-DEF5-4A13-83D8-46C06041A7DF}">
-  <dimension ref="A1:S262"/>
+  <dimension ref="A1:S276"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="19" width="14.109375" customWidth="1"/>
@@ -14866,13 +15136,13 @@
     </row>
     <row r="262" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A262" s="8" t="s">
-        <v>635</v>
+        <v>672</v>
       </c>
       <c r="B262" s="8" t="s">
-        <v>632</v>
+        <v>673</v>
       </c>
       <c r="C262" s="9" t="s">
-        <v>619</v>
+        <v>674</v>
       </c>
       <c r="D262" s="8" t="s">
         <v>17</v>
@@ -14899,7 +15169,7 @@
         <v>360</v>
       </c>
       <c r="L262" s="8" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="M262" s="8">
         <v>80</v>
@@ -14908,10 +15178,710 @@
       <c r="O262" s="8"/>
       <c r="P262" s="10"/>
       <c r="Q262" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="R262" s="11" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="263" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A263" s="8" t="s">
+        <v>677</v>
+      </c>
+      <c r="B263" s="8" t="s">
+        <v>678</v>
+      </c>
+      <c r="C263" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="D263" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E263" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F263" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G263" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H263" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I263" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J263" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K263" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L263" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M263" s="8">
+        <v>90</v>
+      </c>
+      <c r="N263" s="8"/>
+      <c r="O263" s="8"/>
+      <c r="P263" s="10"/>
+      <c r="Q263" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="R263" s="11" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="264" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A264" s="8" t="s">
+        <v>680</v>
+      </c>
+      <c r="B264" s="8" t="s">
+        <v>681</v>
+      </c>
+      <c r="C264" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="D264" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E264" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F264" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G264" s="8" t="s">
+        <v>683</v>
+      </c>
+      <c r="H264" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I264" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J264" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K264" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="L264" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M264" s="8">
+        <v>70</v>
+      </c>
+      <c r="N264" s="8"/>
+      <c r="O264" s="8"/>
+      <c r="P264" s="10"/>
+      <c r="Q264" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="R264" s="11" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="265" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A265" s="8" t="s">
+        <v>685</v>
+      </c>
+      <c r="B265" s="8" t="s">
+        <v>686</v>
+      </c>
+      <c r="C265" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="D265" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E265" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F265" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G265" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H265" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I265" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J265" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K265" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="L265" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M265" s="8">
+        <v>80</v>
+      </c>
+      <c r="N265" s="8"/>
+      <c r="O265" s="8"/>
+      <c r="P265" s="10"/>
+      <c r="Q265" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="R265" s="11" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="266" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A266" s="8" t="s">
+        <v>688</v>
+      </c>
+      <c r="B266" s="8" t="s">
+        <v>689</v>
+      </c>
+      <c r="C266" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="D266" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E266" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F266" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G266" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H266" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I266" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J266" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K266" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="L266" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M266" s="8">
+        <v>80</v>
+      </c>
+      <c r="N266" s="8"/>
+      <c r="O266" s="8"/>
+      <c r="P266" s="10"/>
+      <c r="Q266" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="R266" s="11" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="267" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A267" s="8" t="s">
+        <v>690</v>
+      </c>
+      <c r="B267" s="8" t="s">
+        <v>691</v>
+      </c>
+      <c r="C267" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="D267" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E267" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F267" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G267" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H267" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I267" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J267" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K267" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="L267" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M267" s="8">
+        <v>80</v>
+      </c>
+      <c r="N267" s="8"/>
+      <c r="O267" s="8"/>
+      <c r="P267" s="10"/>
+      <c r="Q267" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="R267" s="11" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="268" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A268" s="8" t="s">
+        <v>693</v>
+      </c>
+      <c r="B268" s="8" t="s">
+        <v>694</v>
+      </c>
+      <c r="C268" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="D268" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E268" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F268" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G268" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H268" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I268" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J268" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K268" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="L268" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M268" s="8">
+        <v>80</v>
+      </c>
+      <c r="N268" s="8"/>
+      <c r="O268" s="8"/>
+      <c r="P268" s="10"/>
+      <c r="Q268" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="R268" s="11" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="269" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A269" s="8" t="s">
+        <v>696</v>
+      </c>
+      <c r="B269" s="8" t="s">
+        <v>697</v>
+      </c>
+      <c r="C269" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="D269" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E269" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F269" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G269" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H269" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I269" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J269" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K269" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L269" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M269" s="8">
+        <v>90</v>
+      </c>
+      <c r="N269" s="8"/>
+      <c r="O269" s="8"/>
+      <c r="P269" s="10"/>
+      <c r="Q269" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="R269" s="11" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="270" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A270" s="8" t="s">
+        <v>700</v>
+      </c>
+      <c r="B270" s="8" t="s">
+        <v>701</v>
+      </c>
+      <c r="C270" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="D270" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E270" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F270" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G270" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H270" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I270" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J270" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K270" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L270" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M270" s="8">
+        <v>90</v>
+      </c>
+      <c r="N270" s="8"/>
+      <c r="O270" s="8"/>
+      <c r="P270" s="10"/>
+      <c r="Q270" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="R270" s="11" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="271" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A271" s="8" t="s">
+        <v>703</v>
+      </c>
+      <c r="B271" s="8" t="s">
+        <v>704</v>
+      </c>
+      <c r="C271" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="D271" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E271" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F271" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G271" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H271" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="I271" s="8" t="s">
+        <v>705</v>
+      </c>
+      <c r="J271" s="8" t="s">
+        <v>569</v>
+      </c>
+      <c r="K271" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L271" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M271" s="8">
+        <v>60</v>
+      </c>
+      <c r="N271" s="8"/>
+      <c r="O271" s="8"/>
+      <c r="P271" s="10"/>
+      <c r="Q271" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="R271" s="11" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="272" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A272" s="8" t="s">
+        <v>707</v>
+      </c>
+      <c r="B272" s="8" t="s">
+        <v>708</v>
+      </c>
+      <c r="C272" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="D272" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E272" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F272" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G272" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H272" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I272" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J272" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K272" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L272" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M272" s="8">
+        <v>90</v>
+      </c>
+      <c r="N272" s="8"/>
+      <c r="O272" s="8"/>
+      <c r="P272" s="10"/>
+      <c r="Q272" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="R272" s="11" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="273" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A273" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="B273" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="C273" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="D273" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E273" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F273" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G273" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H273" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I273" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J273" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K273" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L273" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M273" s="8">
+        <v>90</v>
+      </c>
+      <c r="N273" s="8"/>
+      <c r="O273" s="8"/>
+      <c r="P273" s="10"/>
+      <c r="Q273" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="R273" s="11" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="274" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A274" s="8" t="s">
+        <v>635</v>
+      </c>
+      <c r="B274" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="C274" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D274" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E274" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F274" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G274" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H274" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I274" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J274" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K274" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L274" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="M274" s="8">
+        <v>80</v>
+      </c>
+      <c r="N274" s="8"/>
+      <c r="O274" s="8"/>
+      <c r="P274" s="10"/>
+      <c r="Q274" s="9" t="s">
         <v>636</v>
       </c>
-      <c r="R262" s="11" t="s">
+      <c r="R274" s="11" t="s">
         <v>637</v>
+      </c>
+    </row>
+    <row r="275" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A275" s="8" t="s">
+        <v>713</v>
+      </c>
+      <c r="B275" s="8" t="s">
+        <v>714</v>
+      </c>
+      <c r="C275" s="9" t="s">
+        <v>715</v>
+      </c>
+      <c r="D275" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E275" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F275" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G275" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H275" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I275" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J275" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K275" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="L275" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M275" s="8">
+        <v>80</v>
+      </c>
+      <c r="N275" s="8"/>
+      <c r="O275" s="8"/>
+      <c r="P275" s="10"/>
+      <c r="Q275" s="9" t="s">
+        <v>716</v>
+      </c>
+      <c r="R275" s="11" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="276" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A276" s="8" t="s">
+        <v>718</v>
+      </c>
+      <c r="B276" s="8" t="s">
+        <v>719</v>
+      </c>
+      <c r="C276" s="9" t="s">
+        <v>715</v>
+      </c>
+      <c r="D276" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E276" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F276" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G276" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H276" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I276" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J276" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K276" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L276" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M276" s="8">
+        <v>90</v>
+      </c>
+      <c r="N276" s="8"/>
+      <c r="O276" s="8"/>
+      <c r="P276" s="10"/>
+      <c r="Q276" s="9" t="s">
+        <v>716</v>
+      </c>
+      <c r="R276" s="11" t="s">
+        <v>720</v>
       </c>
     </row>
   </sheetData>
@@ -14922,7 +15892,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9848E97-FB23-44B1-9CE3-C616F78A0A8B}">
-  <dimension ref="A1:S258"/>
+  <dimension ref="A1:S272"/>
   <sheetFormatPr defaultColWidth="15.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -23241,6 +24211,496 @@
       </c>
       <c r="M258" s="11" t="s">
         <v>650</v>
+      </c>
+    </row>
+    <row r="259" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A259" s="8" t="s">
+        <v>707</v>
+      </c>
+      <c r="B259" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C259" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="D259" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E259" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="F259" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G259" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="H259" s="8">
+        <v>20</v>
+      </c>
+      <c r="I259" s="8"/>
+      <c r="J259" s="8"/>
+      <c r="K259" s="10"/>
+      <c r="L259" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="M259" s="11" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="260" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A260" s="8" t="s">
+        <v>722</v>
+      </c>
+      <c r="B260" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="C260" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="D260" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E260" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="F260" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G260" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="H260" s="8">
+        <v>20</v>
+      </c>
+      <c r="I260" s="8"/>
+      <c r="J260" s="8"/>
+      <c r="K260" s="10"/>
+      <c r="L260" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="M260" s="11" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="261" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A261" s="8" t="s">
+        <v>696</v>
+      </c>
+      <c r="B261" s="8" t="s">
+        <v>697</v>
+      </c>
+      <c r="C261" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="D261" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E261" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="F261" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G261" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="H261" s="8">
+        <v>20</v>
+      </c>
+      <c r="I261" s="8"/>
+      <c r="J261" s="8"/>
+      <c r="K261" s="10"/>
+      <c r="L261" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="M261" s="11" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="262" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A262" s="8" t="s">
+        <v>700</v>
+      </c>
+      <c r="B262" s="8" t="s">
+        <v>701</v>
+      </c>
+      <c r="C262" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="D262" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E262" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="F262" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G262" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="H262" s="8">
+        <v>20</v>
+      </c>
+      <c r="I262" s="8"/>
+      <c r="J262" s="8"/>
+      <c r="K262" s="10"/>
+      <c r="L262" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="M262" s="11" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="263" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A263" s="8" t="s">
+        <v>703</v>
+      </c>
+      <c r="B263" s="8" t="s">
+        <v>704</v>
+      </c>
+      <c r="C263" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="D263" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E263" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="F263" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G263" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="H263" s="8">
+        <v>20</v>
+      </c>
+      <c r="I263" s="8"/>
+      <c r="J263" s="8"/>
+      <c r="K263" s="10"/>
+      <c r="L263" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="M263" s="11" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="264" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A264" s="8" t="s">
+        <v>688</v>
+      </c>
+      <c r="B264" s="8" t="s">
+        <v>689</v>
+      </c>
+      <c r="C264" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="D264" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E264" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F264" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G264" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H264" s="8">
+        <v>40</v>
+      </c>
+      <c r="I264" s="8"/>
+      <c r="J264" s="8"/>
+      <c r="K264" s="10"/>
+      <c r="L264" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M264" s="11" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="265" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A265" s="8" t="s">
+        <v>680</v>
+      </c>
+      <c r="B265" s="8" t="s">
+        <v>681</v>
+      </c>
+      <c r="C265" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="D265" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E265" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F265" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G265" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H265" s="8">
+        <v>40</v>
+      </c>
+      <c r="I265" s="8"/>
+      <c r="J265" s="8"/>
+      <c r="K265" s="10"/>
+      <c r="L265" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M265" s="11" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="266" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A266" s="8" t="s">
+        <v>693</v>
+      </c>
+      <c r="B266" s="8" t="s">
+        <v>694</v>
+      </c>
+      <c r="C266" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="D266" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E266" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F266" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G266" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H266" s="8">
+        <v>40</v>
+      </c>
+      <c r="I266" s="8"/>
+      <c r="J266" s="8"/>
+      <c r="K266" s="10"/>
+      <c r="L266" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M266" s="11" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="267" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A267" s="8" t="s">
+        <v>690</v>
+      </c>
+      <c r="B267" s="8" t="s">
+        <v>691</v>
+      </c>
+      <c r="C267" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="D267" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E267" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F267" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G267" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H267" s="8">
+        <v>40</v>
+      </c>
+      <c r="I267" s="8"/>
+      <c r="J267" s="8"/>
+      <c r="K267" s="10"/>
+      <c r="L267" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M267" s="11" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="268" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A268" s="8" t="s">
+        <v>685</v>
+      </c>
+      <c r="B268" s="8" t="s">
+        <v>686</v>
+      </c>
+      <c r="C268" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="D268" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E268" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F268" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G268" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H268" s="8">
+        <v>40</v>
+      </c>
+      <c r="I268" s="8"/>
+      <c r="J268" s="8"/>
+      <c r="K268" s="10"/>
+      <c r="L268" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M268" s="11" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="269" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A269" s="8" t="s">
+        <v>672</v>
+      </c>
+      <c r="B269" s="8" t="s">
+        <v>673</v>
+      </c>
+      <c r="C269" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="D269" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E269" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F269" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G269" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H269" s="8">
+        <v>40</v>
+      </c>
+      <c r="I269" s="8"/>
+      <c r="J269" s="8"/>
+      <c r="K269" s="10"/>
+      <c r="L269" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="M269" s="11" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="270" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A270" s="8" t="s">
+        <v>677</v>
+      </c>
+      <c r="B270" s="8" t="s">
+        <v>678</v>
+      </c>
+      <c r="C270" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="D270" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E270" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F270" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G270" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H270" s="8">
+        <v>40</v>
+      </c>
+      <c r="I270" s="8"/>
+      <c r="J270" s="8"/>
+      <c r="K270" s="10"/>
+      <c r="L270" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="M270" s="11" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="271" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A271" s="8" t="s">
+        <v>718</v>
+      </c>
+      <c r="B271" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="C271" s="9" t="s">
+        <v>715</v>
+      </c>
+      <c r="D271" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E271" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F271" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G271" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H271" s="8">
+        <v>40</v>
+      </c>
+      <c r="I271" s="8"/>
+      <c r="J271" s="8"/>
+      <c r="K271" s="10"/>
+      <c r="L271" s="9" t="s">
+        <v>716</v>
+      </c>
+      <c r="M271" s="11" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="272" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A272" s="8" t="s">
+        <v>713</v>
+      </c>
+      <c r="B272" s="8" t="s">
+        <v>714</v>
+      </c>
+      <c r="C272" s="9" t="s">
+        <v>715</v>
+      </c>
+      <c r="D272" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E272" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F272" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G272" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H272" s="8">
+        <v>40</v>
+      </c>
+      <c r="I272" s="8"/>
+      <c r="J272" s="8"/>
+      <c r="K272" s="10"/>
+      <c r="L272" s="9" t="s">
+        <v>716</v>
+      </c>
+      <c r="M272" s="11" t="s">
+        <v>729</v>
       </c>
     </row>
   </sheetData>
@@ -23250,7 +24710,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E795EE60-EBCD-4B19-B884-654D5F927670}">
-  <dimension ref="A1:S255"/>
+  <dimension ref="A1:S269"/>
   <sheetFormatPr defaultColWidth="16.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -31470,6 +32930,496 @@
       </c>
       <c r="M255" s="11" t="s">
         <v>658</v>
+      </c>
+    </row>
+    <row r="256" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A256" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="B256" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="C256" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="D256" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E256" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F256" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G256" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H256" s="8">
+        <v>40</v>
+      </c>
+      <c r="I256" s="8"/>
+      <c r="J256" s="8"/>
+      <c r="K256" s="10"/>
+      <c r="L256" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M256" s="11" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="257" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A257" s="8" t="s">
+        <v>731</v>
+      </c>
+      <c r="B257" s="8" t="s">
+        <v>701</v>
+      </c>
+      <c r="C257" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="D257" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E257" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F257" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G257" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H257" s="8">
+        <v>40</v>
+      </c>
+      <c r="I257" s="8"/>
+      <c r="J257" s="8"/>
+      <c r="K257" s="10"/>
+      <c r="L257" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M257" s="11" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="258" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A258" s="8" t="s">
+        <v>732</v>
+      </c>
+      <c r="B258" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C258" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="D258" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E258" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F258" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G258" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H258" s="8">
+        <v>40</v>
+      </c>
+      <c r="I258" s="8"/>
+      <c r="J258" s="8"/>
+      <c r="K258" s="10"/>
+      <c r="L258" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M258" s="11" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="259" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A259" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="B259" s="8" t="s">
+        <v>704</v>
+      </c>
+      <c r="C259" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="D259" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E259" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F259" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G259" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H259" s="8">
+        <v>40</v>
+      </c>
+      <c r="I259" s="8"/>
+      <c r="J259" s="8"/>
+      <c r="K259" s="10"/>
+      <c r="L259" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M259" s="11" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="260" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A260" s="8" t="s">
+        <v>736</v>
+      </c>
+      <c r="B260" s="8" t="s">
+        <v>697</v>
+      </c>
+      <c r="C260" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="D260" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E260" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F260" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G260" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H260" s="8">
+        <v>40</v>
+      </c>
+      <c r="I260" s="8"/>
+      <c r="J260" s="8"/>
+      <c r="K260" s="10"/>
+      <c r="L260" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M260" s="11" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="261" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A261" s="8" t="s">
+        <v>680</v>
+      </c>
+      <c r="B261" s="8" t="s">
+        <v>681</v>
+      </c>
+      <c r="C261" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="D261" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E261" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F261" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G261" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H261" s="8">
+        <v>40</v>
+      </c>
+      <c r="I261" s="8"/>
+      <c r="J261" s="8"/>
+      <c r="K261" s="10"/>
+      <c r="L261" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M261" s="11" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="262" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A262" s="8" t="s">
+        <v>688</v>
+      </c>
+      <c r="B262" s="8" t="s">
+        <v>689</v>
+      </c>
+      <c r="C262" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="D262" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E262" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F262" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G262" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H262" s="8">
+        <v>40</v>
+      </c>
+      <c r="I262" s="8"/>
+      <c r="J262" s="8"/>
+      <c r="K262" s="10"/>
+      <c r="L262" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M262" s="11" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="263" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A263" s="8" t="s">
+        <v>690</v>
+      </c>
+      <c r="B263" s="8" t="s">
+        <v>691</v>
+      </c>
+      <c r="C263" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="D263" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E263" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F263" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G263" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="H263" s="8">
+        <v>30</v>
+      </c>
+      <c r="I263" s="8"/>
+      <c r="J263" s="8"/>
+      <c r="K263" s="10"/>
+      <c r="L263" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M263" s="11" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="264" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A264" s="8" t="s">
+        <v>685</v>
+      </c>
+      <c r="B264" s="8" t="s">
+        <v>686</v>
+      </c>
+      <c r="C264" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="D264" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E264" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F264" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G264" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H264" s="8">
+        <v>40</v>
+      </c>
+      <c r="I264" s="8"/>
+      <c r="J264" s="8"/>
+      <c r="K264" s="10"/>
+      <c r="L264" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M264" s="11" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="265" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A265" s="8" t="s">
+        <v>693</v>
+      </c>
+      <c r="B265" s="8" t="s">
+        <v>694</v>
+      </c>
+      <c r="C265" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="D265" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E265" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F265" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G265" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="H265" s="8">
+        <v>30</v>
+      </c>
+      <c r="I265" s="8"/>
+      <c r="J265" s="8"/>
+      <c r="K265" s="10"/>
+      <c r="L265" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M265" s="11" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="266" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A266" s="8" t="s">
+        <v>672</v>
+      </c>
+      <c r="B266" s="8" t="s">
+        <v>673</v>
+      </c>
+      <c r="C266" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="D266" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E266" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F266" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G266" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H266" s="8">
+        <v>40</v>
+      </c>
+      <c r="I266" s="8"/>
+      <c r="J266" s="8"/>
+      <c r="K266" s="10"/>
+      <c r="L266" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="M266" s="11" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="267" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A267" s="8" t="s">
+        <v>677</v>
+      </c>
+      <c r="B267" s="8" t="s">
+        <v>678</v>
+      </c>
+      <c r="C267" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="D267" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E267" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F267" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G267" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H267" s="8">
+        <v>40</v>
+      </c>
+      <c r="I267" s="8"/>
+      <c r="J267" s="8"/>
+      <c r="K267" s="10"/>
+      <c r="L267" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="M267" s="11" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="268" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A268" s="8" t="s">
+        <v>718</v>
+      </c>
+      <c r="B268" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="C268" s="9" t="s">
+        <v>715</v>
+      </c>
+      <c r="D268" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E268" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F268" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G268" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H268" s="8">
+        <v>40</v>
+      </c>
+      <c r="I268" s="8"/>
+      <c r="J268" s="8"/>
+      <c r="K268" s="10"/>
+      <c r="L268" s="9" t="s">
+        <v>716</v>
+      </c>
+      <c r="M268" s="11" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="269" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A269" s="8" t="s">
+        <v>713</v>
+      </c>
+      <c r="B269" s="8" t="s">
+        <v>714</v>
+      </c>
+      <c r="C269" s="9" t="s">
+        <v>715</v>
+      </c>
+      <c r="D269" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E269" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F269" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G269" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H269" s="8">
+        <v>40</v>
+      </c>
+      <c r="I269" s="8"/>
+      <c r="J269" s="8"/>
+      <c r="K269" s="10"/>
+      <c r="L269" s="9" t="s">
+        <v>716</v>
+      </c>
+      <c r="M269" s="11" t="s">
+        <v>742</v>
       </c>
     </row>
   </sheetData>
@@ -31479,7 +33429,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41BB7886-C4B6-45DF-87F2-53652B8B0BB3}">
-  <dimension ref="A1:S252"/>
+  <dimension ref="A1:S266"/>
   <sheetFormatPr defaultColWidth="12.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -39603,6 +41553,496 @@
       </c>
       <c r="M252" s="11" t="s">
         <v>665</v>
+      </c>
+    </row>
+    <row r="253" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A253" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="B253" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="C253" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="D253" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E253" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F253" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G253" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H253" s="8">
+        <v>40</v>
+      </c>
+      <c r="I253" s="8"/>
+      <c r="J253" s="8"/>
+      <c r="K253" s="10"/>
+      <c r="L253" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M253" s="11" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="254" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A254" s="8" t="s">
+        <v>731</v>
+      </c>
+      <c r="B254" s="8" t="s">
+        <v>701</v>
+      </c>
+      <c r="C254" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="D254" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E254" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F254" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G254" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H254" s="8">
+        <v>40</v>
+      </c>
+      <c r="I254" s="8"/>
+      <c r="J254" s="8"/>
+      <c r="K254" s="10"/>
+      <c r="L254" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M254" s="11" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="255" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A255" s="8" t="s">
+        <v>732</v>
+      </c>
+      <c r="B255" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C255" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="D255" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E255" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F255" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G255" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H255" s="8">
+        <v>40</v>
+      </c>
+      <c r="I255" s="8"/>
+      <c r="J255" s="8"/>
+      <c r="K255" s="10"/>
+      <c r="L255" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M255" s="11" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="256" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A256" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="B256" s="8" t="s">
+        <v>704</v>
+      </c>
+      <c r="C256" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="D256" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E256" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F256" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G256" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H256" s="8">
+        <v>40</v>
+      </c>
+      <c r="I256" s="8"/>
+      <c r="J256" s="8"/>
+      <c r="K256" s="10"/>
+      <c r="L256" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M256" s="11" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="257" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A257" s="8" t="s">
+        <v>736</v>
+      </c>
+      <c r="B257" s="8" t="s">
+        <v>697</v>
+      </c>
+      <c r="C257" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="D257" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E257" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F257" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G257" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H257" s="8">
+        <v>40</v>
+      </c>
+      <c r="I257" s="8"/>
+      <c r="J257" s="8"/>
+      <c r="K257" s="10"/>
+      <c r="L257" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M257" s="11" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="258" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A258" s="8" t="s">
+        <v>680</v>
+      </c>
+      <c r="B258" s="8" t="s">
+        <v>681</v>
+      </c>
+      <c r="C258" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="D258" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E258" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F258" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G258" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H258" s="8">
+        <v>40</v>
+      </c>
+      <c r="I258" s="8"/>
+      <c r="J258" s="8"/>
+      <c r="K258" s="10"/>
+      <c r="L258" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M258" s="11" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="259" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A259" s="8" t="s">
+        <v>688</v>
+      </c>
+      <c r="B259" s="8" t="s">
+        <v>689</v>
+      </c>
+      <c r="C259" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="D259" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E259" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F259" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G259" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H259" s="8">
+        <v>40</v>
+      </c>
+      <c r="I259" s="8"/>
+      <c r="J259" s="8"/>
+      <c r="K259" s="10"/>
+      <c r="L259" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M259" s="11" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="260" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A260" s="8" t="s">
+        <v>690</v>
+      </c>
+      <c r="B260" s="8" t="s">
+        <v>691</v>
+      </c>
+      <c r="C260" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="D260" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E260" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F260" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G260" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H260" s="8">
+        <v>40</v>
+      </c>
+      <c r="I260" s="8"/>
+      <c r="J260" s="8"/>
+      <c r="K260" s="10"/>
+      <c r="L260" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M260" s="11" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="261" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A261" s="8" t="s">
+        <v>693</v>
+      </c>
+      <c r="B261" s="8" t="s">
+        <v>694</v>
+      </c>
+      <c r="C261" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="D261" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E261" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F261" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G261" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H261" s="8">
+        <v>40</v>
+      </c>
+      <c r="I261" s="8"/>
+      <c r="J261" s="8"/>
+      <c r="K261" s="10"/>
+      <c r="L261" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M261" s="11" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="262" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A262" s="8" t="s">
+        <v>685</v>
+      </c>
+      <c r="B262" s="8" t="s">
+        <v>686</v>
+      </c>
+      <c r="C262" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="D262" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E262" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F262" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G262" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H262" s="8">
+        <v>40</v>
+      </c>
+      <c r="I262" s="8"/>
+      <c r="J262" s="8"/>
+      <c r="K262" s="10"/>
+      <c r="L262" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M262" s="11" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="263" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A263" s="8" t="s">
+        <v>672</v>
+      </c>
+      <c r="B263" s="8" t="s">
+        <v>673</v>
+      </c>
+      <c r="C263" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="D263" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E263" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="F263" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G263" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H263" s="8">
+        <v>30</v>
+      </c>
+      <c r="I263" s="8"/>
+      <c r="J263" s="8"/>
+      <c r="K263" s="10"/>
+      <c r="L263" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="M263" s="11" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="264" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A264" s="8" t="s">
+        <v>677</v>
+      </c>
+      <c r="B264" s="8" t="s">
+        <v>678</v>
+      </c>
+      <c r="C264" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="D264" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E264" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F264" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G264" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H264" s="8">
+        <v>40</v>
+      </c>
+      <c r="I264" s="8"/>
+      <c r="J264" s="8"/>
+      <c r="K264" s="10"/>
+      <c r="L264" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="M264" s="11" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="265" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A265" s="8" t="s">
+        <v>718</v>
+      </c>
+      <c r="B265" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="C265" s="9" t="s">
+        <v>715</v>
+      </c>
+      <c r="D265" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="E265" s="8" t="s">
+        <v>748</v>
+      </c>
+      <c r="F265" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G265" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H265" s="8">
+        <v>20</v>
+      </c>
+      <c r="I265" s="8"/>
+      <c r="J265" s="8"/>
+      <c r="K265" s="10"/>
+      <c r="L265" s="9" t="s">
+        <v>716</v>
+      </c>
+      <c r="M265" s="11" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="266" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A266" s="8" t="s">
+        <v>713</v>
+      </c>
+      <c r="B266" s="8" t="s">
+        <v>714</v>
+      </c>
+      <c r="C266" s="9" t="s">
+        <v>715</v>
+      </c>
+      <c r="D266" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="E266" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="F266" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G266" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H266" s="8">
+        <v>20</v>
+      </c>
+      <c r="I266" s="8"/>
+      <c r="J266" s="8"/>
+      <c r="K266" s="10"/>
+      <c r="L266" s="9" t="s">
+        <v>716</v>
+      </c>
+      <c r="M266" s="11" t="s">
+        <v>749</v>
       </c>
     </row>
   </sheetData>
@@ -39612,7 +42052,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{083B2BF1-723B-4775-8297-318920D3FD0C}">
-  <dimension ref="A1:S252"/>
+  <dimension ref="A1:S266"/>
   <sheetFormatPr defaultColWidth="13.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -47738,6 +50178,496 @@
         <v>671</v>
       </c>
     </row>
+    <row r="253" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A253" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="B253" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="C253" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="D253" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E253" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F253" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="G253" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H253" s="8">
+        <v>30</v>
+      </c>
+      <c r="I253" s="8"/>
+      <c r="J253" s="8"/>
+      <c r="K253" s="10"/>
+      <c r="L253" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M253" s="11" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="254" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A254" s="8" t="s">
+        <v>731</v>
+      </c>
+      <c r="B254" s="8" t="s">
+        <v>701</v>
+      </c>
+      <c r="C254" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="D254" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E254" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F254" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="G254" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H254" s="8">
+        <v>30</v>
+      </c>
+      <c r="I254" s="8"/>
+      <c r="J254" s="8"/>
+      <c r="K254" s="10"/>
+      <c r="L254" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M254" s="11" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="255" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A255" s="8" t="s">
+        <v>732</v>
+      </c>
+      <c r="B255" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C255" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="D255" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E255" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F255" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="G255" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H255" s="8">
+        <v>30</v>
+      </c>
+      <c r="I255" s="8"/>
+      <c r="J255" s="8"/>
+      <c r="K255" s="10"/>
+      <c r="L255" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M255" s="11" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="256" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A256" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="B256" s="8" t="s">
+        <v>704</v>
+      </c>
+      <c r="C256" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="D256" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E256" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F256" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="G256" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H256" s="8">
+        <v>30</v>
+      </c>
+      <c r="I256" s="8"/>
+      <c r="J256" s="8"/>
+      <c r="K256" s="10"/>
+      <c r="L256" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M256" s="11" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="257" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A257" s="8" t="s">
+        <v>736</v>
+      </c>
+      <c r="B257" s="8" t="s">
+        <v>697</v>
+      </c>
+      <c r="C257" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="D257" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E257" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F257" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="G257" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H257" s="8">
+        <v>30</v>
+      </c>
+      <c r="I257" s="8"/>
+      <c r="J257" s="8"/>
+      <c r="K257" s="10"/>
+      <c r="L257" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M257" s="11" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="258" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A258" s="8" t="s">
+        <v>693</v>
+      </c>
+      <c r="B258" s="8" t="s">
+        <v>694</v>
+      </c>
+      <c r="C258" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="D258" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E258" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F258" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="G258" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H258" s="8">
+        <v>40</v>
+      </c>
+      <c r="I258" s="8"/>
+      <c r="J258" s="8"/>
+      <c r="K258" s="10"/>
+      <c r="L258" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M258" s="11" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="259" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A259" s="8" t="s">
+        <v>680</v>
+      </c>
+      <c r="B259" s="8" t="s">
+        <v>681</v>
+      </c>
+      <c r="C259" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="D259" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E259" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F259" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="G259" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H259" s="8">
+        <v>40</v>
+      </c>
+      <c r="I259" s="8"/>
+      <c r="J259" s="8"/>
+      <c r="K259" s="10"/>
+      <c r="L259" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M259" s="11" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="260" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A260" s="8" t="s">
+        <v>688</v>
+      </c>
+      <c r="B260" s="8" t="s">
+        <v>689</v>
+      </c>
+      <c r="C260" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="D260" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E260" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F260" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="G260" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H260" s="8">
+        <v>40</v>
+      </c>
+      <c r="I260" s="8"/>
+      <c r="J260" s="8"/>
+      <c r="K260" s="10"/>
+      <c r="L260" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M260" s="11" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="261" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A261" s="8" t="s">
+        <v>690</v>
+      </c>
+      <c r="B261" s="8" t="s">
+        <v>691</v>
+      </c>
+      <c r="C261" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="D261" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E261" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F261" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="G261" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H261" s="8">
+        <v>40</v>
+      </c>
+      <c r="I261" s="8"/>
+      <c r="J261" s="8"/>
+      <c r="K261" s="10"/>
+      <c r="L261" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M261" s="11" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="262" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A262" s="8" t="s">
+        <v>685</v>
+      </c>
+      <c r="B262" s="8" t="s">
+        <v>686</v>
+      </c>
+      <c r="C262" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="D262" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E262" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F262" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="G262" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H262" s="8">
+        <v>40</v>
+      </c>
+      <c r="I262" s="8"/>
+      <c r="J262" s="8"/>
+      <c r="K262" s="10"/>
+      <c r="L262" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="M262" s="11" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="263" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A263" s="8" t="s">
+        <v>672</v>
+      </c>
+      <c r="B263" s="8" t="s">
+        <v>673</v>
+      </c>
+      <c r="C263" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="D263" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E263" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F263" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="G263" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H263" s="8">
+        <v>40</v>
+      </c>
+      <c r="I263" s="8"/>
+      <c r="J263" s="8"/>
+      <c r="K263" s="10"/>
+      <c r="L263" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="M263" s="11" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="264" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A264" s="8" t="s">
+        <v>677</v>
+      </c>
+      <c r="B264" s="8" t="s">
+        <v>678</v>
+      </c>
+      <c r="C264" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="D264" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E264" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F264" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="G264" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H264" s="8">
+        <v>40</v>
+      </c>
+      <c r="I264" s="8"/>
+      <c r="J264" s="8"/>
+      <c r="K264" s="10"/>
+      <c r="L264" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="M264" s="11" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="265" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A265" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B265" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="C265" s="9" t="s">
+        <v>715</v>
+      </c>
+      <c r="D265" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E265" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F265" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="G265" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H265" s="8">
+        <v>40</v>
+      </c>
+      <c r="I265" s="8"/>
+      <c r="J265" s="8"/>
+      <c r="K265" s="10"/>
+      <c r="L265" s="9" t="s">
+        <v>716</v>
+      </c>
+      <c r="M265" s="11" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="266" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A266" s="8" t="s">
+        <v>760</v>
+      </c>
+      <c r="B266" s="8" t="s">
+        <v>714</v>
+      </c>
+      <c r="C266" s="9" t="s">
+        <v>715</v>
+      </c>
+      <c r="D266" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E266" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F266" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="G266" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H266" s="8">
+        <v>40</v>
+      </c>
+      <c r="I266" s="8"/>
+      <c r="J266" s="8"/>
+      <c r="K266" s="10"/>
+      <c r="L266" s="9" t="s">
+        <v>716</v>
+      </c>
+      <c r="M266" s="11" t="s">
+        <v>761</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/data/Integracao Armazem.xlsx
+++ b/data/Integracao Armazem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58DE67F7-4FBA-4A9E-B6E3-AECE1E5EB479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D29B8032-1AEE-4417-AB4D-97F83E862284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="4" xr2:uid="{422D47E6-8DC3-4B25-BD50-E675C15B05CB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{422D47E6-8DC3-4B25-BD50-E675C15B05CB}"/>
   </bookViews>
   <sheets>
     <sheet name="M1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8999" uniqueCount="762">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9136" uniqueCount="792">
   <si>
     <t>Selecione o EPI que NÃO é obrigatório durante o processo de montagem de paletes</t>
   </si>
@@ -2445,6 +2445,96 @@
   </si>
   <si>
     <t>11:50</t>
+  </si>
+  <si>
+    <t>ANDERSON DUCLOSIL</t>
+  </si>
+  <si>
+    <t>23697071866</t>
+  </si>
+  <si>
+    <t>11/05/2026</t>
+  </si>
+  <si>
+    <t>12/05/2026</t>
+  </si>
+  <si>
+    <t>15:34</t>
+  </si>
+  <si>
+    <t>ECTOR LUDIERY REIS</t>
+  </si>
+  <si>
+    <t>13081603994</t>
+  </si>
+  <si>
+    <t>14/05/2026</t>
+  </si>
+  <si>
+    <t>15/05/2026</t>
+  </si>
+  <si>
+    <t>15:03</t>
+  </si>
+  <si>
+    <t>Gabriel Ribeiro Luongo</t>
+  </si>
+  <si>
+    <t>86721194015</t>
+  </si>
+  <si>
+    <t>MAYCK VINICIUS PROTAZIO SANTOS</t>
+  </si>
+  <si>
+    <t>05718728593</t>
+  </si>
+  <si>
+    <t>06/05/2026</t>
+  </si>
+  <si>
+    <t>18/05/2026</t>
+  </si>
+  <si>
+    <t>15:33</t>
+  </si>
+  <si>
+    <t>Devemos ter garantir a maior parte do Picking com produtos de baixo giro, pois têm mais saída</t>
+  </si>
+  <si>
+    <t>15:39</t>
+  </si>
+  <si>
+    <t>15:35</t>
+  </si>
+  <si>
+    <t>Após a separação do palete, o mesmo é liberado para carregamento</t>
+  </si>
+  <si>
+    <t>15:44</t>
+  </si>
+  <si>
+    <t>13/05/2026</t>
+  </si>
+  <si>
+    <t>10:28</t>
+  </si>
+  <si>
+    <t>15:46</t>
+  </si>
+  <si>
+    <t>02021353907</t>
+  </si>
+  <si>
+    <t>12/02/2026</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>15:48</t>
+  </si>
+  <si>
+    <t>10:36</t>
   </si>
 </sst>
 </file>
@@ -2834,7 +2924,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D8EC4C0-DEF5-4A13-83D8-46C06041A7DF}">
-  <dimension ref="A1:S276"/>
+  <dimension ref="A1:S280"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="19" width="14.109375" customWidth="1"/>
@@ -15884,6 +15974,206 @@
         <v>720</v>
       </c>
     </row>
+    <row r="277" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A277" s="8" t="s">
+        <v>762</v>
+      </c>
+      <c r="B277" s="8" t="s">
+        <v>763</v>
+      </c>
+      <c r="C277" s="9" t="s">
+        <v>764</v>
+      </c>
+      <c r="D277" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E277" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F277" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G277" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H277" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I277" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J277" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K277" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="L277" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M277" s="8">
+        <v>80</v>
+      </c>
+      <c r="N277" s="8"/>
+      <c r="O277" s="8"/>
+      <c r="P277" s="10"/>
+      <c r="Q277" s="9" t="s">
+        <v>765</v>
+      </c>
+      <c r="R277" s="11" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="278" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A278" s="8" t="s">
+        <v>767</v>
+      </c>
+      <c r="B278" s="8" t="s">
+        <v>768</v>
+      </c>
+      <c r="C278" s="9" t="s">
+        <v>769</v>
+      </c>
+      <c r="D278" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E278" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F278" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G278" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H278" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I278" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J278" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K278" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="L278" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M278" s="8">
+        <v>80</v>
+      </c>
+      <c r="N278" s="8"/>
+      <c r="O278" s="8"/>
+      <c r="P278" s="10"/>
+      <c r="Q278" s="9" t="s">
+        <v>770</v>
+      </c>
+      <c r="R278" s="11" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="279" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A279" s="8" t="s">
+        <v>772</v>
+      </c>
+      <c r="B279" s="8" t="s">
+        <v>773</v>
+      </c>
+      <c r="C279" s="9" t="s">
+        <v>769</v>
+      </c>
+      <c r="D279" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E279" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F279" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G279" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H279" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I279" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J279" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="K279" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="L279" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M279" s="8">
+        <v>70</v>
+      </c>
+      <c r="N279" s="8"/>
+      <c r="O279" s="8"/>
+      <c r="P279" s="10"/>
+      <c r="Q279" s="9" t="s">
+        <v>770</v>
+      </c>
+      <c r="R279" s="11" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="280" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A280" s="8" t="s">
+        <v>774</v>
+      </c>
+      <c r="B280" s="8" t="s">
+        <v>775</v>
+      </c>
+      <c r="C280" s="9" t="s">
+        <v>776</v>
+      </c>
+      <c r="D280" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E280" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F280" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G280" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H280" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I280" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J280" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K280" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L280" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M280" s="8">
+        <v>90</v>
+      </c>
+      <c r="N280" s="8"/>
+      <c r="O280" s="8"/>
+      <c r="P280" s="10"/>
+      <c r="Q280" s="9" t="s">
+        <v>777</v>
+      </c>
+      <c r="R280" s="11" t="s">
+        <v>778</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -15892,7 +16182,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9848E97-FB23-44B1-9CE3-C616F78A0A8B}">
-  <dimension ref="A1:S272"/>
+  <dimension ref="A1:S274"/>
   <sheetFormatPr defaultColWidth="15.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -24701,6 +24991,76 @@
       </c>
       <c r="M272" s="11" t="s">
         <v>729</v>
+      </c>
+    </row>
+    <row r="273" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A273" s="8" t="s">
+        <v>762</v>
+      </c>
+      <c r="B273" s="8" t="s">
+        <v>763</v>
+      </c>
+      <c r="C273" s="9" t="s">
+        <v>764</v>
+      </c>
+      <c r="D273" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E273" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="F273" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="G273" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="H273" s="8">
+        <v>10</v>
+      </c>
+      <c r="I273" s="8"/>
+      <c r="J273" s="8"/>
+      <c r="K273" s="10"/>
+      <c r="L273" s="9" t="s">
+        <v>765</v>
+      </c>
+      <c r="M273" s="11" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="274" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A274" s="8" t="s">
+        <v>774</v>
+      </c>
+      <c r="B274" s="8" t="s">
+        <v>775</v>
+      </c>
+      <c r="C274" s="9" t="s">
+        <v>776</v>
+      </c>
+      <c r="D274" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E274" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F274" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G274" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H274" s="8">
+        <v>40</v>
+      </c>
+      <c r="I274" s="8"/>
+      <c r="J274" s="8"/>
+      <c r="K274" s="10"/>
+      <c r="L274" s="9" t="s">
+        <v>777</v>
+      </c>
+      <c r="M274" s="11" t="s">
+        <v>781</v>
       </c>
     </row>
   </sheetData>
@@ -24710,7 +25070,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E795EE60-EBCD-4B19-B884-654D5F927670}">
-  <dimension ref="A1:S269"/>
+  <dimension ref="A1:S271"/>
   <sheetFormatPr defaultColWidth="16.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -33420,6 +33780,76 @@
       </c>
       <c r="M269" s="11" t="s">
         <v>742</v>
+      </c>
+    </row>
+    <row r="270" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A270" s="8" t="s">
+        <v>774</v>
+      </c>
+      <c r="B270" s="8" t="s">
+        <v>775</v>
+      </c>
+      <c r="C270" s="9" t="s">
+        <v>776</v>
+      </c>
+      <c r="D270" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E270" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F270" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G270" s="8" t="s">
+        <v>782</v>
+      </c>
+      <c r="H270" s="8">
+        <v>30</v>
+      </c>
+      <c r="I270" s="8"/>
+      <c r="J270" s="8"/>
+      <c r="K270" s="10"/>
+      <c r="L270" s="9" t="s">
+        <v>777</v>
+      </c>
+      <c r="M270" s="11" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="271" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A271" s="8" t="s">
+        <v>762</v>
+      </c>
+      <c r="B271" s="8" t="s">
+        <v>763</v>
+      </c>
+      <c r="C271" s="9" t="s">
+        <v>764</v>
+      </c>
+      <c r="D271" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E271" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F271" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G271" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="H271" s="8">
+        <v>30</v>
+      </c>
+      <c r="I271" s="8"/>
+      <c r="J271" s="8"/>
+      <c r="K271" s="10"/>
+      <c r="L271" s="9" t="s">
+        <v>784</v>
+      </c>
+      <c r="M271" s="11" t="s">
+        <v>785</v>
       </c>
     </row>
   </sheetData>
@@ -33429,7 +33859,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41BB7886-C4B6-45DF-87F2-53652B8B0BB3}">
-  <dimension ref="A1:S266"/>
+  <dimension ref="A1:S269"/>
   <sheetFormatPr defaultColWidth="12.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -42043,6 +42473,111 @@
       </c>
       <c r="M266" s="11" t="s">
         <v>749</v>
+      </c>
+    </row>
+    <row r="267" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A267" s="8" t="s">
+        <v>774</v>
+      </c>
+      <c r="B267" s="8" t="s">
+        <v>775</v>
+      </c>
+      <c r="C267" s="9" t="s">
+        <v>776</v>
+      </c>
+      <c r="D267" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E267" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F267" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G267" s="8" t="s">
+        <v>661</v>
+      </c>
+      <c r="H267" s="8">
+        <v>30</v>
+      </c>
+      <c r="I267" s="8"/>
+      <c r="J267" s="8"/>
+      <c r="K267" s="10"/>
+      <c r="L267" s="9" t="s">
+        <v>777</v>
+      </c>
+      <c r="M267" s="11" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="268" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A268" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="B268" s="8" t="s">
+        <v>787</v>
+      </c>
+      <c r="C268" s="9" t="s">
+        <v>788</v>
+      </c>
+      <c r="D268" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="E268" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F268" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G268" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H268" s="8">
+        <v>30</v>
+      </c>
+      <c r="I268" s="8"/>
+      <c r="J268" s="8"/>
+      <c r="K268" s="10"/>
+      <c r="L268" s="9" t="s">
+        <v>777</v>
+      </c>
+      <c r="M268" s="11" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="269" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A269" s="8" t="s">
+        <v>762</v>
+      </c>
+      <c r="B269" s="8" t="s">
+        <v>763</v>
+      </c>
+      <c r="C269" s="9" t="s">
+        <v>764</v>
+      </c>
+      <c r="D269" s="8" t="s">
+        <v>519</v>
+      </c>
+      <c r="E269" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F269" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G269" s="8" t="s">
+        <v>661</v>
+      </c>
+      <c r="H269" s="8">
+        <v>20</v>
+      </c>
+      <c r="I269" s="8"/>
+      <c r="J269" s="8"/>
+      <c r="K269" s="10"/>
+      <c r="L269" s="9" t="s">
+        <v>784</v>
+      </c>
+      <c r="M269" s="11" t="s">
+        <v>687</v>
       </c>
     </row>
   </sheetData>
@@ -42052,7 +42587,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{083B2BF1-723B-4775-8297-318920D3FD0C}">
-  <dimension ref="A1:S266"/>
+  <dimension ref="A1:S268"/>
   <sheetFormatPr defaultColWidth="13.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -50668,6 +51203,76 @@
         <v>761</v>
       </c>
     </row>
+    <row r="267" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A267" s="8" t="s">
+        <v>774</v>
+      </c>
+      <c r="B267" s="8" t="s">
+        <v>775</v>
+      </c>
+      <c r="C267" s="9" t="s">
+        <v>776</v>
+      </c>
+      <c r="D267" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E267" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F267" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="G267" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H267" s="8">
+        <v>40</v>
+      </c>
+      <c r="I267" s="8"/>
+      <c r="J267" s="8"/>
+      <c r="K267" s="10"/>
+      <c r="L267" s="9" t="s">
+        <v>777</v>
+      </c>
+      <c r="M267" s="11" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="268" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A268" s="8" t="s">
+        <v>762</v>
+      </c>
+      <c r="B268" s="8" t="s">
+        <v>763</v>
+      </c>
+      <c r="C268" s="9" t="s">
+        <v>764</v>
+      </c>
+      <c r="D268" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="E268" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F268" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="G268" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H268" s="8">
+        <v>30</v>
+      </c>
+      <c r="I268" s="8"/>
+      <c r="J268" s="8"/>
+      <c r="K268" s="10"/>
+      <c r="L268" s="9" t="s">
+        <v>784</v>
+      </c>
+      <c r="M268" s="11" t="s">
+        <v>791</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/data/Integracao Armazem.xlsx
+++ b/data/Integracao Armazem.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D29B8032-1AEE-4417-AB4D-97F83E862284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D096CEA-766F-49DE-8BB9-BFEFCBB1D962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{422D47E6-8DC3-4B25-BD50-E675C15B05CB}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9136" uniqueCount="792">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10193" uniqueCount="907">
   <si>
     <t>Selecione o EPI que NÃO é obrigatório durante o processo de montagem de paletes</t>
   </si>
@@ -2535,6 +2535,351 @@
   </si>
   <si>
     <t>10:36</t>
+  </si>
+  <si>
+    <t>Fabio Fabris da Silva</t>
+  </si>
+  <si>
+    <t>146.489.159-17</t>
+  </si>
+  <si>
+    <t>21/05/2026</t>
+  </si>
+  <si>
+    <t>25/05/2026</t>
+  </si>
+  <si>
+    <t>09:46</t>
+  </si>
+  <si>
+    <t>Evair Cardoso dos Santos</t>
+  </si>
+  <si>
+    <t>07004471560</t>
+  </si>
+  <si>
+    <t>26/05/2026</t>
+  </si>
+  <si>
+    <t>16:19</t>
+  </si>
+  <si>
+    <t>Gabriel dos Santos Anastacio</t>
+  </si>
+  <si>
+    <t>07950074507</t>
+  </si>
+  <si>
+    <t>15:58</t>
+  </si>
+  <si>
+    <t>Carlos Henrique Aragão De Santana</t>
+  </si>
+  <si>
+    <t>868.348.335-52</t>
+  </si>
+  <si>
+    <t>Kauã Bruno Gomes Dias</t>
+  </si>
+  <si>
+    <t>08065194524</t>
+  </si>
+  <si>
+    <t>15:56</t>
+  </si>
+  <si>
+    <t>Allan Ferreira Miranda Silva</t>
+  </si>
+  <si>
+    <t>828.014.955-49</t>
+  </si>
+  <si>
+    <t>15:54</t>
+  </si>
+  <si>
+    <t>Daniel dos Santos Freitas</t>
+  </si>
+  <si>
+    <t>06274840508</t>
+  </si>
+  <si>
+    <t>15:52</t>
+  </si>
+  <si>
+    <t>elias Francisco de Jesus</t>
+  </si>
+  <si>
+    <t>04566699579</t>
+  </si>
+  <si>
+    <t>15:51</t>
+  </si>
+  <si>
+    <t>Leonardo dos anjos Almeida</t>
+  </si>
+  <si>
+    <t>85056359572</t>
+  </si>
+  <si>
+    <t>Luis Filipe Dantas Da Silva</t>
+  </si>
+  <si>
+    <t>86229838540</t>
+  </si>
+  <si>
+    <t>15:49</t>
+  </si>
+  <si>
+    <t>Paulo Alexandre Oliveira Santos</t>
+  </si>
+  <si>
+    <t>86152039541</t>
+  </si>
+  <si>
+    <t>Jonailton batista dos santos primo</t>
+  </si>
+  <si>
+    <t>86496982554</t>
+  </si>
+  <si>
+    <t>Matheus Souza Silva dos Santos</t>
+  </si>
+  <si>
+    <t>864.511.055-54</t>
+  </si>
+  <si>
+    <t>Gustavo Almeida de Sousa</t>
+  </si>
+  <si>
+    <t>02530517541</t>
+  </si>
+  <si>
+    <t>15:47</t>
+  </si>
+  <si>
+    <t>ERICK MARCOS LOPES DOS SANTOS</t>
+  </si>
+  <si>
+    <t>06630823745</t>
+  </si>
+  <si>
+    <t>Rodrigo Moreira Protasio</t>
+  </si>
+  <si>
+    <t>09888627511</t>
+  </si>
+  <si>
+    <t>Misael Bahiana da Cruz</t>
+  </si>
+  <si>
+    <t>10599343532</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>Thiago da Silva de Jesus</t>
+  </si>
+  <si>
+    <t>03831061505</t>
+  </si>
+  <si>
+    <t>Luiz Felipe da Silva</t>
+  </si>
+  <si>
+    <t>087210319</t>
+  </si>
+  <si>
+    <t>27/05/2026</t>
+  </si>
+  <si>
+    <t>11:57</t>
+  </si>
+  <si>
+    <t>Jean Carlos Fortunato</t>
+  </si>
+  <si>
+    <t>10015709957</t>
+  </si>
+  <si>
+    <t>11:56</t>
+  </si>
+  <si>
+    <t>Rodrigo Mendes da silva</t>
+  </si>
+  <si>
+    <t>12943058912</t>
+  </si>
+  <si>
+    <t>28/05/2026</t>
+  </si>
+  <si>
+    <t>23:58</t>
+  </si>
+  <si>
+    <t>Sedemar vargas</t>
+  </si>
+  <si>
+    <t>06466473937</t>
+  </si>
+  <si>
+    <t>23:51</t>
+  </si>
+  <si>
+    <t>RAI DA SILVA SANTOS</t>
+  </si>
+  <si>
+    <t>11951310543</t>
+  </si>
+  <si>
+    <t>29/05/2026</t>
+  </si>
+  <si>
+    <t>16:06</t>
+  </si>
+  <si>
+    <t>Wendel Costa Santos</t>
+  </si>
+  <si>
+    <t>096.455.055-50</t>
+  </si>
+  <si>
+    <t>Irlan Barreto Lopes Ramos</t>
+  </si>
+  <si>
+    <t>86638485520</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>16:25</t>
+  </si>
+  <si>
+    <t>16:21</t>
+  </si>
+  <si>
+    <t>Gabriel dos Santos Anastácio</t>
+  </si>
+  <si>
+    <t>16:20</t>
+  </si>
+  <si>
+    <t>16:18</t>
+  </si>
+  <si>
+    <t>Jonailton Batista dos Santos primo</t>
+  </si>
+  <si>
+    <t>16:16</t>
+  </si>
+  <si>
+    <t>MISAEL BAHIANA DA CRUZ</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>O endereço do Picking não precisa ser padronizado</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>08721031967</t>
+  </si>
+  <si>
+    <t>16:44</t>
+  </si>
+  <si>
+    <t>16:43</t>
+  </si>
+  <si>
+    <t>Daniel dos Santos Silva</t>
+  </si>
+  <si>
+    <t>079.500.745-07</t>
+  </si>
+  <si>
+    <t>Lastro dos produtos, chapatex e papelão</t>
+  </si>
+  <si>
+    <t>16:42</t>
+  </si>
+  <si>
+    <t>16:41</t>
+  </si>
+  <si>
+    <t>16:40</t>
+  </si>
+  <si>
+    <t>16:39</t>
+  </si>
+  <si>
+    <t>Caixas de leite podem ficar na base do palete</t>
+  </si>
+  <si>
+    <t>14:21</t>
+  </si>
+  <si>
+    <t>10:27</t>
+  </si>
+  <si>
+    <t>14:33</t>
+  </si>
+  <si>
+    <t>14:28</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>14:13</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>14:06</t>
+  </si>
+  <si>
+    <t>14:03</t>
+  </si>
+  <si>
+    <t>14:02</t>
+  </si>
+  <si>
+    <t>14:01</t>
+  </si>
+  <si>
+    <t>13:59</t>
+  </si>
+  <si>
+    <t>14:37</t>
+  </si>
+  <si>
+    <t>Separar quantidade correta e do produto correto, porém avariado</t>
+  </si>
+  <si>
+    <t>14:32</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>Separar quantidade a menos do produto correto</t>
+  </si>
+  <si>
+    <t>A remuneração variável é calculada pelo tempo que fico com o palete aberto</t>
+  </si>
+  <si>
+    <t>Ponto laboral, hora extra e paletes montados</t>
+  </si>
+  <si>
+    <t>14:27</t>
+  </si>
+  <si>
+    <t>14:24</t>
   </si>
 </sst>
 </file>
@@ -2924,7 +3269,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D8EC4C0-DEF5-4A13-83D8-46C06041A7DF}">
-  <dimension ref="A1:S280"/>
+  <dimension ref="A1:S306"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="19" width="14.109375" customWidth="1"/>
@@ -16174,6 +16519,1306 @@
         <v>778</v>
       </c>
     </row>
+    <row r="281" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A281" s="8" t="s">
+        <v>792</v>
+      </c>
+      <c r="B281" s="8" t="s">
+        <v>793</v>
+      </c>
+      <c r="C281" s="9" t="s">
+        <v>794</v>
+      </c>
+      <c r="D281" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E281" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F281" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G281" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H281" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I281" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J281" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K281" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L281" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M281" s="8">
+        <v>90</v>
+      </c>
+      <c r="N281" s="8"/>
+      <c r="O281" s="8"/>
+      <c r="P281" s="10"/>
+      <c r="Q281" s="9" t="s">
+        <v>795</v>
+      </c>
+      <c r="R281" s="11" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="282" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A282" s="8" t="s">
+        <v>797</v>
+      </c>
+      <c r="B282" s="8" t="s">
+        <v>798</v>
+      </c>
+      <c r="C282" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D282" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="E282" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F282" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G282" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H282" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="I282" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J282" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K282" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="L282" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M282" s="8">
+        <v>60</v>
+      </c>
+      <c r="N282" s="8"/>
+      <c r="O282" s="8"/>
+      <c r="P282" s="10"/>
+      <c r="Q282" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="R282" s="11" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="283" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A283" s="8" t="s">
+        <v>801</v>
+      </c>
+      <c r="B283" s="8" t="s">
+        <v>802</v>
+      </c>
+      <c r="C283" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D283" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E283" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F283" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G283" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H283" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="I283" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J283" s="8" t="s">
+        <v>569</v>
+      </c>
+      <c r="K283" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="L283" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M283" s="8">
+        <v>60</v>
+      </c>
+      <c r="N283" s="8"/>
+      <c r="O283" s="8"/>
+      <c r="P283" s="10"/>
+      <c r="Q283" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="R283" s="11" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="284" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A284" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="B284" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="C284" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D284" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E284" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F284" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G284" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H284" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I284" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J284" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K284" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L284" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="M284" s="8">
+        <v>70</v>
+      </c>
+      <c r="N284" s="8"/>
+      <c r="O284" s="8"/>
+      <c r="P284" s="10"/>
+      <c r="Q284" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="R284" s="11" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="285" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A285" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="B285" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="C285" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D285" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E285" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F285" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G285" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H285" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I285" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J285" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K285" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L285" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M285" s="8">
+        <v>90</v>
+      </c>
+      <c r="N285" s="8"/>
+      <c r="O285" s="8"/>
+      <c r="P285" s="10"/>
+      <c r="Q285" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="R285" s="11" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="286" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A286" s="8" t="s">
+        <v>809</v>
+      </c>
+      <c r="B286" s="8" t="s">
+        <v>810</v>
+      </c>
+      <c r="C286" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D286" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E286" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F286" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G286" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H286" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I286" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J286" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K286" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="L286" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M286" s="8">
+        <v>70</v>
+      </c>
+      <c r="N286" s="8"/>
+      <c r="O286" s="8"/>
+      <c r="P286" s="10"/>
+      <c r="Q286" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="R286" s="11" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="287" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A287" s="8" t="s">
+        <v>812</v>
+      </c>
+      <c r="B287" s="8" t="s">
+        <v>813</v>
+      </c>
+      <c r="C287" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D287" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E287" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F287" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G287" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="H287" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I287" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="J287" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K287" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="L287" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M287" s="8">
+        <v>50</v>
+      </c>
+      <c r="N287" s="8"/>
+      <c r="O287" s="8"/>
+      <c r="P287" s="10"/>
+      <c r="Q287" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="R287" s="11" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="288" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A288" s="8" t="s">
+        <v>815</v>
+      </c>
+      <c r="B288" s="8" t="s">
+        <v>816</v>
+      </c>
+      <c r="C288" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D288" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E288" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F288" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G288" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H288" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I288" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J288" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K288" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="L288" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M288" s="8">
+        <v>70</v>
+      </c>
+      <c r="N288" s="8"/>
+      <c r="O288" s="8"/>
+      <c r="P288" s="10"/>
+      <c r="Q288" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="R288" s="11" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="289" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A289" s="8" t="s">
+        <v>818</v>
+      </c>
+      <c r="B289" s="8" t="s">
+        <v>819</v>
+      </c>
+      <c r="C289" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D289" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E289" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F289" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G289" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H289" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="I289" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J289" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K289" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="L289" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="M289" s="8">
+        <v>60</v>
+      </c>
+      <c r="N289" s="8"/>
+      <c r="O289" s="8"/>
+      <c r="P289" s="10"/>
+      <c r="Q289" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="R289" s="11" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="290" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A290" s="8" t="s">
+        <v>820</v>
+      </c>
+      <c r="B290" s="8" t="s">
+        <v>821</v>
+      </c>
+      <c r="C290" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D290" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E290" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F290" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G290" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H290" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I290" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J290" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K290" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L290" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M290" s="8">
+        <v>90</v>
+      </c>
+      <c r="N290" s="8"/>
+      <c r="O290" s="8"/>
+      <c r="P290" s="10"/>
+      <c r="Q290" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="R290" s="11" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="291" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A291" s="8" t="s">
+        <v>823</v>
+      </c>
+      <c r="B291" s="8" t="s">
+        <v>824</v>
+      </c>
+      <c r="C291" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D291" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E291" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F291" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G291" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H291" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I291" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J291" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K291" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L291" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M291" s="8">
+        <v>90</v>
+      </c>
+      <c r="N291" s="8"/>
+      <c r="O291" s="8"/>
+      <c r="P291" s="10"/>
+      <c r="Q291" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="R291" s="11" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="292" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A292" s="8" t="s">
+        <v>797</v>
+      </c>
+      <c r="B292" s="8" t="s">
+        <v>798</v>
+      </c>
+      <c r="C292" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D292" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E292" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F292" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G292" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H292" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I292" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J292" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K292" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="L292" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M292" s="8">
+        <v>70</v>
+      </c>
+      <c r="N292" s="8"/>
+      <c r="O292" s="8"/>
+      <c r="P292" s="10"/>
+      <c r="Q292" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="R292" s="11" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="293" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A293" s="8" t="s">
+        <v>825</v>
+      </c>
+      <c r="B293" s="8" t="s">
+        <v>826</v>
+      </c>
+      <c r="C293" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D293" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E293" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F293" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G293" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H293" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I293" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J293" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K293" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L293" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M293" s="8">
+        <v>90</v>
+      </c>
+      <c r="N293" s="8"/>
+      <c r="O293" s="8"/>
+      <c r="P293" s="10"/>
+      <c r="Q293" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="R293" s="11" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="294" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A294" s="8" t="s">
+        <v>827</v>
+      </c>
+      <c r="B294" s="8" t="s">
+        <v>828</v>
+      </c>
+      <c r="C294" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D294" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E294" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F294" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G294" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H294" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I294" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J294" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K294" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L294" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M294" s="8">
+        <v>90</v>
+      </c>
+      <c r="N294" s="8"/>
+      <c r="O294" s="8"/>
+      <c r="P294" s="10"/>
+      <c r="Q294" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="R294" s="11" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="295" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A295" s="8" t="s">
+        <v>829</v>
+      </c>
+      <c r="B295" s="8" t="s">
+        <v>830</v>
+      </c>
+      <c r="C295" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D295" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E295" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F295" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G295" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H295" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I295" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J295" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K295" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L295" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M295" s="8">
+        <v>90</v>
+      </c>
+      <c r="N295" s="8"/>
+      <c r="O295" s="8"/>
+      <c r="P295" s="10"/>
+      <c r="Q295" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="R295" s="11" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="296" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A296" s="8" t="s">
+        <v>832</v>
+      </c>
+      <c r="B296" s="8" t="s">
+        <v>833</v>
+      </c>
+      <c r="C296" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D296" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E296" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F296" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G296" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H296" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I296" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J296" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K296" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L296" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M296" s="8">
+        <v>90</v>
+      </c>
+      <c r="N296" s="8"/>
+      <c r="O296" s="8"/>
+      <c r="P296" s="10"/>
+      <c r="Q296" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="R296" s="11" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="297" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A297" s="8" t="s">
+        <v>834</v>
+      </c>
+      <c r="B297" s="8" t="s">
+        <v>835</v>
+      </c>
+      <c r="C297" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D297" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E297" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F297" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G297" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H297" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I297" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J297" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K297" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="L297" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M297" s="8">
+        <v>80</v>
+      </c>
+      <c r="N297" s="8"/>
+      <c r="O297" s="8"/>
+      <c r="P297" s="10"/>
+      <c r="Q297" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="R297" s="11" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="298" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A298" s="8" t="s">
+        <v>836</v>
+      </c>
+      <c r="B298" s="8" t="s">
+        <v>837</v>
+      </c>
+      <c r="C298" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D298" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E298" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F298" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G298" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H298" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I298" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J298" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K298" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L298" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M298" s="8">
+        <v>90</v>
+      </c>
+      <c r="N298" s="8"/>
+      <c r="O298" s="8"/>
+      <c r="P298" s="10"/>
+      <c r="Q298" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="R298" s="11" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="299" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A299" s="8" t="s">
+        <v>839</v>
+      </c>
+      <c r="B299" s="8" t="s">
+        <v>840</v>
+      </c>
+      <c r="C299" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D299" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E299" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F299" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G299" s="8" t="s">
+        <v>683</v>
+      </c>
+      <c r="H299" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="I299" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J299" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K299" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="L299" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M299" s="8">
+        <v>60</v>
+      </c>
+      <c r="N299" s="8"/>
+      <c r="O299" s="8"/>
+      <c r="P299" s="10"/>
+      <c r="Q299" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="R299" s="11" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="300" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A300" s="8" t="s">
+        <v>841</v>
+      </c>
+      <c r="B300" s="8" t="s">
+        <v>842</v>
+      </c>
+      <c r="C300" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D300" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E300" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F300" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G300" s="8" t="s">
+        <v>683</v>
+      </c>
+      <c r="H300" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I300" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J300" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K300" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L300" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="M300" s="8">
+        <v>70</v>
+      </c>
+      <c r="N300" s="8"/>
+      <c r="O300" s="8"/>
+      <c r="P300" s="10"/>
+      <c r="Q300" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="R300" s="11" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="301" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A301" s="8" t="s">
+        <v>845</v>
+      </c>
+      <c r="B301" s="8" t="s">
+        <v>846</v>
+      </c>
+      <c r="C301" s="9" t="s">
+        <v>795</v>
+      </c>
+      <c r="D301" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E301" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F301" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G301" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H301" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="I301" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J301" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K301" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="L301" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M301" s="8">
+        <v>70</v>
+      </c>
+      <c r="N301" s="8"/>
+      <c r="O301" s="8"/>
+      <c r="P301" s="10"/>
+      <c r="Q301" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="R301" s="11" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="302" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A302" s="8" t="s">
+        <v>848</v>
+      </c>
+      <c r="B302" s="8" t="s">
+        <v>849</v>
+      </c>
+      <c r="C302" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D302" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E302" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F302" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G302" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H302" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I302" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J302" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K302" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L302" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M302" s="8">
+        <v>90</v>
+      </c>
+      <c r="N302" s="8"/>
+      <c r="O302" s="8"/>
+      <c r="P302" s="10"/>
+      <c r="Q302" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="R302" s="11" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="303" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A303" s="8" t="s">
+        <v>852</v>
+      </c>
+      <c r="B303" s="8" t="s">
+        <v>853</v>
+      </c>
+      <c r="C303" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D303" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E303" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F303" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G303" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H303" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I303" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J303" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K303" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="L303" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M303" s="8">
+        <v>80</v>
+      </c>
+      <c r="N303" s="8"/>
+      <c r="O303" s="8"/>
+      <c r="P303" s="10"/>
+      <c r="Q303" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="R303" s="11" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="304" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A304" s="8" t="s">
+        <v>855</v>
+      </c>
+      <c r="B304" s="8" t="s">
+        <v>856</v>
+      </c>
+      <c r="C304" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D304" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E304" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F304" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G304" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H304" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I304" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J304" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K304" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L304" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M304" s="8">
+        <v>90</v>
+      </c>
+      <c r="N304" s="8"/>
+      <c r="O304" s="8"/>
+      <c r="P304" s="10"/>
+      <c r="Q304" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="R304" s="11" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="305" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A305" s="8" t="s">
+        <v>859</v>
+      </c>
+      <c r="B305" s="8" t="s">
+        <v>860</v>
+      </c>
+      <c r="C305" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D305" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E305" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F305" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G305" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H305" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I305" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="J305" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K305" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="L305" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M305" s="8">
+        <v>70</v>
+      </c>
+      <c r="N305" s="8"/>
+      <c r="O305" s="8"/>
+      <c r="P305" s="10"/>
+      <c r="Q305" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="R305" s="11" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="306" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A306" s="8" t="s">
+        <v>861</v>
+      </c>
+      <c r="B306" s="8" t="s">
+        <v>862</v>
+      </c>
+      <c r="C306" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D306" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E306" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F306" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G306" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H306" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I306" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J306" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="K306" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L306" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M306" s="8">
+        <v>80</v>
+      </c>
+      <c r="N306" s="8"/>
+      <c r="O306" s="8"/>
+      <c r="P306" s="10"/>
+      <c r="Q306" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="R306" s="11" t="s">
+        <v>863</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -16182,7 +17827,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9848E97-FB23-44B1-9CE3-C616F78A0A8B}">
-  <dimension ref="A1:S274"/>
+  <dimension ref="A1:S293"/>
   <sheetFormatPr defaultColWidth="15.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -25061,6 +26706,671 @@
       </c>
       <c r="M274" s="11" t="s">
         <v>781</v>
+      </c>
+    </row>
+    <row r="275" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A275" s="8" t="s">
+        <v>792</v>
+      </c>
+      <c r="B275" s="8" t="s">
+        <v>793</v>
+      </c>
+      <c r="C275" s="9" t="s">
+        <v>794</v>
+      </c>
+      <c r="D275" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E275" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F275" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G275" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="H275" s="8">
+        <v>30</v>
+      </c>
+      <c r="I275" s="8"/>
+      <c r="J275" s="8"/>
+      <c r="K275" s="10"/>
+      <c r="L275" s="9" t="s">
+        <v>795</v>
+      </c>
+      <c r="M275" s="11" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="276" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A276" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="B276" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="C276" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D276" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E276" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="F276" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G276" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H276" s="8">
+        <v>30</v>
+      </c>
+      <c r="I276" s="8"/>
+      <c r="J276" s="8"/>
+      <c r="K276" s="10"/>
+      <c r="L276" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="M276" s="11" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="277" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A277" s="8" t="s">
+        <v>815</v>
+      </c>
+      <c r="B277" s="8" t="s">
+        <v>816</v>
+      </c>
+      <c r="C277" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D277" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="E277" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F277" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="G277" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="H277" s="8">
+        <v>10</v>
+      </c>
+      <c r="I277" s="8"/>
+      <c r="J277" s="8"/>
+      <c r="K277" s="10"/>
+      <c r="L277" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="M277" s="11" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="278" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A278" s="8" t="s">
+        <v>866</v>
+      </c>
+      <c r="B278" s="8" t="s">
+        <v>802</v>
+      </c>
+      <c r="C278" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D278" s="8" t="s">
+        <v>646</v>
+      </c>
+      <c r="E278" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="F278" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G278" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H278" s="8">
+        <v>20</v>
+      </c>
+      <c r="I278" s="8"/>
+      <c r="J278" s="8"/>
+      <c r="K278" s="10"/>
+      <c r="L278" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="M278" s="11" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="279" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A279" s="8" t="s">
+        <v>823</v>
+      </c>
+      <c r="B279" s="8" t="s">
+        <v>824</v>
+      </c>
+      <c r="C279" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D279" s="8" t="s">
+        <v>646</v>
+      </c>
+      <c r="E279" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F279" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G279" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="H279" s="8">
+        <v>20</v>
+      </c>
+      <c r="I279" s="8"/>
+      <c r="J279" s="8"/>
+      <c r="K279" s="10"/>
+      <c r="L279" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="M279" s="11" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="280" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A280" s="8" t="s">
+        <v>829</v>
+      </c>
+      <c r="B280" s="8" t="s">
+        <v>830</v>
+      </c>
+      <c r="C280" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D280" s="8" t="s">
+        <v>646</v>
+      </c>
+      <c r="E280" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F280" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G280" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="H280" s="8">
+        <v>20</v>
+      </c>
+      <c r="I280" s="8"/>
+      <c r="J280" s="8"/>
+      <c r="K280" s="10"/>
+      <c r="L280" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="M280" s="11" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="281" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A281" s="8" t="s">
+        <v>809</v>
+      </c>
+      <c r="B281" s="8" t="s">
+        <v>810</v>
+      </c>
+      <c r="C281" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D281" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E281" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="F281" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G281" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="H281" s="8">
+        <v>20</v>
+      </c>
+      <c r="I281" s="8"/>
+      <c r="J281" s="8"/>
+      <c r="K281" s="10"/>
+      <c r="L281" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="M281" s="11" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="282" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A282" s="8" t="s">
+        <v>820</v>
+      </c>
+      <c r="B282" s="8" t="s">
+        <v>821</v>
+      </c>
+      <c r="C282" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D282" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E282" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F282" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G282" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="H282" s="8">
+        <v>30</v>
+      </c>
+      <c r="I282" s="8"/>
+      <c r="J282" s="8"/>
+      <c r="K282" s="10"/>
+      <c r="L282" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="M282" s="11" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="283" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A283" s="8" t="s">
+        <v>834</v>
+      </c>
+      <c r="B283" s="8" t="s">
+        <v>835</v>
+      </c>
+      <c r="C283" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D283" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E283" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F283" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G283" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="H283" s="8">
+        <v>30</v>
+      </c>
+      <c r="I283" s="8"/>
+      <c r="J283" s="8"/>
+      <c r="K283" s="10"/>
+      <c r="L283" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="M283" s="11" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="284" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A284" s="8" t="s">
+        <v>827</v>
+      </c>
+      <c r="B284" s="8" t="s">
+        <v>828</v>
+      </c>
+      <c r="C284" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D284" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E284" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="F284" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G284" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H284" s="8">
+        <v>30</v>
+      </c>
+      <c r="I284" s="8"/>
+      <c r="J284" s="8"/>
+      <c r="K284" s="10"/>
+      <c r="L284" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="M284" s="11" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="285" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A285" s="8" t="s">
+        <v>818</v>
+      </c>
+      <c r="B285" s="8" t="s">
+        <v>819</v>
+      </c>
+      <c r="C285" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D285" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E285" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F285" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G285" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H285" s="8">
+        <v>40</v>
+      </c>
+      <c r="I285" s="8"/>
+      <c r="J285" s="8"/>
+      <c r="K285" s="10"/>
+      <c r="L285" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="M285" s="11" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="286" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A286" s="8" t="s">
+        <v>812</v>
+      </c>
+      <c r="B286" s="8" t="s">
+        <v>813</v>
+      </c>
+      <c r="C286" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D286" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="E286" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F286" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="G286" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="H286" s="8">
+        <v>10</v>
+      </c>
+      <c r="I286" s="8"/>
+      <c r="J286" s="8"/>
+      <c r="K286" s="10"/>
+      <c r="L286" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="M286" s="11" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="287" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A287" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="B287" s="8" t="s">
+        <v>826</v>
+      </c>
+      <c r="C287" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D287" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E287" s="8" t="s">
+        <v>613</v>
+      </c>
+      <c r="F287" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G287" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H287" s="8">
+        <v>30</v>
+      </c>
+      <c r="I287" s="8"/>
+      <c r="J287" s="8"/>
+      <c r="K287" s="10"/>
+      <c r="L287" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="M287" s="11" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="288" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A288" s="8" t="s">
+        <v>839</v>
+      </c>
+      <c r="B288" s="8" t="s">
+        <v>840</v>
+      </c>
+      <c r="C288" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D288" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E288" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F288" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G288" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H288" s="8">
+        <v>40</v>
+      </c>
+      <c r="I288" s="8"/>
+      <c r="J288" s="8"/>
+      <c r="K288" s="10"/>
+      <c r="L288" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="M288" s="11" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="289" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A289" s="8" t="s">
+        <v>832</v>
+      </c>
+      <c r="B289" s="8" t="s">
+        <v>833</v>
+      </c>
+      <c r="C289" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D289" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="E289" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F289" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G289" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="H289" s="8">
+        <v>20</v>
+      </c>
+      <c r="I289" s="8"/>
+      <c r="J289" s="8"/>
+      <c r="K289" s="10"/>
+      <c r="L289" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="M289" s="11" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="290" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A290" s="8" t="s">
+        <v>871</v>
+      </c>
+      <c r="B290" s="8" t="s">
+        <v>837</v>
+      </c>
+      <c r="C290" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D290" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E290" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F290" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G290" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H290" s="8">
+        <v>40</v>
+      </c>
+      <c r="I290" s="8"/>
+      <c r="J290" s="8"/>
+      <c r="K290" s="10"/>
+      <c r="L290" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="M290" s="11" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="291" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A291" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="B291" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="C291" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D291" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E291" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F291" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="G291" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="H291" s="8">
+        <v>20</v>
+      </c>
+      <c r="I291" s="8"/>
+      <c r="J291" s="8"/>
+      <c r="K291" s="10"/>
+      <c r="L291" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="M291" s="11" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="292" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A292" s="8" t="s">
+        <v>845</v>
+      </c>
+      <c r="B292" s="8" t="s">
+        <v>846</v>
+      </c>
+      <c r="C292" s="9" t="s">
+        <v>795</v>
+      </c>
+      <c r="D292" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E292" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F292" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="G292" s="8" t="s">
+        <v>873</v>
+      </c>
+      <c r="H292" s="8">
+        <v>20</v>
+      </c>
+      <c r="I292" s="8"/>
+      <c r="J292" s="8"/>
+      <c r="K292" s="10"/>
+      <c r="L292" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M292" s="11" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="293" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A293" s="8" t="s">
+        <v>841</v>
+      </c>
+      <c r="B293" s="8" t="s">
+        <v>875</v>
+      </c>
+      <c r="C293" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D293" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E293" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="F293" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="G293" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="H293" s="8">
+        <v>10</v>
+      </c>
+      <c r="I293" s="8"/>
+      <c r="J293" s="8"/>
+      <c r="K293" s="10"/>
+      <c r="L293" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M293" s="11" t="s">
+        <v>874</v>
       </c>
     </row>
   </sheetData>
@@ -25070,7 +27380,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E795EE60-EBCD-4B19-B884-654D5F927670}">
-  <dimension ref="A1:S271"/>
+  <dimension ref="A1:S291"/>
   <sheetFormatPr defaultColWidth="16.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -33850,6 +36160,706 @@
       </c>
       <c r="M271" s="11" t="s">
         <v>785</v>
+      </c>
+    </row>
+    <row r="272" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A272" s="8" t="s">
+        <v>792</v>
+      </c>
+      <c r="B272" s="8" t="s">
+        <v>793</v>
+      </c>
+      <c r="C272" s="9" t="s">
+        <v>794</v>
+      </c>
+      <c r="D272" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E272" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F272" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="G272" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H272" s="8">
+        <v>30</v>
+      </c>
+      <c r="I272" s="8"/>
+      <c r="J272" s="8"/>
+      <c r="K272" s="10"/>
+      <c r="L272" s="9" t="s">
+        <v>795</v>
+      </c>
+      <c r="M272" s="11" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="273" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A273" s="8" t="s">
+        <v>818</v>
+      </c>
+      <c r="B273" s="8" t="s">
+        <v>819</v>
+      </c>
+      <c r="C273" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D273" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E273" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="F273" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G273" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H273" s="8">
+        <v>30</v>
+      </c>
+      <c r="I273" s="8"/>
+      <c r="J273" s="8"/>
+      <c r="K273" s="10"/>
+      <c r="L273" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="M273" s="11" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="274" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A274" s="8" t="s">
+        <v>834</v>
+      </c>
+      <c r="B274" s="8" t="s">
+        <v>835</v>
+      </c>
+      <c r="C274" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D274" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E274" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F274" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G274" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H274" s="8">
+        <v>40</v>
+      </c>
+      <c r="I274" s="8"/>
+      <c r="J274" s="8"/>
+      <c r="K274" s="10"/>
+      <c r="L274" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="M274" s="11" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="275" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A275" s="8" t="s">
+        <v>878</v>
+      </c>
+      <c r="B275" s="8" t="s">
+        <v>813</v>
+      </c>
+      <c r="C275" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D275" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E275" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F275" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="G275" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H275" s="8">
+        <v>30</v>
+      </c>
+      <c r="I275" s="8"/>
+      <c r="J275" s="8"/>
+      <c r="K275" s="10"/>
+      <c r="L275" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="M275" s="11" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="276" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A276" s="8" t="s">
+        <v>866</v>
+      </c>
+      <c r="B276" s="8" t="s">
+        <v>879</v>
+      </c>
+      <c r="C276" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D276" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E276" s="8" t="s">
+        <v>880</v>
+      </c>
+      <c r="F276" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G276" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H276" s="8">
+        <v>30</v>
+      </c>
+      <c r="I276" s="8"/>
+      <c r="J276" s="8"/>
+      <c r="K276" s="10"/>
+      <c r="L276" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="M276" s="11" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="277" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A277" s="8" t="s">
+        <v>820</v>
+      </c>
+      <c r="B277" s="8" t="s">
+        <v>821</v>
+      </c>
+      <c r="C277" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D277" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E277" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F277" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G277" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="H277" s="8">
+        <v>30</v>
+      </c>
+      <c r="I277" s="8"/>
+      <c r="J277" s="8"/>
+      <c r="K277" s="10"/>
+      <c r="L277" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="M277" s="11" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="278" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A278" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="B278" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="C278" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D278" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E278" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F278" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G278" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H278" s="8">
+        <v>40</v>
+      </c>
+      <c r="I278" s="8"/>
+      <c r="J278" s="8"/>
+      <c r="K278" s="10"/>
+      <c r="L278" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="M278" s="11" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="279" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A279" s="8" t="s">
+        <v>809</v>
+      </c>
+      <c r="B279" s="8" t="s">
+        <v>810</v>
+      </c>
+      <c r="C279" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D279" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E279" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F279" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G279" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H279" s="8">
+        <v>40</v>
+      </c>
+      <c r="I279" s="8"/>
+      <c r="J279" s="8"/>
+      <c r="K279" s="10"/>
+      <c r="L279" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="M279" s="11" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="280" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A280" s="8" t="s">
+        <v>815</v>
+      </c>
+      <c r="B280" s="8" t="s">
+        <v>816</v>
+      </c>
+      <c r="C280" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D280" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E280" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="F280" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G280" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H280" s="8">
+        <v>30</v>
+      </c>
+      <c r="I280" s="8"/>
+      <c r="J280" s="8"/>
+      <c r="K280" s="10"/>
+      <c r="L280" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="M280" s="11" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="281" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A281" s="8" t="s">
+        <v>829</v>
+      </c>
+      <c r="B281" s="8" t="s">
+        <v>830</v>
+      </c>
+      <c r="C281" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D281" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E281" s="8" t="s">
+        <v>880</v>
+      </c>
+      <c r="F281" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G281" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H281" s="8">
+        <v>30</v>
+      </c>
+      <c r="I281" s="8"/>
+      <c r="J281" s="8"/>
+      <c r="K281" s="10"/>
+      <c r="L281" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="M281" s="11" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="282" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A282" s="8" t="s">
+        <v>823</v>
+      </c>
+      <c r="B282" s="8" t="s">
+        <v>824</v>
+      </c>
+      <c r="C282" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D282" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E282" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F282" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G282" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H282" s="8">
+        <v>40</v>
+      </c>
+      <c r="I282" s="8"/>
+      <c r="J282" s="8"/>
+      <c r="K282" s="10"/>
+      <c r="L282" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="M282" s="11" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="283" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A283" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="B283" s="8" t="s">
+        <v>826</v>
+      </c>
+      <c r="C283" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D283" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E283" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="F283" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G283" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H283" s="8">
+        <v>30</v>
+      </c>
+      <c r="I283" s="8"/>
+      <c r="J283" s="8"/>
+      <c r="K283" s="10"/>
+      <c r="L283" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="M283" s="11" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="284" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A284" s="8" t="s">
+        <v>827</v>
+      </c>
+      <c r="B284" s="8" t="s">
+        <v>828</v>
+      </c>
+      <c r="C284" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D284" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E284" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F284" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G284" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H284" s="8">
+        <v>40</v>
+      </c>
+      <c r="I284" s="8"/>
+      <c r="J284" s="8"/>
+      <c r="K284" s="10"/>
+      <c r="L284" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="M284" s="11" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="285" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A285" s="8" t="s">
+        <v>797</v>
+      </c>
+      <c r="B285" s="8" t="s">
+        <v>798</v>
+      </c>
+      <c r="C285" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D285" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E285" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="F285" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G285" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H285" s="8">
+        <v>30</v>
+      </c>
+      <c r="I285" s="8"/>
+      <c r="J285" s="8"/>
+      <c r="K285" s="10"/>
+      <c r="L285" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="M285" s="11" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="286" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A286" s="8" t="s">
+        <v>839</v>
+      </c>
+      <c r="B286" s="8" t="s">
+        <v>840</v>
+      </c>
+      <c r="C286" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D286" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E286" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F286" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G286" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H286" s="8">
+        <v>40</v>
+      </c>
+      <c r="I286" s="8"/>
+      <c r="J286" s="8"/>
+      <c r="K286" s="10"/>
+      <c r="L286" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="M286" s="11" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="287" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A287" s="8" t="s">
+        <v>832</v>
+      </c>
+      <c r="B287" s="8" t="s">
+        <v>833</v>
+      </c>
+      <c r="C287" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D287" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E287" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F287" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G287" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H287" s="8">
+        <v>40</v>
+      </c>
+      <c r="I287" s="8"/>
+      <c r="J287" s="8"/>
+      <c r="K287" s="10"/>
+      <c r="L287" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="M287" s="11" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="288" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A288" s="8" t="s">
+        <v>871</v>
+      </c>
+      <c r="B288" s="8" t="s">
+        <v>837</v>
+      </c>
+      <c r="C288" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D288" s="8" t="s">
+        <v>885</v>
+      </c>
+      <c r="E288" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F288" s="8" t="s">
+        <v>652</v>
+      </c>
+      <c r="G288" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H288" s="8">
+        <v>20</v>
+      </c>
+      <c r="I288" s="8"/>
+      <c r="J288" s="8"/>
+      <c r="K288" s="10"/>
+      <c r="L288" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="M288" s="11" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="289" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A289" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="B289" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="C289" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D289" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E289" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F289" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G289" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H289" s="8">
+        <v>40</v>
+      </c>
+      <c r="I289" s="8"/>
+      <c r="J289" s="8"/>
+      <c r="K289" s="10"/>
+      <c r="L289" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="M289" s="11" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="290" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A290" s="8" t="s">
+        <v>841</v>
+      </c>
+      <c r="B290" s="8" t="s">
+        <v>875</v>
+      </c>
+      <c r="C290" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D290" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E290" s="8" t="s">
+        <v>880</v>
+      </c>
+      <c r="F290" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G290" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H290" s="8">
+        <v>30</v>
+      </c>
+      <c r="I290" s="8"/>
+      <c r="J290" s="8"/>
+      <c r="K290" s="10"/>
+      <c r="L290" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M290" s="11" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="291" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A291" s="8" t="s">
+        <v>845</v>
+      </c>
+      <c r="B291" s="8" t="s">
+        <v>846</v>
+      </c>
+      <c r="C291" s="9" t="s">
+        <v>795</v>
+      </c>
+      <c r="D291" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E291" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="F291" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G291" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H291" s="8">
+        <v>30</v>
+      </c>
+      <c r="I291" s="8"/>
+      <c r="J291" s="8"/>
+      <c r="K291" s="10"/>
+      <c r="L291" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M291" s="11" t="s">
+        <v>886</v>
       </c>
     </row>
   </sheetData>
@@ -33859,7 +36869,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41BB7886-C4B6-45DF-87F2-53652B8B0BB3}">
-  <dimension ref="A1:S269"/>
+  <dimension ref="A1:S289"/>
   <sheetFormatPr defaultColWidth="12.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -42578,6 +45588,706 @@
       </c>
       <c r="M269" s="11" t="s">
         <v>687</v>
+      </c>
+    </row>
+    <row r="270" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A270" s="8" t="s">
+        <v>792</v>
+      </c>
+      <c r="B270" s="8" t="s">
+        <v>793</v>
+      </c>
+      <c r="C270" s="9" t="s">
+        <v>794</v>
+      </c>
+      <c r="D270" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E270" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F270" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G270" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H270" s="8">
+        <v>40</v>
+      </c>
+      <c r="I270" s="8"/>
+      <c r="J270" s="8"/>
+      <c r="K270" s="10"/>
+      <c r="L270" s="9" t="s">
+        <v>795</v>
+      </c>
+      <c r="M270" s="11" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="271" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A271" s="8" t="s">
+        <v>812</v>
+      </c>
+      <c r="B271" s="8" t="s">
+        <v>813</v>
+      </c>
+      <c r="C271" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D271" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E271" s="8" t="s">
+        <v>520</v>
+      </c>
+      <c r="F271" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G271" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H271" s="8">
+        <v>30</v>
+      </c>
+      <c r="I271" s="8"/>
+      <c r="J271" s="8"/>
+      <c r="K271" s="10"/>
+      <c r="L271" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M271" s="11" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="272" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A272" s="8" t="s">
+        <v>812</v>
+      </c>
+      <c r="B272" s="8" t="s">
+        <v>813</v>
+      </c>
+      <c r="C272" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D272" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E272" s="8" t="s">
+        <v>520</v>
+      </c>
+      <c r="F272" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G272" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H272" s="8">
+        <v>30</v>
+      </c>
+      <c r="I272" s="8"/>
+      <c r="J272" s="8"/>
+      <c r="K272" s="10"/>
+      <c r="L272" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M272" s="11" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="273" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A273" s="8" t="s">
+        <v>812</v>
+      </c>
+      <c r="B273" s="8" t="s">
+        <v>813</v>
+      </c>
+      <c r="C273" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D273" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E273" s="8" t="s">
+        <v>520</v>
+      </c>
+      <c r="F273" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G273" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H273" s="8">
+        <v>30</v>
+      </c>
+      <c r="I273" s="8"/>
+      <c r="J273" s="8"/>
+      <c r="K273" s="10"/>
+      <c r="L273" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M273" s="11" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="274" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A274" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="B274" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="C274" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D274" s="8" t="s">
+        <v>519</v>
+      </c>
+      <c r="E274" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F274" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G274" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H274" s="8">
+        <v>30</v>
+      </c>
+      <c r="I274" s="8"/>
+      <c r="J274" s="8"/>
+      <c r="K274" s="10"/>
+      <c r="L274" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M274" s="11" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="275" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A275" s="8" t="s">
+        <v>809</v>
+      </c>
+      <c r="B275" s="8" t="s">
+        <v>810</v>
+      </c>
+      <c r="C275" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D275" s="8" t="s">
+        <v>519</v>
+      </c>
+      <c r="E275" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F275" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G275" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H275" s="8">
+        <v>30</v>
+      </c>
+      <c r="I275" s="8"/>
+      <c r="J275" s="8"/>
+      <c r="K275" s="10"/>
+      <c r="L275" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M275" s="11" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="276" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A276" s="8" t="s">
+        <v>834</v>
+      </c>
+      <c r="B276" s="8" t="s">
+        <v>835</v>
+      </c>
+      <c r="C276" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D276" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E276" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F276" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G276" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H276" s="8">
+        <v>40</v>
+      </c>
+      <c r="I276" s="8"/>
+      <c r="J276" s="8"/>
+      <c r="K276" s="10"/>
+      <c r="L276" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M276" s="11" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="277" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A277" s="8" t="s">
+        <v>820</v>
+      </c>
+      <c r="B277" s="8" t="s">
+        <v>821</v>
+      </c>
+      <c r="C277" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D277" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E277" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F277" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G277" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H277" s="8">
+        <v>40</v>
+      </c>
+      <c r="I277" s="8"/>
+      <c r="J277" s="8"/>
+      <c r="K277" s="10"/>
+      <c r="L277" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M277" s="11" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="278" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A278" s="8" t="s">
+        <v>866</v>
+      </c>
+      <c r="B278" s="8" t="s">
+        <v>879</v>
+      </c>
+      <c r="C278" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D278" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E278" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="F278" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G278" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H278" s="8">
+        <v>30</v>
+      </c>
+      <c r="I278" s="8"/>
+      <c r="J278" s="8"/>
+      <c r="K278" s="10"/>
+      <c r="L278" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M278" s="11" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="279" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A279" s="8" t="s">
+        <v>815</v>
+      </c>
+      <c r="B279" s="8" t="s">
+        <v>816</v>
+      </c>
+      <c r="C279" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D279" s="8" t="s">
+        <v>519</v>
+      </c>
+      <c r="E279" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F279" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G279" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H279" s="8">
+        <v>30</v>
+      </c>
+      <c r="I279" s="8"/>
+      <c r="J279" s="8"/>
+      <c r="K279" s="10"/>
+      <c r="L279" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M279" s="11" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="280" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A280" s="8" t="s">
+        <v>818</v>
+      </c>
+      <c r="B280" s="8" t="s">
+        <v>819</v>
+      </c>
+      <c r="C280" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D280" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="E280" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F280" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G280" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H280" s="8">
+        <v>30</v>
+      </c>
+      <c r="I280" s="8"/>
+      <c r="J280" s="8"/>
+      <c r="K280" s="10"/>
+      <c r="L280" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M280" s="11" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="281" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A281" s="8" t="s">
+        <v>827</v>
+      </c>
+      <c r="B281" s="8" t="s">
+        <v>828</v>
+      </c>
+      <c r="C281" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D281" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E281" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F281" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G281" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H281" s="8">
+        <v>40</v>
+      </c>
+      <c r="I281" s="8"/>
+      <c r="J281" s="8"/>
+      <c r="K281" s="10"/>
+      <c r="L281" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M281" s="11" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="282" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A282" s="8" t="s">
+        <v>797</v>
+      </c>
+      <c r="B282" s="8" t="s">
+        <v>798</v>
+      </c>
+      <c r="C282" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="D282" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E282" s="8" t="s">
+        <v>520</v>
+      </c>
+      <c r="F282" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G282" s="8" t="s">
+        <v>523</v>
+      </c>
+      <c r="H282" s="8">
+        <v>20</v>
+      </c>
+      <c r="I282" s="8"/>
+      <c r="J282" s="8"/>
+      <c r="K282" s="10"/>
+      <c r="L282" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M282" s="11" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="283" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A283" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="B283" s="8" t="s">
+        <v>826</v>
+      </c>
+      <c r="C283" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D283" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E283" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F283" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G283" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H283" s="8">
+        <v>40</v>
+      </c>
+      <c r="I283" s="8"/>
+      <c r="J283" s="8"/>
+      <c r="K283" s="10"/>
+      <c r="L283" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M283" s="11" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="284" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A284" s="8" t="s">
+        <v>823</v>
+      </c>
+      <c r="B284" s="8" t="s">
+        <v>824</v>
+      </c>
+      <c r="C284" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D284" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E284" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F284" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G284" s="8" t="s">
+        <v>661</v>
+      </c>
+      <c r="H284" s="8">
+        <v>30</v>
+      </c>
+      <c r="I284" s="8"/>
+      <c r="J284" s="8"/>
+      <c r="K284" s="10"/>
+      <c r="L284" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M284" s="11" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="285" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A285" s="8" t="s">
+        <v>829</v>
+      </c>
+      <c r="B285" s="8" t="s">
+        <v>830</v>
+      </c>
+      <c r="C285" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D285" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E285" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F285" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G285" s="8" t="s">
+        <v>661</v>
+      </c>
+      <c r="H285" s="8">
+        <v>30</v>
+      </c>
+      <c r="I285" s="8"/>
+      <c r="J285" s="8"/>
+      <c r="K285" s="10"/>
+      <c r="L285" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M285" s="11" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="286" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A286" s="8" t="s">
+        <v>839</v>
+      </c>
+      <c r="B286" s="8" t="s">
+        <v>840</v>
+      </c>
+      <c r="C286" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D286" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="E286" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="F286" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G286" s="8" t="s">
+        <v>661</v>
+      </c>
+      <c r="H286" s="8">
+        <v>10</v>
+      </c>
+      <c r="I286" s="8"/>
+      <c r="J286" s="8"/>
+      <c r="K286" s="10"/>
+      <c r="L286" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M286" s="11" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="287" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A287" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="B287" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="C287" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D287" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E287" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F287" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G287" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H287" s="8">
+        <v>40</v>
+      </c>
+      <c r="I287" s="8"/>
+      <c r="J287" s="8"/>
+      <c r="K287" s="10"/>
+      <c r="L287" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M287" s="11" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="288" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A288" s="8" t="s">
+        <v>832</v>
+      </c>
+      <c r="B288" s="8" t="s">
+        <v>833</v>
+      </c>
+      <c r="C288" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D288" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E288" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F288" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G288" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H288" s="8">
+        <v>40</v>
+      </c>
+      <c r="I288" s="8"/>
+      <c r="J288" s="8"/>
+      <c r="K288" s="10"/>
+      <c r="L288" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M288" s="11" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="289" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A289" s="8" t="s">
+        <v>836</v>
+      </c>
+      <c r="B289" s="8" t="s">
+        <v>837</v>
+      </c>
+      <c r="C289" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D289" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E289" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F289" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G289" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H289" s="8">
+        <v>40</v>
+      </c>
+      <c r="I289" s="8"/>
+      <c r="J289" s="8"/>
+      <c r="K289" s="10"/>
+      <c r="L289" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M289" s="11" t="s">
+        <v>897</v>
       </c>
     </row>
   </sheetData>
@@ -42587,7 +46297,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{083B2BF1-723B-4775-8297-318920D3FD0C}">
-  <dimension ref="A1:S268"/>
+  <dimension ref="A1:S286"/>
   <sheetFormatPr defaultColWidth="13.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -51273,6 +54983,636 @@
         <v>791</v>
       </c>
     </row>
+    <row r="269" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A269" s="8" t="s">
+        <v>792</v>
+      </c>
+      <c r="B269" s="8" t="s">
+        <v>793</v>
+      </c>
+      <c r="C269" s="9" t="s">
+        <v>794</v>
+      </c>
+      <c r="D269" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E269" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F269" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="G269" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H269" s="8">
+        <v>40</v>
+      </c>
+      <c r="I269" s="8"/>
+      <c r="J269" s="8"/>
+      <c r="K269" s="10"/>
+      <c r="L269" s="9" t="s">
+        <v>795</v>
+      </c>
+      <c r="M269" s="11" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="270" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A270" s="8" t="s">
+        <v>812</v>
+      </c>
+      <c r="B270" s="8" t="s">
+        <v>813</v>
+      </c>
+      <c r="C270" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D270" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E270" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F270" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="G270" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H270" s="8">
+        <v>40</v>
+      </c>
+      <c r="I270" s="8"/>
+      <c r="J270" s="8"/>
+      <c r="K270" s="10"/>
+      <c r="L270" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M270" s="11" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="271" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A271" s="8" t="s">
+        <v>815</v>
+      </c>
+      <c r="B271" s="8" t="s">
+        <v>816</v>
+      </c>
+      <c r="C271" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D271" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="E271" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F271" s="8" t="s">
+        <v>552</v>
+      </c>
+      <c r="G271" s="8" t="s">
+        <v>899</v>
+      </c>
+      <c r="H271" s="8">
+        <v>10</v>
+      </c>
+      <c r="I271" s="8"/>
+      <c r="J271" s="8"/>
+      <c r="K271" s="10"/>
+      <c r="L271" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M271" s="11" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="272" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A272" s="8" t="s">
+        <v>820</v>
+      </c>
+      <c r="B272" s="8" t="s">
+        <v>821</v>
+      </c>
+      <c r="C272" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D272" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E272" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F272" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="G272" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="H272" s="8">
+        <v>20</v>
+      </c>
+      <c r="I272" s="8"/>
+      <c r="J272" s="8"/>
+      <c r="K272" s="10"/>
+      <c r="L272" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M272" s="11" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="273" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A273" s="8" t="s">
+        <v>823</v>
+      </c>
+      <c r="B273" s="8" t="s">
+        <v>824</v>
+      </c>
+      <c r="C273" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D273" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="E273" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F273" s="8" t="s">
+        <v>552</v>
+      </c>
+      <c r="G273" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H273" s="8">
+        <v>20</v>
+      </c>
+      <c r="I273" s="8"/>
+      <c r="J273" s="8"/>
+      <c r="K273" s="10"/>
+      <c r="L273" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M273" s="11" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="274" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A274" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="B274" s="8" t="s">
+        <v>826</v>
+      </c>
+      <c r="C274" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D274" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E274" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F274" s="8" t="s">
+        <v>552</v>
+      </c>
+      <c r="G274" s="8" t="s">
+        <v>902</v>
+      </c>
+      <c r="H274" s="8">
+        <v>20</v>
+      </c>
+      <c r="I274" s="8"/>
+      <c r="J274" s="8"/>
+      <c r="K274" s="10"/>
+      <c r="L274" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M274" s="11" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="275" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A275" s="8" t="s">
+        <v>866</v>
+      </c>
+      <c r="B275" s="8" t="s">
+        <v>879</v>
+      </c>
+      <c r="C275" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D275" s="8" t="s">
+        <v>546</v>
+      </c>
+      <c r="E275" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F275" s="8" t="s">
+        <v>552</v>
+      </c>
+      <c r="G275" s="8" t="s">
+        <v>557</v>
+      </c>
+      <c r="H275" s="8">
+        <v>10</v>
+      </c>
+      <c r="I275" s="8"/>
+      <c r="J275" s="8"/>
+      <c r="K275" s="10"/>
+      <c r="L275" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M275" s="11" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="276" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A276" s="8" t="s">
+        <v>818</v>
+      </c>
+      <c r="B276" s="8" t="s">
+        <v>819</v>
+      </c>
+      <c r="C276" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D276" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="E276" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F276" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="G276" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H276" s="8">
+        <v>30</v>
+      </c>
+      <c r="I276" s="8"/>
+      <c r="J276" s="8"/>
+      <c r="K276" s="10"/>
+      <c r="L276" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M276" s="11" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="277" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A277" s="8" t="s">
+        <v>834</v>
+      </c>
+      <c r="B277" s="8" t="s">
+        <v>835</v>
+      </c>
+      <c r="C277" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D277" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E277" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F277" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="G277" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H277" s="8">
+        <v>40</v>
+      </c>
+      <c r="I277" s="8"/>
+      <c r="J277" s="8"/>
+      <c r="K277" s="10"/>
+      <c r="L277" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M277" s="11" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="278" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A278" s="8" t="s">
+        <v>797</v>
+      </c>
+      <c r="B278" s="8" t="s">
+        <v>798</v>
+      </c>
+      <c r="C278" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D278" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="E278" s="8" t="s">
+        <v>903</v>
+      </c>
+      <c r="F278" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="G278" s="8" t="s">
+        <v>899</v>
+      </c>
+      <c r="H278" s="8">
+        <v>10</v>
+      </c>
+      <c r="I278" s="8"/>
+      <c r="J278" s="8"/>
+      <c r="K278" s="10"/>
+      <c r="L278" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M278" s="11" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="279" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A279" s="8" t="s">
+        <v>809</v>
+      </c>
+      <c r="B279" s="8" t="s">
+        <v>810</v>
+      </c>
+      <c r="C279" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D279" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E279" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F279" s="8" t="s">
+        <v>904</v>
+      </c>
+      <c r="G279" s="8" t="s">
+        <v>902</v>
+      </c>
+      <c r="H279" s="8">
+        <v>20</v>
+      </c>
+      <c r="I279" s="8"/>
+      <c r="J279" s="8"/>
+      <c r="K279" s="10"/>
+      <c r="L279" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M279" s="11" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="280" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A280" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="B280" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="C280" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D280" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E280" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F280" s="8" t="s">
+        <v>904</v>
+      </c>
+      <c r="G280" s="8" t="s">
+        <v>902</v>
+      </c>
+      <c r="H280" s="8">
+        <v>20</v>
+      </c>
+      <c r="I280" s="8"/>
+      <c r="J280" s="8"/>
+      <c r="K280" s="10"/>
+      <c r="L280" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M280" s="11" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="281" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A281" s="8" t="s">
+        <v>829</v>
+      </c>
+      <c r="B281" s="8" t="s">
+        <v>830</v>
+      </c>
+      <c r="C281" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D281" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="E281" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F281" s="8" t="s">
+        <v>552</v>
+      </c>
+      <c r="G281" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H281" s="8">
+        <v>20</v>
+      </c>
+      <c r="I281" s="8"/>
+      <c r="J281" s="8"/>
+      <c r="K281" s="10"/>
+      <c r="L281" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M281" s="11" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="282" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A282" s="8" t="s">
+        <v>827</v>
+      </c>
+      <c r="B282" s="8" t="s">
+        <v>828</v>
+      </c>
+      <c r="C282" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D282" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E282" s="8" t="s">
+        <v>903</v>
+      </c>
+      <c r="F282" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="G282" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H282" s="8">
+        <v>20</v>
+      </c>
+      <c r="I282" s="8"/>
+      <c r="J282" s="8"/>
+      <c r="K282" s="10"/>
+      <c r="L282" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M282" s="11" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="283" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A283" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="B283" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="C283" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D283" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E283" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F283" s="8" t="s">
+        <v>904</v>
+      </c>
+      <c r="G283" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H283" s="8">
+        <v>30</v>
+      </c>
+      <c r="I283" s="8"/>
+      <c r="J283" s="8"/>
+      <c r="K283" s="10"/>
+      <c r="L283" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M283" s="11" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="284" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A284" s="8" t="s">
+        <v>839</v>
+      </c>
+      <c r="B284" s="8" t="s">
+        <v>840</v>
+      </c>
+      <c r="C284" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D284" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E284" s="8" t="s">
+        <v>903</v>
+      </c>
+      <c r="F284" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="G284" s="8" t="s">
+        <v>899</v>
+      </c>
+      <c r="H284" s="8">
+        <v>10</v>
+      </c>
+      <c r="I284" s="8"/>
+      <c r="J284" s="8"/>
+      <c r="K284" s="10"/>
+      <c r="L284" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M284" s="11" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="285" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A285" s="8" t="s">
+        <v>832</v>
+      </c>
+      <c r="B285" s="8" t="s">
+        <v>833</v>
+      </c>
+      <c r="C285" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D285" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E285" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F285" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="G285" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H285" s="8">
+        <v>40</v>
+      </c>
+      <c r="I285" s="8"/>
+      <c r="J285" s="8"/>
+      <c r="K285" s="10"/>
+      <c r="L285" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M285" s="11" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="286" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A286" s="8" t="s">
+        <v>871</v>
+      </c>
+      <c r="B286" s="8" t="s">
+        <v>837</v>
+      </c>
+      <c r="C286" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D286" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E286" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F286" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="G286" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="H286" s="8">
+        <v>30</v>
+      </c>
+      <c r="I286" s="8"/>
+      <c r="J286" s="8"/>
+      <c r="K286" s="10"/>
+      <c r="L286" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="M286" s="11" t="s">
+        <v>906</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/data/Integracao Armazem.xlsx
+++ b/data/Integracao Armazem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D096CEA-766F-49DE-8BB9-BFEFCBB1D962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F69664E1-19CC-418B-80D3-ABE9FD2F667C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{422D47E6-8DC3-4B25-BD50-E675C15B05CB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="4" xr2:uid="{422D47E6-8DC3-4B25-BD50-E675C15B05CB}"/>
   </bookViews>
   <sheets>
     <sheet name="M1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10193" uniqueCount="907">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11018" uniqueCount="1000">
   <si>
     <t>Selecione o EPI que NÃO é obrigatório durante o processo de montagem de paletes</t>
   </si>
@@ -2880,6 +2880,285 @@
   </si>
   <si>
     <t>14:24</t>
+  </si>
+  <si>
+    <t>Rubens sergio Candido filho</t>
+  </si>
+  <si>
+    <t>42318547858</t>
+  </si>
+  <si>
+    <t>Ricardo Marcelino da Silva</t>
+  </si>
+  <si>
+    <t>33111474801</t>
+  </si>
+  <si>
+    <t>17:25</t>
+  </si>
+  <si>
+    <t>rodnei Conceição Franco rosário</t>
+  </si>
+  <si>
+    <t>403.502.778-26</t>
+  </si>
+  <si>
+    <t>17:24</t>
+  </si>
+  <si>
+    <t>Gabriel martins mariano</t>
+  </si>
+  <si>
+    <t>53176268890</t>
+  </si>
+  <si>
+    <t>Rodrigo dos Santos Silva</t>
+  </si>
+  <si>
+    <t>281.610.538-55</t>
+  </si>
+  <si>
+    <t>Samuel Rodrigues De Aquino</t>
+  </si>
+  <si>
+    <t>57628148814</t>
+  </si>
+  <si>
+    <t>ELTON SILVA DE JESUS</t>
+  </si>
+  <si>
+    <t>06631492580</t>
+  </si>
+  <si>
+    <t>30/05/2026</t>
+  </si>
+  <si>
+    <t>21:23</t>
+  </si>
+  <si>
+    <t>DAVID WENDSON NASCIMENTO DE ALBUQUERQUE</t>
+  </si>
+  <si>
+    <t>05662763569</t>
+  </si>
+  <si>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>William Oliveira dos Santos</t>
+  </si>
+  <si>
+    <t>097.848.235-27</t>
+  </si>
+  <si>
+    <t>Data inválida</t>
+  </si>
+  <si>
+    <t>MONICA DE JESUS BEZERRA</t>
+  </si>
+  <si>
+    <t>03961******</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>01/06/2026</t>
+  </si>
+  <si>
+    <t>Irlan Barreto Lopes ramos</t>
+  </si>
+  <si>
+    <t>14:46</t>
+  </si>
+  <si>
+    <t>Kauã Gomes de Souza</t>
+  </si>
+  <si>
+    <t>57723453892</t>
+  </si>
+  <si>
+    <t>02/06/2026</t>
+  </si>
+  <si>
+    <t>11:44</t>
+  </si>
+  <si>
+    <t>Claret junior Ochoa reina</t>
+  </si>
+  <si>
+    <t>70812337247</t>
+  </si>
+  <si>
+    <t>11:11</t>
+  </si>
+  <si>
+    <t>Rodrigo Mendes da Silva</t>
+  </si>
+  <si>
+    <t>22:50</t>
+  </si>
+  <si>
+    <t>Sedemar Vargas</t>
+  </si>
+  <si>
+    <t>22:43</t>
+  </si>
+  <si>
+    <t>RODNEI CONCEICAO FRANCO ROSARIO</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>Samuel Rodrigues</t>
+  </si>
+  <si>
+    <t>57628148824</t>
+  </si>
+  <si>
+    <t>GABRIEL MARTINS MARIANO</t>
+  </si>
+  <si>
+    <t>16:23</t>
+  </si>
+  <si>
+    <t>DAVID SIDRONE COSTA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>04280352569</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>21:28</t>
+  </si>
+  <si>
+    <t>14:54</t>
+  </si>
+  <si>
+    <t>Não é necessário pensar no layout do Picking pois não afeta a rotina da separação</t>
+  </si>
+  <si>
+    <t>12:11</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>Rodrigo Mendes Da Silva</t>
+  </si>
+  <si>
+    <t>23:16</t>
+  </si>
+  <si>
+    <t>23:07</t>
+  </si>
+  <si>
+    <t>17:31</t>
+  </si>
+  <si>
+    <t>Samuel Rodrigues Aquino</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>Wendel Costa Santo</t>
+  </si>
+  <si>
+    <t>David Wendson Nascimento de Albuquerque</t>
+  </si>
+  <si>
+    <t>21:24</t>
+  </si>
+  <si>
+    <t>17:14</t>
+  </si>
+  <si>
+    <t>WILLAMS FERREIRA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>04954275512</t>
+  </si>
+  <si>
+    <t>17:11</t>
+  </si>
+  <si>
+    <t>8663848552”</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>14:57</t>
+  </si>
+  <si>
+    <t>12:21</t>
+  </si>
+  <si>
+    <t>Os produtos não precisam respeitar as regras de separação por lastro</t>
+  </si>
+  <si>
+    <t>23:37</t>
+  </si>
+  <si>
+    <t>23:30</t>
+  </si>
+  <si>
+    <t>Rodnei Conceição Franco rosário</t>
+  </si>
+  <si>
+    <t>16:59</t>
+  </si>
+  <si>
+    <t>21:31</t>
+  </si>
+  <si>
+    <t>17:13</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>Irlan Barreto Lopes Ramoa</t>
+  </si>
+  <si>
+    <t>15:04</t>
+  </si>
+  <si>
+    <t>12:41</t>
+  </si>
+  <si>
+    <t>17:19</t>
+  </si>
+  <si>
+    <t>17:18</t>
+  </si>
+  <si>
+    <t>31/05/2026</t>
+  </si>
+  <si>
+    <t>22:38</t>
+  </si>
+  <si>
+    <t>22:37</t>
+  </si>
+  <si>
+    <t>21:35</t>
+  </si>
+  <si>
+    <t>17:12</t>
+  </si>
+  <si>
+    <t>17:08</t>
+  </si>
+  <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>12:51</t>
   </si>
 </sst>
 </file>
@@ -3269,7 +3548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D8EC4C0-DEF5-4A13-83D8-46C06041A7DF}">
-  <dimension ref="A1:S306"/>
+  <dimension ref="A1:S319"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="19" width="14.109375" customWidth="1"/>
@@ -17671,13 +17950,13 @@
     </row>
     <row r="304" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A304" s="8" t="s">
-        <v>855</v>
+        <v>907</v>
       </c>
       <c r="B304" s="8" t="s">
-        <v>856</v>
+        <v>908</v>
       </c>
       <c r="C304" s="9" t="s">
-        <v>857</v>
+        <v>850</v>
       </c>
       <c r="D304" s="8" t="s">
         <v>17</v>
@@ -17716,18 +17995,18 @@
         <v>857</v>
       </c>
       <c r="R304" s="11" t="s">
-        <v>858</v>
+        <v>733</v>
       </c>
     </row>
     <row r="305" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A305" s="8" t="s">
-        <v>859</v>
+        <v>909</v>
       </c>
       <c r="B305" s="8" t="s">
-        <v>860</v>
+        <v>910</v>
       </c>
       <c r="C305" s="9" t="s">
-        <v>857</v>
+        <v>850</v>
       </c>
       <c r="D305" s="8" t="s">
         <v>17</v>
@@ -17736,28 +18015,28 @@
         <v>18</v>
       </c>
       <c r="F305" s="8" t="s">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="G305" s="8" t="s">
         <v>356</v>
       </c>
       <c r="H305" s="8" t="s">
-        <v>357</v>
+        <v>633</v>
       </c>
       <c r="I305" s="8" t="s">
-        <v>382</v>
+        <v>358</v>
       </c>
       <c r="J305" s="8" t="s">
-        <v>359</v>
+        <v>569</v>
       </c>
       <c r="K305" s="8" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="L305" s="8" t="s">
         <v>366</v>
       </c>
       <c r="M305" s="8">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="N305" s="8"/>
       <c r="O305" s="8"/>
@@ -17766,18 +18045,18 @@
         <v>857</v>
       </c>
       <c r="R305" s="11" t="s">
-        <v>858</v>
+        <v>911</v>
       </c>
     </row>
     <row r="306" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A306" s="8" t="s">
-        <v>861</v>
+        <v>912</v>
       </c>
       <c r="B306" s="8" t="s">
-        <v>862</v>
+        <v>913</v>
       </c>
       <c r="C306" s="9" t="s">
-        <v>857</v>
+        <v>850</v>
       </c>
       <c r="D306" s="8" t="s">
         <v>17</v>
@@ -17798,7 +18077,7 @@
         <v>358</v>
       </c>
       <c r="J306" s="8" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="K306" s="8" t="s">
         <v>360</v>
@@ -17807,7 +18086,7 @@
         <v>366</v>
       </c>
       <c r="M306" s="8">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N306" s="8"/>
       <c r="O306" s="8"/>
@@ -17816,7 +18095,661 @@
         <v>857</v>
       </c>
       <c r="R306" s="11" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="307" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A307" s="8" t="s">
+        <v>915</v>
+      </c>
+      <c r="B307" s="8" t="s">
+        <v>916</v>
+      </c>
+      <c r="C307" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="D307" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E307" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F307" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G307" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H307" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I307" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J307" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K307" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L307" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M307" s="8">
+        <v>90</v>
+      </c>
+      <c r="N307" s="8"/>
+      <c r="O307" s="8"/>
+      <c r="P307" s="10"/>
+      <c r="Q307" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="R307" s="11" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="308" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A308" s="8" t="s">
+        <v>917</v>
+      </c>
+      <c r="B308" s="8" t="s">
+        <v>918</v>
+      </c>
+      <c r="C308" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="D308" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E308" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F308" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G308" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H308" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I308" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J308" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K308" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L308" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M308" s="8">
+        <v>90</v>
+      </c>
+      <c r="N308" s="8"/>
+      <c r="O308" s="8"/>
+      <c r="P308" s="10"/>
+      <c r="Q308" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="R308" s="11" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="309" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A309" s="8" t="s">
+        <v>919</v>
+      </c>
+      <c r="B309" s="8" t="s">
+        <v>920</v>
+      </c>
+      <c r="C309" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="D309" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E309" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F309" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G309" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H309" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I309" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J309" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K309" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L309" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M309" s="8">
+        <v>90</v>
+      </c>
+      <c r="N309" s="8"/>
+      <c r="O309" s="8"/>
+      <c r="P309" s="10"/>
+      <c r="Q309" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="R309" s="11" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="310" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A310" s="8" t="s">
+        <v>855</v>
+      </c>
+      <c r="B310" s="8" t="s">
+        <v>856</v>
+      </c>
+      <c r="C310" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D310" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E310" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F310" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G310" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H310" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I310" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J310" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K310" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L310" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M310" s="8">
+        <v>90</v>
+      </c>
+      <c r="N310" s="8"/>
+      <c r="O310" s="8"/>
+      <c r="P310" s="10"/>
+      <c r="Q310" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="R310" s="11" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="311" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A311" s="8" t="s">
+        <v>859</v>
+      </c>
+      <c r="B311" s="8" t="s">
+        <v>860</v>
+      </c>
+      <c r="C311" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D311" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E311" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F311" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G311" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H311" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I311" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="J311" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K311" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="L311" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M311" s="8">
+        <v>70</v>
+      </c>
+      <c r="N311" s="8"/>
+      <c r="O311" s="8"/>
+      <c r="P311" s="10"/>
+      <c r="Q311" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="R311" s="11" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="312" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A312" s="8" t="s">
+        <v>861</v>
+      </c>
+      <c r="B312" s="8" t="s">
+        <v>862</v>
+      </c>
+      <c r="C312" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D312" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E312" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F312" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G312" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H312" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I312" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J312" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="K312" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L312" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M312" s="8">
+        <v>80</v>
+      </c>
+      <c r="N312" s="8"/>
+      <c r="O312" s="8"/>
+      <c r="P312" s="10"/>
+      <c r="Q312" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="R312" s="11" t="s">
         <v>863</v>
+      </c>
+    </row>
+    <row r="313" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A313" s="8" t="s">
+        <v>921</v>
+      </c>
+      <c r="B313" s="8" t="s">
+        <v>922</v>
+      </c>
+      <c r="C313" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D313" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E313" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F313" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G313" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H313" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I313" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J313" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K313" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L313" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M313" s="8">
+        <v>90</v>
+      </c>
+      <c r="N313" s="8"/>
+      <c r="O313" s="8"/>
+      <c r="P313" s="10"/>
+      <c r="Q313" s="9" t="s">
+        <v>923</v>
+      </c>
+      <c r="R313" s="11" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="314" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A314" s="8" t="s">
+        <v>925</v>
+      </c>
+      <c r="B314" s="8" t="s">
+        <v>926</v>
+      </c>
+      <c r="C314" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D314" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E314" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F314" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G314" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H314" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I314" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J314" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K314" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="L314" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M314" s="8">
+        <v>80</v>
+      </c>
+      <c r="N314" s="8"/>
+      <c r="O314" s="8"/>
+      <c r="P314" s="10"/>
+      <c r="Q314" s="9" t="s">
+        <v>923</v>
+      </c>
+      <c r="R314" s="11" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="315" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A315" s="8" t="s">
+        <v>928</v>
+      </c>
+      <c r="B315" s="8" t="s">
+        <v>929</v>
+      </c>
+      <c r="C315" s="9" t="s">
+        <v>930</v>
+      </c>
+      <c r="D315" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E315" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F315" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G315" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H315" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I315" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J315" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K315" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L315" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="M315" s="8">
+        <v>80</v>
+      </c>
+      <c r="N315" s="8" t="s">
+        <v>931</v>
+      </c>
+      <c r="O315" s="8" t="s">
+        <v>932</v>
+      </c>
+      <c r="P315" s="10"/>
+      <c r="Q315" s="9" t="s">
+        <v>923</v>
+      </c>
+      <c r="R315" s="11" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="316" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A316" s="8" t="s">
+        <v>855</v>
+      </c>
+      <c r="B316" s="8" t="s">
+        <v>856</v>
+      </c>
+      <c r="C316" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D316" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E316" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F316" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G316" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H316" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I316" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="J316" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K316" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L316" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M316" s="8">
+        <v>80</v>
+      </c>
+      <c r="N316" s="8"/>
+      <c r="O316" s="8"/>
+      <c r="P316" s="10"/>
+      <c r="Q316" s="9" t="s">
+        <v>934</v>
+      </c>
+      <c r="R316" s="11" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="317" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A317" s="8" t="s">
+        <v>935</v>
+      </c>
+      <c r="B317" s="8" t="s">
+        <v>862</v>
+      </c>
+      <c r="C317" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D317" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E317" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F317" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G317" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H317" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I317" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J317" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="K317" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="L317" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M317" s="8">
+        <v>70</v>
+      </c>
+      <c r="N317" s="8"/>
+      <c r="O317" s="8"/>
+      <c r="P317" s="10"/>
+      <c r="Q317" s="9" t="s">
+        <v>934</v>
+      </c>
+      <c r="R317" s="11" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="318" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A318" s="8" t="s">
+        <v>937</v>
+      </c>
+      <c r="B318" s="8" t="s">
+        <v>938</v>
+      </c>
+      <c r="C318" s="9" t="s">
+        <v>934</v>
+      </c>
+      <c r="D318" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E318" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F318" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G318" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H318" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I318" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J318" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="K318" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L318" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M318" s="8">
+        <v>90</v>
+      </c>
+      <c r="N318" s="8"/>
+      <c r="O318" s="8"/>
+      <c r="P318" s="10"/>
+      <c r="Q318" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="R318" s="11" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="319" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A319" s="8" t="s">
+        <v>941</v>
+      </c>
+      <c r="B319" s="8" t="s">
+        <v>942</v>
+      </c>
+      <c r="C319" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="D319" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E319" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F319" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G319" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H319" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I319" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J319" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="K319" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="L319" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M319" s="8">
+        <v>70</v>
+      </c>
+      <c r="N319" s="8"/>
+      <c r="O319" s="8"/>
+      <c r="P319" s="10"/>
+      <c r="Q319" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="R319" s="11" t="s">
+        <v>943</v>
       </c>
     </row>
   </sheetData>
@@ -17827,7 +18760,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9848E97-FB23-44B1-9CE3-C616F78A0A8B}">
-  <dimension ref="A1:S293"/>
+  <dimension ref="A1:S311"/>
   <sheetFormatPr defaultColWidth="15.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -27371,6 +28304,640 @@
       </c>
       <c r="M293" s="11" t="s">
         <v>874</v>
+      </c>
+    </row>
+    <row r="294" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A294" s="8" t="s">
+        <v>944</v>
+      </c>
+      <c r="B294" s="8" t="s">
+        <v>849</v>
+      </c>
+      <c r="C294" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D294" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E294" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="F294" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G294" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H294" s="8">
+        <v>30</v>
+      </c>
+      <c r="I294" s="8"/>
+      <c r="J294" s="8"/>
+      <c r="K294" s="10"/>
+      <c r="L294" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M294" s="11" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="295" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A295" s="8" t="s">
+        <v>946</v>
+      </c>
+      <c r="B295" s="8" t="s">
+        <v>853</v>
+      </c>
+      <c r="C295" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D295" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E295" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F295" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G295" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H295" s="8">
+        <v>40</v>
+      </c>
+      <c r="I295" s="8"/>
+      <c r="J295" s="8"/>
+      <c r="K295" s="10"/>
+      <c r="L295" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M295" s="11" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="296" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A296" s="8" t="s">
+        <v>948</v>
+      </c>
+      <c r="B296" s="8" t="s">
+        <v>913</v>
+      </c>
+      <c r="C296" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="D296" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E296" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F296" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G296" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H296" s="8">
+        <v>40</v>
+      </c>
+      <c r="I296" s="8"/>
+      <c r="J296" s="8"/>
+      <c r="K296" s="10"/>
+      <c r="L296" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M296" s="11" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="297" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A297" s="8" t="s">
+        <v>907</v>
+      </c>
+      <c r="B297" s="8" t="s">
+        <v>908</v>
+      </c>
+      <c r="C297" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="D297" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E297" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="F297" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="G297" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H297" s="8">
+        <v>20</v>
+      </c>
+      <c r="I297" s="8"/>
+      <c r="J297" s="8"/>
+      <c r="K297" s="10"/>
+      <c r="L297" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M297" s="11" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="298" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A298" s="8" t="s">
+        <v>909</v>
+      </c>
+      <c r="B298" s="8" t="s">
+        <v>910</v>
+      </c>
+      <c r="C298" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="D298" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E298" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F298" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G298" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H298" s="8">
+        <v>40</v>
+      </c>
+      <c r="I298" s="8"/>
+      <c r="J298" s="8"/>
+      <c r="K298" s="10"/>
+      <c r="L298" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M298" s="11" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="299" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A299" s="8" t="s">
+        <v>950</v>
+      </c>
+      <c r="B299" s="8" t="s">
+        <v>951</v>
+      </c>
+      <c r="C299" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="D299" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E299" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F299" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G299" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H299" s="8">
+        <v>40</v>
+      </c>
+      <c r="I299" s="8"/>
+      <c r="J299" s="8"/>
+      <c r="K299" s="10"/>
+      <c r="L299" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M299" s="11" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="300" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A300" s="8" t="s">
+        <v>917</v>
+      </c>
+      <c r="B300" s="8" t="s">
+        <v>918</v>
+      </c>
+      <c r="C300" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="D300" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E300" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F300" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G300" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H300" s="8">
+        <v>40</v>
+      </c>
+      <c r="I300" s="8"/>
+      <c r="J300" s="8"/>
+      <c r="K300" s="10"/>
+      <c r="L300" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M300" s="11" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="301" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A301" s="8" t="s">
+        <v>952</v>
+      </c>
+      <c r="B301" s="8" t="s">
+        <v>916</v>
+      </c>
+      <c r="C301" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="D301" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E301" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F301" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G301" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H301" s="8">
+        <v>40</v>
+      </c>
+      <c r="I301" s="8"/>
+      <c r="J301" s="8"/>
+      <c r="K301" s="10"/>
+      <c r="L301" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M301" s="11" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="302" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A302" s="8" t="s">
+        <v>859</v>
+      </c>
+      <c r="B302" s="8" t="s">
+        <v>860</v>
+      </c>
+      <c r="C302" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D302" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="E302" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="F302" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="G302" s="8" t="s">
+        <v>873</v>
+      </c>
+      <c r="H302" s="8">
+        <v>0</v>
+      </c>
+      <c r="I302" s="8"/>
+      <c r="J302" s="8"/>
+      <c r="K302" s="10"/>
+      <c r="L302" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M302" s="11" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="303" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A303" s="8" t="s">
+        <v>861</v>
+      </c>
+      <c r="B303" s="8" t="s">
+        <v>862</v>
+      </c>
+      <c r="C303" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D303" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E303" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F303" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G303" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="H303" s="8">
+        <v>30</v>
+      </c>
+      <c r="I303" s="8"/>
+      <c r="J303" s="8"/>
+      <c r="K303" s="10"/>
+      <c r="L303" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M303" s="11" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="304" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A304" s="8" t="s">
+        <v>855</v>
+      </c>
+      <c r="B304" s="8" t="s">
+        <v>856</v>
+      </c>
+      <c r="C304" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D304" s="8" t="s">
+        <v>646</v>
+      </c>
+      <c r="E304" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="F304" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="G304" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="H304" s="8">
+        <v>0</v>
+      </c>
+      <c r="I304" s="8"/>
+      <c r="J304" s="8"/>
+      <c r="K304" s="10"/>
+      <c r="L304" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M304" s="11" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="305" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A305" s="8" t="s">
+        <v>954</v>
+      </c>
+      <c r="B305" s="8" t="s">
+        <v>955</v>
+      </c>
+      <c r="C305" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D305" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E305" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F305" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G305" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H305" s="8">
+        <v>40</v>
+      </c>
+      <c r="I305" s="8"/>
+      <c r="J305" s="8"/>
+      <c r="K305" s="10"/>
+      <c r="L305" s="9" t="s">
+        <v>923</v>
+      </c>
+      <c r="M305" s="11" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="306" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A306" s="8" t="s">
+        <v>921</v>
+      </c>
+      <c r="B306" s="8" t="s">
+        <v>922</v>
+      </c>
+      <c r="C306" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D306" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E306" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F306" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G306" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="H306" s="8">
+        <v>40</v>
+      </c>
+      <c r="I306" s="8"/>
+      <c r="J306" s="8"/>
+      <c r="K306" s="10"/>
+      <c r="L306" s="9" t="s">
+        <v>923</v>
+      </c>
+      <c r="M306" s="11" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="307" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A307" s="8" t="s">
+        <v>928</v>
+      </c>
+      <c r="B307" s="8" t="s">
+        <v>929</v>
+      </c>
+      <c r="C307" s="9" t="s">
+        <v>930</v>
+      </c>
+      <c r="D307" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E307" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F307" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G307" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="H307" s="8">
+        <v>30</v>
+      </c>
+      <c r="I307" s="8" t="s">
+        <v>931</v>
+      </c>
+      <c r="J307" s="8" t="s">
+        <v>932</v>
+      </c>
+      <c r="K307" s="10"/>
+      <c r="L307" s="9" t="s">
+        <v>923</v>
+      </c>
+      <c r="M307" s="11" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="308" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A308" s="8" t="s">
+        <v>861</v>
+      </c>
+      <c r="B308" s="8" t="s">
+        <v>862</v>
+      </c>
+      <c r="C308" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D308" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E308" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F308" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G308" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="H308" s="8">
+        <v>30</v>
+      </c>
+      <c r="I308" s="8"/>
+      <c r="J308" s="8"/>
+      <c r="K308" s="10"/>
+      <c r="L308" s="9" t="s">
+        <v>934</v>
+      </c>
+      <c r="M308" s="11" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="309" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A309" s="8" t="s">
+        <v>855</v>
+      </c>
+      <c r="B309" s="8" t="s">
+        <v>856</v>
+      </c>
+      <c r="C309" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D309" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="E309" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="F309" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="G309" s="8" t="s">
+        <v>959</v>
+      </c>
+      <c r="H309" s="8">
+        <v>0</v>
+      </c>
+      <c r="I309" s="8"/>
+      <c r="J309" s="8"/>
+      <c r="K309" s="10"/>
+      <c r="L309" s="9" t="s">
+        <v>934</v>
+      </c>
+      <c r="M309" s="11" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="310" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A310" s="8" t="s">
+        <v>937</v>
+      </c>
+      <c r="B310" s="8" t="s">
+        <v>938</v>
+      </c>
+      <c r="C310" s="9" t="s">
+        <v>934</v>
+      </c>
+      <c r="D310" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E310" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F310" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G310" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="H310" s="8">
+        <v>30</v>
+      </c>
+      <c r="I310" s="8"/>
+      <c r="J310" s="8"/>
+      <c r="K310" s="10"/>
+      <c r="L310" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="M310" s="11" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="311" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A311" s="8" t="s">
+        <v>941</v>
+      </c>
+      <c r="B311" s="8" t="s">
+        <v>942</v>
+      </c>
+      <c r="C311" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="D311" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="E311" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="F311" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="G311" s="8" t="s">
+        <v>959</v>
+      </c>
+      <c r="H311" s="8">
+        <v>10</v>
+      </c>
+      <c r="I311" s="8"/>
+      <c r="J311" s="8"/>
+      <c r="K311" s="10"/>
+      <c r="L311" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="M311" s="11" t="s">
+        <v>961</v>
       </c>
     </row>
   </sheetData>
@@ -27380,7 +28947,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E795EE60-EBCD-4B19-B884-654D5F927670}">
-  <dimension ref="A1:S291"/>
+  <dimension ref="A1:S309"/>
   <sheetFormatPr defaultColWidth="16.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -36860,6 +38427,636 @@
       </c>
       <c r="M291" s="11" t="s">
         <v>886</v>
+      </c>
+    </row>
+    <row r="292" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A292" s="8" t="s">
+        <v>962</v>
+      </c>
+      <c r="B292" s="8" t="s">
+        <v>849</v>
+      </c>
+      <c r="C292" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D292" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E292" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="F292" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G292" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H292" s="8">
+        <v>30</v>
+      </c>
+      <c r="I292" s="8"/>
+      <c r="J292" s="8"/>
+      <c r="K292" s="10"/>
+      <c r="L292" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M292" s="11" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="293" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A293" s="8" t="s">
+        <v>946</v>
+      </c>
+      <c r="B293" s="8" t="s">
+        <v>853</v>
+      </c>
+      <c r="C293" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D293" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E293" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="F293" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G293" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H293" s="8">
+        <v>30</v>
+      </c>
+      <c r="I293" s="8"/>
+      <c r="J293" s="8"/>
+      <c r="K293" s="10"/>
+      <c r="L293" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M293" s="11" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="294" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A294" s="8" t="s">
+        <v>907</v>
+      </c>
+      <c r="B294" s="8" t="s">
+        <v>908</v>
+      </c>
+      <c r="C294" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="D294" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E294" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="F294" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G294" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="H294" s="8">
+        <v>20</v>
+      </c>
+      <c r="I294" s="8"/>
+      <c r="J294" s="8"/>
+      <c r="K294" s="10"/>
+      <c r="L294" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M294" s="11" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="295" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A295" s="8" t="s">
+        <v>966</v>
+      </c>
+      <c r="B295" s="8" t="s">
+        <v>951</v>
+      </c>
+      <c r="C295" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="D295" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E295" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F295" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G295" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H295" s="8">
+        <v>40</v>
+      </c>
+      <c r="I295" s="8"/>
+      <c r="J295" s="8"/>
+      <c r="K295" s="10"/>
+      <c r="L295" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M295" s="11" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="296" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A296" s="8" t="s">
+        <v>952</v>
+      </c>
+      <c r="B296" s="8" t="s">
+        <v>916</v>
+      </c>
+      <c r="C296" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="D296" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E296" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F296" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G296" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H296" s="8">
+        <v>40</v>
+      </c>
+      <c r="I296" s="8"/>
+      <c r="J296" s="8"/>
+      <c r="K296" s="10"/>
+      <c r="L296" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M296" s="11" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="297" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A297" s="8" t="s">
+        <v>909</v>
+      </c>
+      <c r="B297" s="8" t="s">
+        <v>910</v>
+      </c>
+      <c r="C297" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="D297" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E297" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F297" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G297" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H297" s="8">
+        <v>40</v>
+      </c>
+      <c r="I297" s="8"/>
+      <c r="J297" s="8"/>
+      <c r="K297" s="10"/>
+      <c r="L297" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M297" s="11" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="298" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A298" s="8" t="s">
+        <v>948</v>
+      </c>
+      <c r="B298" s="8" t="s">
+        <v>913</v>
+      </c>
+      <c r="C298" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="D298" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E298" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F298" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G298" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H298" s="8">
+        <v>40</v>
+      </c>
+      <c r="I298" s="8"/>
+      <c r="J298" s="8"/>
+      <c r="K298" s="10"/>
+      <c r="L298" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M298" s="11" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="299" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A299" s="8" t="s">
+        <v>917</v>
+      </c>
+      <c r="B299" s="8" t="s">
+        <v>918</v>
+      </c>
+      <c r="C299" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="D299" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E299" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F299" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G299" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H299" s="8">
+        <v>40</v>
+      </c>
+      <c r="I299" s="8"/>
+      <c r="J299" s="8"/>
+      <c r="K299" s="10"/>
+      <c r="L299" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M299" s="11" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="300" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A300" s="8" t="s">
+        <v>855</v>
+      </c>
+      <c r="B300" s="8" t="s">
+        <v>856</v>
+      </c>
+      <c r="C300" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D300" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E300" s="8" t="s">
+        <v>880</v>
+      </c>
+      <c r="F300" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G300" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="H300" s="8">
+        <v>20</v>
+      </c>
+      <c r="I300" s="8"/>
+      <c r="J300" s="8"/>
+      <c r="K300" s="10"/>
+      <c r="L300" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M300" s="11" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="301" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A301" s="8" t="s">
+        <v>968</v>
+      </c>
+      <c r="B301" s="8" t="s">
+        <v>860</v>
+      </c>
+      <c r="C301" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D301" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E301" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F301" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G301" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="H301" s="8">
+        <v>30</v>
+      </c>
+      <c r="I301" s="8"/>
+      <c r="J301" s="8"/>
+      <c r="K301" s="10"/>
+      <c r="L301" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M301" s="11" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="302" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A302" s="8" t="s">
+        <v>861</v>
+      </c>
+      <c r="B302" s="8" t="s">
+        <v>862</v>
+      </c>
+      <c r="C302" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D302" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E302" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F302" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G302" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="H302" s="8">
+        <v>30</v>
+      </c>
+      <c r="I302" s="8"/>
+      <c r="J302" s="8"/>
+      <c r="K302" s="10"/>
+      <c r="L302" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M302" s="11" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="303" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A303" s="8" t="s">
+        <v>969</v>
+      </c>
+      <c r="B303" s="8" t="s">
+        <v>926</v>
+      </c>
+      <c r="C303" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D303" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E303" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F303" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G303" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H303" s="8">
+        <v>40</v>
+      </c>
+      <c r="I303" s="8"/>
+      <c r="J303" s="8"/>
+      <c r="K303" s="10"/>
+      <c r="L303" s="9" t="s">
+        <v>934</v>
+      </c>
+      <c r="M303" s="11" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="304" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A304" s="8" t="s">
+        <v>921</v>
+      </c>
+      <c r="B304" s="8" t="s">
+        <v>922</v>
+      </c>
+      <c r="C304" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D304" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E304" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F304" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G304" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H304" s="8">
+        <v>40</v>
+      </c>
+      <c r="I304" s="8"/>
+      <c r="J304" s="8"/>
+      <c r="K304" s="10"/>
+      <c r="L304" s="9" t="s">
+        <v>934</v>
+      </c>
+      <c r="M304" s="11" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="305" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A305" s="8" t="s">
+        <v>972</v>
+      </c>
+      <c r="B305" s="8" t="s">
+        <v>973</v>
+      </c>
+      <c r="C305" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D305" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E305" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F305" s="8" t="s">
+        <v>652</v>
+      </c>
+      <c r="G305" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H305" s="8">
+        <v>30</v>
+      </c>
+      <c r="I305" s="8"/>
+      <c r="J305" s="8"/>
+      <c r="K305" s="10"/>
+      <c r="L305" s="9" t="s">
+        <v>934</v>
+      </c>
+      <c r="M305" s="11" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="306" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A306" s="8" t="s">
+        <v>861</v>
+      </c>
+      <c r="B306" s="8" t="s">
+        <v>975</v>
+      </c>
+      <c r="C306" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D306" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E306" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="F306" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G306" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="H306" s="8">
+        <v>20</v>
+      </c>
+      <c r="I306" s="8"/>
+      <c r="J306" s="8"/>
+      <c r="K306" s="10"/>
+      <c r="L306" s="9" t="s">
+        <v>934</v>
+      </c>
+      <c r="M306" s="11" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="307" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A307" s="8" t="s">
+        <v>855</v>
+      </c>
+      <c r="B307" s="8" t="s">
+        <v>856</v>
+      </c>
+      <c r="C307" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D307" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E307" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F307" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G307" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="H307" s="8">
+        <v>30</v>
+      </c>
+      <c r="I307" s="8"/>
+      <c r="J307" s="8"/>
+      <c r="K307" s="10"/>
+      <c r="L307" s="9" t="s">
+        <v>934</v>
+      </c>
+      <c r="M307" s="11" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="308" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A308" s="8" t="s">
+        <v>937</v>
+      </c>
+      <c r="B308" s="8" t="s">
+        <v>938</v>
+      </c>
+      <c r="C308" s="9" t="s">
+        <v>934</v>
+      </c>
+      <c r="D308" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E308" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="F308" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G308" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H308" s="8">
+        <v>40</v>
+      </c>
+      <c r="I308" s="8"/>
+      <c r="J308" s="8"/>
+      <c r="K308" s="10"/>
+      <c r="L308" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="M308" s="11" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="309" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A309" s="8" t="s">
+        <v>941</v>
+      </c>
+      <c r="B309" s="8" t="s">
+        <v>942</v>
+      </c>
+      <c r="C309" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="D309" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="E309" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="F309" s="8" t="s">
+        <v>979</v>
+      </c>
+      <c r="G309" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="H309" s="8">
+        <v>20</v>
+      </c>
+      <c r="I309" s="8"/>
+      <c r="J309" s="8"/>
+      <c r="K309" s="10"/>
+      <c r="L309" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="M309" s="11" t="s">
+        <v>940</v>
       </c>
     </row>
   </sheetData>
@@ -36869,7 +39066,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41BB7886-C4B6-45DF-87F2-53652B8B0BB3}">
-  <dimension ref="A1:S289"/>
+  <dimension ref="A1:S307"/>
   <sheetFormatPr defaultColWidth="12.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -46288,6 +48485,636 @@
       </c>
       <c r="M289" s="11" t="s">
         <v>897</v>
+      </c>
+    </row>
+    <row r="290" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A290" s="8" t="s">
+        <v>962</v>
+      </c>
+      <c r="B290" s="8" t="s">
+        <v>849</v>
+      </c>
+      <c r="C290" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D290" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E290" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F290" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G290" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H290" s="8">
+        <v>40</v>
+      </c>
+      <c r="I290" s="8"/>
+      <c r="J290" s="8"/>
+      <c r="K290" s="10"/>
+      <c r="L290" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M290" s="11" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="291" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A291" s="8" t="s">
+        <v>946</v>
+      </c>
+      <c r="B291" s="8" t="s">
+        <v>853</v>
+      </c>
+      <c r="C291" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D291" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E291" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F291" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G291" s="8" t="s">
+        <v>523</v>
+      </c>
+      <c r="H291" s="8">
+        <v>30</v>
+      </c>
+      <c r="I291" s="8"/>
+      <c r="J291" s="8"/>
+      <c r="K291" s="10"/>
+      <c r="L291" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M291" s="11" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="292" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A292" s="8" t="s">
+        <v>950</v>
+      </c>
+      <c r="B292" s="8" t="s">
+        <v>951</v>
+      </c>
+      <c r="C292" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="D292" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E292" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F292" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G292" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H292" s="8">
+        <v>40</v>
+      </c>
+      <c r="I292" s="8"/>
+      <c r="J292" s="8"/>
+      <c r="K292" s="10"/>
+      <c r="L292" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M292" s="11" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="293" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A293" s="8" t="s">
+        <v>952</v>
+      </c>
+      <c r="B293" s="8" t="s">
+        <v>916</v>
+      </c>
+      <c r="C293" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="D293" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E293" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F293" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G293" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H293" s="8">
+        <v>40</v>
+      </c>
+      <c r="I293" s="8"/>
+      <c r="J293" s="8"/>
+      <c r="K293" s="10"/>
+      <c r="L293" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M293" s="11" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="294" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A294" s="8" t="s">
+        <v>982</v>
+      </c>
+      <c r="B294" s="8" t="s">
+        <v>913</v>
+      </c>
+      <c r="C294" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="D294" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E294" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F294" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G294" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H294" s="8">
+        <v>40</v>
+      </c>
+      <c r="I294" s="8"/>
+      <c r="J294" s="8"/>
+      <c r="K294" s="10"/>
+      <c r="L294" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M294" s="11" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="295" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A295" s="8" t="s">
+        <v>917</v>
+      </c>
+      <c r="B295" s="8" t="s">
+        <v>918</v>
+      </c>
+      <c r="C295" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="D295" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E295" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F295" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G295" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H295" s="8">
+        <v>40</v>
+      </c>
+      <c r="I295" s="8"/>
+      <c r="J295" s="8"/>
+      <c r="K295" s="10"/>
+      <c r="L295" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M295" s="11" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="296" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A296" s="8" t="s">
+        <v>907</v>
+      </c>
+      <c r="B296" s="8" t="s">
+        <v>908</v>
+      </c>
+      <c r="C296" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="D296" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E296" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F296" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G296" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H296" s="8">
+        <v>40</v>
+      </c>
+      <c r="I296" s="8"/>
+      <c r="J296" s="8"/>
+      <c r="K296" s="10"/>
+      <c r="L296" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M296" s="11" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="297" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A297" s="8" t="s">
+        <v>909</v>
+      </c>
+      <c r="B297" s="8" t="s">
+        <v>910</v>
+      </c>
+      <c r="C297" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="D297" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E297" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F297" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G297" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H297" s="8">
+        <v>40</v>
+      </c>
+      <c r="I297" s="8"/>
+      <c r="J297" s="8"/>
+      <c r="K297" s="10"/>
+      <c r="L297" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M297" s="11" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="298" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A298" s="8" t="s">
+        <v>855</v>
+      </c>
+      <c r="B298" s="8" t="s">
+        <v>856</v>
+      </c>
+      <c r="C298" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D298" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E298" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F298" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G298" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H298" s="8">
+        <v>40</v>
+      </c>
+      <c r="I298" s="8"/>
+      <c r="J298" s="8"/>
+      <c r="K298" s="10"/>
+      <c r="L298" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M298" s="11" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="299" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A299" s="8" t="s">
+        <v>861</v>
+      </c>
+      <c r="B299" s="8" t="s">
+        <v>862</v>
+      </c>
+      <c r="C299" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D299" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E299" s="8" t="s">
+        <v>520</v>
+      </c>
+      <c r="F299" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G299" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H299" s="8">
+        <v>30</v>
+      </c>
+      <c r="I299" s="8"/>
+      <c r="J299" s="8"/>
+      <c r="K299" s="10"/>
+      <c r="L299" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M299" s="11" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="300" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A300" s="8" t="s">
+        <v>859</v>
+      </c>
+      <c r="B300" s="8" t="s">
+        <v>860</v>
+      </c>
+      <c r="C300" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D300" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E300" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F300" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G300" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H300" s="8">
+        <v>40</v>
+      </c>
+      <c r="I300" s="8"/>
+      <c r="J300" s="8"/>
+      <c r="K300" s="10"/>
+      <c r="L300" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M300" s="11" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="301" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A301" s="8" t="s">
+        <v>969</v>
+      </c>
+      <c r="B301" s="8" t="s">
+        <v>926</v>
+      </c>
+      <c r="C301" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D301" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="E301" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F301" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G301" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H301" s="8">
+        <v>30</v>
+      </c>
+      <c r="I301" s="8"/>
+      <c r="J301" s="8"/>
+      <c r="K301" s="10"/>
+      <c r="L301" s="9" t="s">
+        <v>934</v>
+      </c>
+      <c r="M301" s="11" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="302" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A302" s="8" t="s">
+        <v>921</v>
+      </c>
+      <c r="B302" s="8" t="s">
+        <v>922</v>
+      </c>
+      <c r="C302" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D302" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E302" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F302" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="G302" s="8" t="s">
+        <v>661</v>
+      </c>
+      <c r="H302" s="8">
+        <v>20</v>
+      </c>
+      <c r="I302" s="8"/>
+      <c r="J302" s="8"/>
+      <c r="K302" s="10"/>
+      <c r="L302" s="9" t="s">
+        <v>934</v>
+      </c>
+      <c r="M302" s="11" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="303" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A303" s="8" t="s">
+        <v>972</v>
+      </c>
+      <c r="B303" s="8" t="s">
+        <v>973</v>
+      </c>
+      <c r="C303" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="D303" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E303" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="F303" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="G303" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H303" s="8">
+        <v>30</v>
+      </c>
+      <c r="I303" s="8"/>
+      <c r="J303" s="8"/>
+      <c r="K303" s="10"/>
+      <c r="L303" s="9" t="s">
+        <v>934</v>
+      </c>
+      <c r="M303" s="11" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="304" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A304" s="8" t="s">
+        <v>987</v>
+      </c>
+      <c r="B304" s="8" t="s">
+        <v>862</v>
+      </c>
+      <c r="C304" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D304" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E304" s="8" t="s">
+        <v>520</v>
+      </c>
+      <c r="F304" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="G304" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H304" s="8">
+        <v>20</v>
+      </c>
+      <c r="I304" s="8"/>
+      <c r="J304" s="8"/>
+      <c r="K304" s="10"/>
+      <c r="L304" s="9" t="s">
+        <v>934</v>
+      </c>
+      <c r="M304" s="11" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="305" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A305" s="8" t="s">
+        <v>855</v>
+      </c>
+      <c r="B305" s="8" t="s">
+        <v>856</v>
+      </c>
+      <c r="C305" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D305" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E305" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="F305" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G305" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H305" s="8">
+        <v>30</v>
+      </c>
+      <c r="I305" s="8"/>
+      <c r="J305" s="8"/>
+      <c r="K305" s="10"/>
+      <c r="L305" s="9" t="s">
+        <v>934</v>
+      </c>
+      <c r="M305" s="11" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="306" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A306" s="8" t="s">
+        <v>937</v>
+      </c>
+      <c r="B306" s="8" t="s">
+        <v>938</v>
+      </c>
+      <c r="C306" s="9" t="s">
+        <v>934</v>
+      </c>
+      <c r="D306" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E306" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="F306" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G306" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H306" s="8">
+        <v>30</v>
+      </c>
+      <c r="I306" s="8"/>
+      <c r="J306" s="8"/>
+      <c r="K306" s="10"/>
+      <c r="L306" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="M306" s="11" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="307" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A307" s="8" t="s">
+        <v>941</v>
+      </c>
+      <c r="B307" s="8" t="s">
+        <v>942</v>
+      </c>
+      <c r="C307" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="D307" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="E307" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="F307" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="G307" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="H307" s="8">
+        <v>30</v>
+      </c>
+      <c r="I307" s="8"/>
+      <c r="J307" s="8"/>
+      <c r="K307" s="10"/>
+      <c r="L307" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="M307" s="11" t="s">
+        <v>844</v>
       </c>
     </row>
   </sheetData>
@@ -46297,7 +49124,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{083B2BF1-723B-4775-8297-318920D3FD0C}">
-  <dimension ref="A1:S286"/>
+  <dimension ref="A1:S303"/>
   <sheetFormatPr defaultColWidth="13.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -55613,6 +58440,601 @@
         <v>906</v>
       </c>
     </row>
+    <row r="287" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A287" s="8" t="s">
+        <v>907</v>
+      </c>
+      <c r="B287" s="8" t="s">
+        <v>908</v>
+      </c>
+      <c r="C287" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="D287" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E287" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F287" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="G287" s="8" t="s">
+        <v>899</v>
+      </c>
+      <c r="H287" s="8">
+        <v>30</v>
+      </c>
+      <c r="I287" s="8"/>
+      <c r="J287" s="8"/>
+      <c r="K287" s="10"/>
+      <c r="L287" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M287" s="11" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="288" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A288" s="8" t="s">
+        <v>948</v>
+      </c>
+      <c r="B288" s="8" t="s">
+        <v>913</v>
+      </c>
+      <c r="C288" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="D288" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E288" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F288" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="G288" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H288" s="8">
+        <v>40</v>
+      </c>
+      <c r="I288" s="8"/>
+      <c r="J288" s="8"/>
+      <c r="K288" s="10"/>
+      <c r="L288" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M288" s="11" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="289" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A289" s="8" t="s">
+        <v>909</v>
+      </c>
+      <c r="B289" s="8" t="s">
+        <v>910</v>
+      </c>
+      <c r="C289" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="D289" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E289" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F289" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="G289" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H289" s="8">
+        <v>40</v>
+      </c>
+      <c r="I289" s="8"/>
+      <c r="J289" s="8"/>
+      <c r="K289" s="10"/>
+      <c r="L289" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M289" s="11" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="290" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A290" s="8" t="s">
+        <v>950</v>
+      </c>
+      <c r="B290" s="8" t="s">
+        <v>951</v>
+      </c>
+      <c r="C290" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="D290" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E290" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F290" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="G290" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H290" s="8">
+        <v>40</v>
+      </c>
+      <c r="I290" s="8"/>
+      <c r="J290" s="8"/>
+      <c r="K290" s="10"/>
+      <c r="L290" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M290" s="11" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="291" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A291" s="8" t="s">
+        <v>952</v>
+      </c>
+      <c r="B291" s="8" t="s">
+        <v>916</v>
+      </c>
+      <c r="C291" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="D291" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E291" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F291" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="G291" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H291" s="8">
+        <v>40</v>
+      </c>
+      <c r="I291" s="8"/>
+      <c r="J291" s="8"/>
+      <c r="K291" s="10"/>
+      <c r="L291" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M291" s="11" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="292" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A292" s="8" t="s">
+        <v>917</v>
+      </c>
+      <c r="B292" s="8" t="s">
+        <v>918</v>
+      </c>
+      <c r="C292" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="D292" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E292" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F292" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="G292" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H292" s="8">
+        <v>40</v>
+      </c>
+      <c r="I292" s="8"/>
+      <c r="J292" s="8"/>
+      <c r="K292" s="10"/>
+      <c r="L292" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M292" s="11" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="293" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A293" s="8" t="s">
+        <v>855</v>
+      </c>
+      <c r="B293" s="8" t="s">
+        <v>856</v>
+      </c>
+      <c r="C293" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D293" s="8" t="s">
+        <v>607</v>
+      </c>
+      <c r="E293" s="8" t="s">
+        <v>903</v>
+      </c>
+      <c r="F293" s="8" t="s">
+        <v>904</v>
+      </c>
+      <c r="G293" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H293" s="8">
+        <v>10</v>
+      </c>
+      <c r="I293" s="8"/>
+      <c r="J293" s="8"/>
+      <c r="K293" s="10"/>
+      <c r="L293" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M293" s="11" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="294" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A294" s="8" t="s">
+        <v>861</v>
+      </c>
+      <c r="B294" s="8" t="s">
+        <v>862</v>
+      </c>
+      <c r="C294" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D294" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E294" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F294" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="G294" s="8" t="s">
+        <v>899</v>
+      </c>
+      <c r="H294" s="8">
+        <v>30</v>
+      </c>
+      <c r="I294" s="8"/>
+      <c r="J294" s="8"/>
+      <c r="K294" s="10"/>
+      <c r="L294" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M294" s="11" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="295" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A295" s="8" t="s">
+        <v>859</v>
+      </c>
+      <c r="B295" s="8" t="s">
+        <v>860</v>
+      </c>
+      <c r="C295" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D295" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="E295" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F295" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="G295" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H295" s="8">
+        <v>20</v>
+      </c>
+      <c r="I295" s="8"/>
+      <c r="J295" s="8"/>
+      <c r="K295" s="10"/>
+      <c r="L295" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="M295" s="11" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="296" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A296" s="8" t="s">
+        <v>962</v>
+      </c>
+      <c r="B296" s="8" t="s">
+        <v>849</v>
+      </c>
+      <c r="C296" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D296" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E296" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F296" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="G296" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H296" s="8">
+        <v>40</v>
+      </c>
+      <c r="I296" s="8"/>
+      <c r="J296" s="8"/>
+      <c r="K296" s="10"/>
+      <c r="L296" s="9" t="s">
+        <v>992</v>
+      </c>
+      <c r="M296" s="11" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="297" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A297" s="8" t="s">
+        <v>946</v>
+      </c>
+      <c r="B297" s="8" t="s">
+        <v>853</v>
+      </c>
+      <c r="C297" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D297" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E297" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F297" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="G297" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H297" s="8">
+        <v>40</v>
+      </c>
+      <c r="I297" s="8"/>
+      <c r="J297" s="8"/>
+      <c r="K297" s="10"/>
+      <c r="L297" s="9" t="s">
+        <v>992</v>
+      </c>
+      <c r="M297" s="11" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="298" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A298" s="8" t="s">
+        <v>969</v>
+      </c>
+      <c r="B298" s="8" t="s">
+        <v>926</v>
+      </c>
+      <c r="C298" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D298" s="8" t="s">
+        <v>546</v>
+      </c>
+      <c r="E298" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F298" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="G298" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H298" s="8">
+        <v>30</v>
+      </c>
+      <c r="I298" s="8"/>
+      <c r="J298" s="8"/>
+      <c r="K298" s="10"/>
+      <c r="L298" s="9" t="s">
+        <v>934</v>
+      </c>
+      <c r="M298" s="11" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="299" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A299" s="8" t="s">
+        <v>921</v>
+      </c>
+      <c r="B299" s="8" t="s">
+        <v>922</v>
+      </c>
+      <c r="C299" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D299" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E299" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F299" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="G299" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H299" s="8">
+        <v>40</v>
+      </c>
+      <c r="I299" s="8"/>
+      <c r="J299" s="8"/>
+      <c r="K299" s="10"/>
+      <c r="L299" s="9" t="s">
+        <v>934</v>
+      </c>
+      <c r="M299" s="11" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="300" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A300" s="8" t="s">
+        <v>972</v>
+      </c>
+      <c r="B300" s="8" t="s">
+        <v>973</v>
+      </c>
+      <c r="C300" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="D300" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E300" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F300" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="G300" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H300" s="8">
+        <v>40</v>
+      </c>
+      <c r="I300" s="8"/>
+      <c r="J300" s="8"/>
+      <c r="K300" s="10"/>
+      <c r="L300" s="9" t="s">
+        <v>934</v>
+      </c>
+      <c r="M300" s="11" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="301" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A301" s="8" t="s">
+        <v>861</v>
+      </c>
+      <c r="B301" s="8" t="s">
+        <v>862</v>
+      </c>
+      <c r="C301" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D301" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="E301" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F301" s="8" t="s">
+        <v>556</v>
+      </c>
+      <c r="G301" s="8" t="s">
+        <v>899</v>
+      </c>
+      <c r="H301" s="8">
+        <v>10</v>
+      </c>
+      <c r="I301" s="8"/>
+      <c r="J301" s="8"/>
+      <c r="K301" s="10"/>
+      <c r="L301" s="9" t="s">
+        <v>934</v>
+      </c>
+      <c r="M301" s="11" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="302" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A302" s="8" t="s">
+        <v>855</v>
+      </c>
+      <c r="B302" s="8" t="s">
+        <v>856</v>
+      </c>
+      <c r="C302" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="D302" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="E302" s="8" t="s">
+        <v>903</v>
+      </c>
+      <c r="F302" s="8" t="s">
+        <v>552</v>
+      </c>
+      <c r="G302" s="8" t="s">
+        <v>899</v>
+      </c>
+      <c r="H302" s="8">
+        <v>0</v>
+      </c>
+      <c r="I302" s="8"/>
+      <c r="J302" s="8"/>
+      <c r="K302" s="10"/>
+      <c r="L302" s="9" t="s">
+        <v>934</v>
+      </c>
+      <c r="M302" s="11" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="303" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A303" s="8" t="s">
+        <v>937</v>
+      </c>
+      <c r="B303" s="8" t="s">
+        <v>938</v>
+      </c>
+      <c r="C303" s="9" t="s">
+        <v>934</v>
+      </c>
+      <c r="D303" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E303" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="F303" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="G303" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="H303" s="8">
+        <v>40</v>
+      </c>
+      <c r="I303" s="8"/>
+      <c r="J303" s="8"/>
+      <c r="K303" s="10"/>
+      <c r="L303" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="M303" s="11" t="s">
+        <v>999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/data/Integracao Armazem.xlsx
+++ b/data/Integracao Armazem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{274CCF60-1562-40B7-953E-F7E32334B68F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DE2AF04-3E6F-45C3-A6B3-A73A8C06F36D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{422D47E6-8DC3-4B25-BD50-E675C15B05CB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{422D47E6-8DC3-4B25-BD50-E675C15B05CB}"/>
   </bookViews>
   <sheets>
     <sheet name="M1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11458" uniqueCount="1071">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11666" uniqueCount="1094">
   <si>
     <t>Selecione o EPI que NÃO é obrigatório durante o processo de montagem de paletes</t>
   </si>
@@ -3372,6 +3372,75 @@
   </si>
   <si>
     <t>17:07</t>
+  </si>
+  <si>
+    <t>JEFFERSON THIAGO DE OLIVEIRA ARAUJO</t>
+  </si>
+  <si>
+    <t>11475124937</t>
+  </si>
+  <si>
+    <t>20/07/2026</t>
+  </si>
+  <si>
+    <t>ALEF HENRIQUE DA SILVA</t>
+  </si>
+  <si>
+    <t>17548571755</t>
+  </si>
+  <si>
+    <t>01/07/2026</t>
+  </si>
+  <si>
+    <t>08/07/2026</t>
+  </si>
+  <si>
+    <t>11:39</t>
+  </si>
+  <si>
+    <t>JOSE APARECIDO QUEIROS DA HORA</t>
+  </si>
+  <si>
+    <t>03/07/2026</t>
+  </si>
+  <si>
+    <t>11:04</t>
+  </si>
+  <si>
+    <t>VAGNER EVANGELISTA</t>
+  </si>
+  <si>
+    <t>10:56</t>
+  </si>
+  <si>
+    <t>11:42</t>
+  </si>
+  <si>
+    <t>14:23</t>
+  </si>
+  <si>
+    <t>11:31</t>
+  </si>
+  <si>
+    <t>11:29</t>
+  </si>
+  <si>
+    <t>Adilson Ramos Filho</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>Caso tenha problemas com meu usuário devo pedir a senha de outro funcionário</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>15:19</t>
   </si>
 </sst>
 </file>
@@ -3794,7 +3863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D8EC4C0-DEF5-4A13-83D8-46C06041A7DF}">
-  <dimension ref="A1:S335"/>
+  <dimension ref="A1:S337"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="19" width="14.109375" customWidth="1"/>
@@ -19798,6 +19867,106 @@
         <v>1070</v>
       </c>
     </row>
+    <row r="336" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A336" s="22" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B336" s="22" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C336" s="23" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D336" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="E336" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="F336" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="G336" s="22" t="s">
+        <v>356</v>
+      </c>
+      <c r="H336" s="22" t="s">
+        <v>357</v>
+      </c>
+      <c r="I336" s="22" t="s">
+        <v>358</v>
+      </c>
+      <c r="J336" s="22" t="s">
+        <v>373</v>
+      </c>
+      <c r="K336" s="22" t="s">
+        <v>360</v>
+      </c>
+      <c r="L336" s="22" t="s">
+        <v>366</v>
+      </c>
+      <c r="M336" s="22">
+        <v>80</v>
+      </c>
+      <c r="N336" s="22"/>
+      <c r="O336" s="22"/>
+      <c r="P336" s="15"/>
+      <c r="Q336" s="23" t="s">
+        <v>1073</v>
+      </c>
+      <c r="R336" s="24" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="337" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A337" s="22" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B337" s="22" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C337" s="23" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D337" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="E337" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="F337" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="G337" s="22" t="s">
+        <v>356</v>
+      </c>
+      <c r="H337" s="22" t="s">
+        <v>357</v>
+      </c>
+      <c r="I337" s="22" t="s">
+        <v>358</v>
+      </c>
+      <c r="J337" s="22" t="s">
+        <v>359</v>
+      </c>
+      <c r="K337" s="22" t="s">
+        <v>360</v>
+      </c>
+      <c r="L337" s="22" t="s">
+        <v>366</v>
+      </c>
+      <c r="M337" s="22">
+        <v>90</v>
+      </c>
+      <c r="N337" s="22"/>
+      <c r="O337" s="22"/>
+      <c r="P337" s="15"/>
+      <c r="Q337" s="23" t="s">
+        <v>1077</v>
+      </c>
+      <c r="R337" s="24" t="s">
+        <v>1078</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -19806,7 +19975,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9848E97-FB23-44B1-9CE3-C616F78A0A8B}">
-  <dimension ref="A1:S319"/>
+  <dimension ref="A1:S324"/>
   <sheetFormatPr defaultColWidth="15.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -30264,6 +30433,181 @@
       </c>
       <c r="M319" s="24" t="s">
         <v>1051</v>
+      </c>
+    </row>
+    <row r="320" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A320" s="22" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B320" s="22" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C320" s="23" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D320" s="22" t="s">
+        <v>404</v>
+      </c>
+      <c r="E320" s="22" t="s">
+        <v>613</v>
+      </c>
+      <c r="F320" s="22" t="s">
+        <v>434</v>
+      </c>
+      <c r="G320" s="22" t="s">
+        <v>435</v>
+      </c>
+      <c r="H320" s="22">
+        <v>30</v>
+      </c>
+      <c r="I320" s="22"/>
+      <c r="J320" s="22"/>
+      <c r="K320" s="15"/>
+      <c r="L320" s="23" t="s">
+        <v>1080</v>
+      </c>
+      <c r="M320" s="24" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="321" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A321" s="22" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B321" s="22" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C321" s="23" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D321" s="22" t="s">
+        <v>446</v>
+      </c>
+      <c r="E321" s="22" t="s">
+        <v>437</v>
+      </c>
+      <c r="F321" s="22" t="s">
+        <v>434</v>
+      </c>
+      <c r="G321" s="22" t="s">
+        <v>435</v>
+      </c>
+      <c r="H321" s="22">
+        <v>30</v>
+      </c>
+      <c r="I321" s="22"/>
+      <c r="J321" s="22"/>
+      <c r="K321" s="15"/>
+      <c r="L321" s="23" t="s">
+        <v>1080</v>
+      </c>
+      <c r="M321" s="24" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="322" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A322" s="22" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B322" s="22" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C322" s="23" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D322" s="22" t="s">
+        <v>404</v>
+      </c>
+      <c r="E322" s="22" t="s">
+        <v>613</v>
+      </c>
+      <c r="F322" s="22" t="s">
+        <v>434</v>
+      </c>
+      <c r="G322" s="22" t="s">
+        <v>435</v>
+      </c>
+      <c r="H322" s="22">
+        <v>30</v>
+      </c>
+      <c r="I322" s="22"/>
+      <c r="J322" s="22"/>
+      <c r="K322" s="15"/>
+      <c r="L322" s="23" t="s">
+        <v>1080</v>
+      </c>
+      <c r="M322" s="24" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="323" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A323" s="22" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B323" s="22" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C323" s="23" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D323" s="22" t="s">
+        <v>404</v>
+      </c>
+      <c r="E323" s="22" t="s">
+        <v>437</v>
+      </c>
+      <c r="F323" s="22" t="s">
+        <v>434</v>
+      </c>
+      <c r="G323" s="22" t="s">
+        <v>435</v>
+      </c>
+      <c r="H323" s="22">
+        <v>40</v>
+      </c>
+      <c r="I323" s="22"/>
+      <c r="J323" s="22"/>
+      <c r="K323" s="15"/>
+      <c r="L323" s="23" t="s">
+        <v>1077</v>
+      </c>
+      <c r="M323" s="24" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="324" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A324" s="22" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B324" s="22" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C324" s="23" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D324" s="22" t="s">
+        <v>404</v>
+      </c>
+      <c r="E324" s="22" t="s">
+        <v>437</v>
+      </c>
+      <c r="F324" s="22" t="s">
+        <v>447</v>
+      </c>
+      <c r="G324" s="22" t="s">
+        <v>435</v>
+      </c>
+      <c r="H324" s="22">
+        <v>30</v>
+      </c>
+      <c r="I324" s="22"/>
+      <c r="J324" s="22"/>
+      <c r="K324" s="15"/>
+      <c r="L324" s="23" t="s">
+        <v>1073</v>
+      </c>
+      <c r="M324" s="24" t="s">
+        <v>1085</v>
       </c>
     </row>
   </sheetData>
@@ -30273,7 +30617,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E795EE60-EBCD-4B19-B884-654D5F927670}">
-  <dimension ref="A1:S316"/>
+  <dimension ref="A1:S320"/>
   <sheetFormatPr defaultColWidth="16.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -40628,6 +40972,146 @@
       </c>
       <c r="M316" s="24" t="s">
         <v>1057</v>
+      </c>
+    </row>
+    <row r="317" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A317" s="22" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B317" s="22" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C317" s="23" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D317" s="22" t="s">
+        <v>479</v>
+      </c>
+      <c r="E317" s="22" t="s">
+        <v>483</v>
+      </c>
+      <c r="F317" s="22" t="s">
+        <v>481</v>
+      </c>
+      <c r="G317" s="22" t="s">
+        <v>484</v>
+      </c>
+      <c r="H317" s="22">
+        <v>20</v>
+      </c>
+      <c r="I317" s="22"/>
+      <c r="J317" s="22"/>
+      <c r="K317" s="15"/>
+      <c r="L317" s="23" t="s">
+        <v>1080</v>
+      </c>
+      <c r="M317" s="24" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="318" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A318" s="22" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B318" s="22" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C318" s="23" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D318" s="22" t="s">
+        <v>479</v>
+      </c>
+      <c r="E318" s="22" t="s">
+        <v>880</v>
+      </c>
+      <c r="F318" s="22" t="s">
+        <v>481</v>
+      </c>
+      <c r="G318" s="22" t="s">
+        <v>482</v>
+      </c>
+      <c r="H318" s="22">
+        <v>30</v>
+      </c>
+      <c r="I318" s="22"/>
+      <c r="J318" s="22"/>
+      <c r="K318" s="15"/>
+      <c r="L318" s="23" t="s">
+        <v>1080</v>
+      </c>
+      <c r="M318" s="24" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="319" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A319" s="22" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B319" s="22" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C319" s="23" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D319" s="22" t="s">
+        <v>479</v>
+      </c>
+      <c r="E319" s="22" t="s">
+        <v>480</v>
+      </c>
+      <c r="F319" s="22" t="s">
+        <v>481</v>
+      </c>
+      <c r="G319" s="22" t="s">
+        <v>482</v>
+      </c>
+      <c r="H319" s="22">
+        <v>40</v>
+      </c>
+      <c r="I319" s="22"/>
+      <c r="J319" s="22"/>
+      <c r="K319" s="15"/>
+      <c r="L319" s="23" t="s">
+        <v>1077</v>
+      </c>
+      <c r="M319" s="24" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="320" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A320" s="22" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B320" s="22" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C320" s="23" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D320" s="22" t="s">
+        <v>479</v>
+      </c>
+      <c r="E320" s="22" t="s">
+        <v>480</v>
+      </c>
+      <c r="F320" s="22" t="s">
+        <v>481</v>
+      </c>
+      <c r="G320" s="22" t="s">
+        <v>482</v>
+      </c>
+      <c r="H320" s="22">
+        <v>40</v>
+      </c>
+      <c r="I320" s="22"/>
+      <c r="J320" s="22"/>
+      <c r="K320" s="15"/>
+      <c r="L320" s="23" t="s">
+        <v>1073</v>
+      </c>
+      <c r="M320" s="24" t="s">
+        <v>644</v>
       </c>
     </row>
   </sheetData>
@@ -40637,7 +41121,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41BB7886-C4B6-45DF-87F2-53652B8B0BB3}">
-  <dimension ref="A1:S312"/>
+  <dimension ref="A1:S318"/>
   <sheetFormatPr defaultColWidth="12.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -50861,6 +51345,216 @@
       </c>
       <c r="M312" s="24" t="s">
         <v>1060</v>
+      </c>
+    </row>
+    <row r="313" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A313" s="22" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B313" s="22" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C313" s="23" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D313" s="22" t="s">
+        <v>513</v>
+      </c>
+      <c r="E313" s="22" t="s">
+        <v>514</v>
+      </c>
+      <c r="F313" s="22" t="s">
+        <v>659</v>
+      </c>
+      <c r="G313" s="22" t="s">
+        <v>523</v>
+      </c>
+      <c r="H313" s="22">
+        <v>20</v>
+      </c>
+      <c r="I313" s="22"/>
+      <c r="J313" s="22"/>
+      <c r="K313" s="15"/>
+      <c r="L313" s="23" t="s">
+        <v>1080</v>
+      </c>
+      <c r="M313" s="24" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="314" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A314" s="22" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B314" s="22" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C314" s="23" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D314" s="22" t="s">
+        <v>513</v>
+      </c>
+      <c r="E314" s="22" t="s">
+        <v>514</v>
+      </c>
+      <c r="F314" s="22" t="s">
+        <v>659</v>
+      </c>
+      <c r="G314" s="22" t="s">
+        <v>523</v>
+      </c>
+      <c r="H314" s="22">
+        <v>20</v>
+      </c>
+      <c r="I314" s="22"/>
+      <c r="J314" s="22"/>
+      <c r="K314" s="15"/>
+      <c r="L314" s="23" t="s">
+        <v>1080</v>
+      </c>
+      <c r="M314" s="24" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="315" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A315" s="22" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B315" s="22" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C315" s="23" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D315" s="22" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E315" s="22" t="s">
+        <v>514</v>
+      </c>
+      <c r="F315" s="22" t="s">
+        <v>659</v>
+      </c>
+      <c r="G315" s="22" t="s">
+        <v>523</v>
+      </c>
+      <c r="H315" s="22">
+        <v>10</v>
+      </c>
+      <c r="I315" s="22"/>
+      <c r="J315" s="22"/>
+      <c r="K315" s="15"/>
+      <c r="L315" s="23" t="s">
+        <v>1080</v>
+      </c>
+      <c r="M315" s="24" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="316" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A316" s="22" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B316" s="22" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C316" s="23" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D316" s="22" t="s">
+        <v>513</v>
+      </c>
+      <c r="E316" s="22" t="s">
+        <v>514</v>
+      </c>
+      <c r="F316" s="22" t="s">
+        <v>518</v>
+      </c>
+      <c r="G316" s="22" t="s">
+        <v>523</v>
+      </c>
+      <c r="H316" s="22">
+        <v>30</v>
+      </c>
+      <c r="I316" s="22"/>
+      <c r="J316" s="22"/>
+      <c r="K316" s="15"/>
+      <c r="L316" s="23" t="s">
+        <v>1080</v>
+      </c>
+      <c r="M316" s="24" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="317" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A317" s="22" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B317" s="22" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C317" s="23" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D317" s="22" t="s">
+        <v>513</v>
+      </c>
+      <c r="E317" s="22" t="s">
+        <v>514</v>
+      </c>
+      <c r="F317" s="22" t="s">
+        <v>518</v>
+      </c>
+      <c r="G317" s="22" t="s">
+        <v>516</v>
+      </c>
+      <c r="H317" s="22">
+        <v>40</v>
+      </c>
+      <c r="I317" s="22"/>
+      <c r="J317" s="22"/>
+      <c r="K317" s="15"/>
+      <c r="L317" s="23" t="s">
+        <v>1077</v>
+      </c>
+      <c r="M317" s="24" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="318" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A318" s="22" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B318" s="22" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C318" s="23" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D318" s="22" t="s">
+        <v>513</v>
+      </c>
+      <c r="E318" s="22" t="s">
+        <v>514</v>
+      </c>
+      <c r="F318" s="22" t="s">
+        <v>518</v>
+      </c>
+      <c r="G318" s="22" t="s">
+        <v>516</v>
+      </c>
+      <c r="H318" s="22">
+        <v>40</v>
+      </c>
+      <c r="I318" s="22"/>
+      <c r="J318" s="22"/>
+      <c r="K318" s="15"/>
+      <c r="L318" s="23" t="s">
+        <v>1073</v>
+      </c>
+      <c r="M318" s="24" t="s">
+        <v>1092</v>
       </c>
     </row>
   </sheetData>
@@ -50870,7 +51564,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{083B2BF1-723B-4775-8297-318920D3FD0C}">
-  <dimension ref="A1:S307"/>
+  <dimension ref="A1:S312"/>
   <sheetFormatPr defaultColWidth="13.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -60921,6 +61615,181 @@
         <v>1062</v>
       </c>
     </row>
+    <row r="308" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A308" s="22" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B308" s="22" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C308" s="23" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D308" s="22" t="s">
+        <v>554</v>
+      </c>
+      <c r="E308" s="22" t="s">
+        <v>903</v>
+      </c>
+      <c r="F308" s="22" t="s">
+        <v>548</v>
+      </c>
+      <c r="G308" s="22" t="s">
+        <v>553</v>
+      </c>
+      <c r="H308" s="22">
+        <v>20</v>
+      </c>
+      <c r="I308" s="22"/>
+      <c r="J308" s="22"/>
+      <c r="K308" s="15"/>
+      <c r="L308" s="23" t="s">
+        <v>1080</v>
+      </c>
+      <c r="M308" s="24" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="309" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A309" s="22" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B309" s="22" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C309" s="23" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D309" s="22" t="s">
+        <v>554</v>
+      </c>
+      <c r="E309" s="22" t="s">
+        <v>903</v>
+      </c>
+      <c r="F309" s="22" t="s">
+        <v>548</v>
+      </c>
+      <c r="G309" s="22" t="s">
+        <v>553</v>
+      </c>
+      <c r="H309" s="22">
+        <v>20</v>
+      </c>
+      <c r="I309" s="22"/>
+      <c r="J309" s="22"/>
+      <c r="K309" s="15"/>
+      <c r="L309" s="23" t="s">
+        <v>1080</v>
+      </c>
+      <c r="M309" s="24" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="310" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A310" s="22" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B310" s="22" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C310" s="23" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D310" s="22" t="s">
+        <v>554</v>
+      </c>
+      <c r="E310" s="22" t="s">
+        <v>903</v>
+      </c>
+      <c r="F310" s="22" t="s">
+        <v>548</v>
+      </c>
+      <c r="G310" s="22" t="s">
+        <v>553</v>
+      </c>
+      <c r="H310" s="22">
+        <v>20</v>
+      </c>
+      <c r="I310" s="22"/>
+      <c r="J310" s="22"/>
+      <c r="K310" s="15"/>
+      <c r="L310" s="23" t="s">
+        <v>1080</v>
+      </c>
+      <c r="M310" s="24" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="311" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A311" s="22" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B311" s="22" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C311" s="23" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D311" s="22" t="s">
+        <v>550</v>
+      </c>
+      <c r="E311" s="22" t="s">
+        <v>551</v>
+      </c>
+      <c r="F311" s="22" t="s">
+        <v>548</v>
+      </c>
+      <c r="G311" s="22" t="s">
+        <v>553</v>
+      </c>
+      <c r="H311" s="22">
+        <v>40</v>
+      </c>
+      <c r="I311" s="22"/>
+      <c r="J311" s="22"/>
+      <c r="K311" s="15"/>
+      <c r="L311" s="23" t="s">
+        <v>1077</v>
+      </c>
+      <c r="M311" s="24" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="312" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A312" s="22" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B312" s="22" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C312" s="23" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D312" s="22" t="s">
+        <v>554</v>
+      </c>
+      <c r="E312" s="22" t="s">
+        <v>551</v>
+      </c>
+      <c r="F312" s="22" t="s">
+        <v>548</v>
+      </c>
+      <c r="G312" s="22" t="s">
+        <v>553</v>
+      </c>
+      <c r="H312" s="22">
+        <v>30</v>
+      </c>
+      <c r="I312" s="22"/>
+      <c r="J312" s="22"/>
+      <c r="K312" s="15"/>
+      <c r="L312" s="23" t="s">
+        <v>1073</v>
+      </c>
+      <c r="M312" s="24" t="s">
+        <v>1093</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/data/Integracao Armazem.xlsx
+++ b/data/Integracao Armazem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\novo_portal_rh\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9D201B0-9434-4221-98BB-7A6FFAC9288A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE5EFE21-611F-4DCE-BD8D-57D65B534C5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{422D47E6-8DC3-4B25-BD50-E675C15B05CB}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="4" xr2:uid="{422D47E6-8DC3-4B25-BD50-E675C15B05CB}"/>
   </bookViews>
   <sheets>
     <sheet name="M1" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12191" uniqueCount="1137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12674" uniqueCount="1225">
   <si>
     <t>Selecione o EPI que NÃO é obrigatório durante o processo de montagem de paletes</t>
   </si>
@@ -3577,6 +3577,270 @@
   </si>
   <si>
     <t>550.245.598-00</t>
+  </si>
+  <si>
+    <t>Alexander Rafael olimpio aviles</t>
+  </si>
+  <si>
+    <t>01765986220</t>
+  </si>
+  <si>
+    <t>27/07/2026</t>
+  </si>
+  <si>
+    <t>20:41</t>
+  </si>
+  <si>
+    <t>Adrian Mateus</t>
+  </si>
+  <si>
+    <t>11843999994</t>
+  </si>
+  <si>
+    <t>28/07/2026</t>
+  </si>
+  <si>
+    <t>15:38</t>
+  </si>
+  <si>
+    <t>Uelinton Gonçalves Siqueira</t>
+  </si>
+  <si>
+    <t>42931968898</t>
+  </si>
+  <si>
+    <t>30/07/2026</t>
+  </si>
+  <si>
+    <t>16:26</t>
+  </si>
+  <si>
+    <t>20:44</t>
+  </si>
+  <si>
+    <t>Matheus Rodrigues</t>
+  </si>
+  <si>
+    <t>SANDRO BATISTA FERREIRA</t>
+  </si>
+  <si>
+    <t>09137788507</t>
+  </si>
+  <si>
+    <t>24/09/2007</t>
+  </si>
+  <si>
+    <t>29/07/2026</t>
+  </si>
+  <si>
+    <t>09:01</t>
+  </si>
+  <si>
+    <t>14/01/2002</t>
+  </si>
+  <si>
+    <t>08:59</t>
+  </si>
+  <si>
+    <t>RAFAEL SEVERINO SANTOS DE LIMA</t>
+  </si>
+  <si>
+    <t>05187128507</t>
+  </si>
+  <si>
+    <t>25/10/1991</t>
+  </si>
+  <si>
+    <t>08:58</t>
+  </si>
+  <si>
+    <t>PAULO ROBERTO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>02947431545</t>
+  </si>
+  <si>
+    <t>22/07/1988</t>
+  </si>
+  <si>
+    <t>08:57</t>
+  </si>
+  <si>
+    <t>LUIS VINICIUS BOMFIM OLIVEIRA</t>
+  </si>
+  <si>
+    <t>09316789516</t>
+  </si>
+  <si>
+    <t>03/07/2002</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>FRANCISCO WALISSON SANTOS DE SOUSA</t>
+  </si>
+  <si>
+    <t>86456667585</t>
+  </si>
+  <si>
+    <t>15/06/1994</t>
+  </si>
+  <si>
+    <t>08:51</t>
+  </si>
+  <si>
+    <t>KAUA ALMEIDA SANTOS</t>
+  </si>
+  <si>
+    <t>30/01/2004</t>
+  </si>
+  <si>
+    <t>08:50</t>
+  </si>
+  <si>
+    <t>FELIPE COSME SOUZA FLORENCIO</t>
+  </si>
+  <si>
+    <t>09144606508</t>
+  </si>
+  <si>
+    <t>07/05/2007</t>
+  </si>
+  <si>
+    <t>08:38</t>
+  </si>
+  <si>
+    <t>DAVI BEZERRA VIEIRA</t>
+  </si>
+  <si>
+    <t>09144893566</t>
+  </si>
+  <si>
+    <t>10/10/2006</t>
+  </si>
+  <si>
+    <t>08:34</t>
+  </si>
+  <si>
+    <t>42931968897</t>
+  </si>
+  <si>
+    <t>20:46</t>
+  </si>
+  <si>
+    <t>16:04</t>
+  </si>
+  <si>
+    <t>14/01/2001</t>
+  </si>
+  <si>
+    <t>09:37</t>
+  </si>
+  <si>
+    <t>09:34</t>
+  </si>
+  <si>
+    <t>22/07/1998</t>
+  </si>
+  <si>
+    <t>09:33</t>
+  </si>
+  <si>
+    <t>03/09/2007</t>
+  </si>
+  <si>
+    <t>09:29</t>
+  </si>
+  <si>
+    <t>09:28</t>
+  </si>
+  <si>
+    <t>09:25</t>
+  </si>
+  <si>
+    <t>17/05/2007</t>
+  </si>
+  <si>
+    <t>09:21</t>
+  </si>
+  <si>
+    <t>09:11</t>
+  </si>
+  <si>
+    <t>09:09</t>
+  </si>
+  <si>
+    <t>16:50</t>
+  </si>
+  <si>
+    <t>20:49</t>
+  </si>
+  <si>
+    <t>10:18</t>
+  </si>
+  <si>
+    <t>10:08</t>
+  </si>
+  <si>
+    <t>10:07</t>
+  </si>
+  <si>
+    <t>27/07/1998</t>
+  </si>
+  <si>
+    <t>10:04</t>
+  </si>
+  <si>
+    <t>03/07/2007</t>
+  </si>
+  <si>
+    <t>10:02</t>
+  </si>
+  <si>
+    <t>30/01/2001</t>
+  </si>
+  <si>
+    <t>09:58</t>
+  </si>
+  <si>
+    <t>09:45</t>
+  </si>
+  <si>
+    <t>17/03/2007</t>
+  </si>
+  <si>
+    <t>09:42</t>
+  </si>
+  <si>
+    <t>10/11/2006</t>
+  </si>
+  <si>
+    <t>09:40</t>
+  </si>
+  <si>
+    <t>20:51</t>
+  </si>
+  <si>
+    <t>16:27</t>
+  </si>
+  <si>
+    <t>09/09/2007</t>
+  </si>
+  <si>
+    <t>24/10/1991</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>10:25</t>
+  </si>
+  <si>
+    <t>10:22</t>
+  </si>
+  <si>
+    <t>10:20</t>
   </si>
 </sst>
 </file>
@@ -3625,7 +3889,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3696,7 +3960,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4020,7 +4283,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D8EC4C0-DEF5-4A13-83D8-46C06041A7DF}">
-  <dimension ref="A1:S352"/>
+  <dimension ref="A1:S355"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="44.88671875" bestFit="1" customWidth="1"/>
@@ -20853,6 +21116,156 @@
         <v>1132</v>
       </c>
     </row>
+    <row r="353" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A353" s="28" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B353" s="28" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C353" s="29" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D353" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E353" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="F353" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="G353" s="28" t="s">
+        <v>356</v>
+      </c>
+      <c r="H353" s="28" t="s">
+        <v>357</v>
+      </c>
+      <c r="I353" s="28" t="s">
+        <v>358</v>
+      </c>
+      <c r="J353" s="28" t="s">
+        <v>359</v>
+      </c>
+      <c r="K353" s="28" t="s">
+        <v>360</v>
+      </c>
+      <c r="L353" s="28" t="s">
+        <v>366</v>
+      </c>
+      <c r="M353" s="28">
+        <v>90</v>
+      </c>
+      <c r="N353" s="28"/>
+      <c r="O353" s="28"/>
+      <c r="P353" s="15"/>
+      <c r="Q353" s="29" t="s">
+        <v>1139</v>
+      </c>
+      <c r="R353" s="30" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="354" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A354" s="28" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B354" s="28" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C354" s="29" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D354" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E354" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="F354" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="G354" s="28" t="s">
+        <v>682</v>
+      </c>
+      <c r="H354" s="28" t="s">
+        <v>357</v>
+      </c>
+      <c r="I354" s="28" t="s">
+        <v>358</v>
+      </c>
+      <c r="J354" s="28" t="s">
+        <v>359</v>
+      </c>
+      <c r="K354" s="28" t="s">
+        <v>365</v>
+      </c>
+      <c r="L354" s="28" t="s">
+        <v>366</v>
+      </c>
+      <c r="M354" s="28">
+        <v>70</v>
+      </c>
+      <c r="N354" s="28"/>
+      <c r="O354" s="28"/>
+      <c r="P354" s="15"/>
+      <c r="Q354" s="29" t="s">
+        <v>1143</v>
+      </c>
+      <c r="R354" s="30" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="355" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A355" s="28" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B355" s="28" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C355" s="29" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D355" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E355" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="F355" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="G355" s="28" t="s">
+        <v>356</v>
+      </c>
+      <c r="H355" s="28" t="s">
+        <v>357</v>
+      </c>
+      <c r="I355" s="28" t="s">
+        <v>358</v>
+      </c>
+      <c r="J355" s="28" t="s">
+        <v>359</v>
+      </c>
+      <c r="K355" s="28" t="s">
+        <v>365</v>
+      </c>
+      <c r="L355" s="28" t="s">
+        <v>366</v>
+      </c>
+      <c r="M355" s="28">
+        <v>80</v>
+      </c>
+      <c r="N355" s="28"/>
+      <c r="O355" s="28"/>
+      <c r="P355" s="15"/>
+      <c r="Q355" s="29" t="s">
+        <v>1147</v>
+      </c>
+      <c r="R355" s="30" t="s">
+        <v>1148</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:S341" xr:uid="{9D8EC4C0-DEF5-4A13-83D8-46C06041A7DF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -20862,7 +21275,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9848E97-FB23-44B1-9CE3-C616F78A0A8B}">
-  <dimension ref="A1:S333"/>
+  <dimension ref="A1:S345"/>
   <sheetFormatPr defaultColWidth="15.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="44.88671875" bestFit="1" customWidth="1"/>
@@ -31788,6 +32201,426 @@
         <v>1100</v>
       </c>
     </row>
+    <row r="334" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A334" s="28" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B334" s="28" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C334" s="29" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D334" s="28" t="s">
+        <v>404</v>
+      </c>
+      <c r="E334" s="28" t="s">
+        <v>612</v>
+      </c>
+      <c r="F334" s="28" t="s">
+        <v>434</v>
+      </c>
+      <c r="G334" s="28" t="s">
+        <v>441</v>
+      </c>
+      <c r="H334" s="28">
+        <v>20</v>
+      </c>
+      <c r="I334" s="28"/>
+      <c r="J334" s="28"/>
+      <c r="K334" s="15"/>
+      <c r="L334" s="29" t="s">
+        <v>1139</v>
+      </c>
+      <c r="M334" s="30" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="335" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A335" s="28" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B335" s="28" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C335" s="29" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D335" s="28" t="s">
+        <v>404</v>
+      </c>
+      <c r="E335" s="28" t="s">
+        <v>612</v>
+      </c>
+      <c r="F335" s="28" t="s">
+        <v>434</v>
+      </c>
+      <c r="G335" s="28" t="s">
+        <v>441</v>
+      </c>
+      <c r="H335" s="28">
+        <v>20</v>
+      </c>
+      <c r="I335" s="28"/>
+      <c r="J335" s="28"/>
+      <c r="K335" s="15"/>
+      <c r="L335" s="29" t="s">
+        <v>1143</v>
+      </c>
+      <c r="M335" s="30" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="336" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A336" s="28" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B336" s="28" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C336" s="29" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D336" s="28" t="s">
+        <v>404</v>
+      </c>
+      <c r="E336" s="28" t="s">
+        <v>437</v>
+      </c>
+      <c r="F336" s="28" t="s">
+        <v>434</v>
+      </c>
+      <c r="G336" s="28" t="s">
+        <v>435</v>
+      </c>
+      <c r="H336" s="28">
+        <v>40</v>
+      </c>
+      <c r="I336" s="28"/>
+      <c r="J336" s="28"/>
+      <c r="K336" s="15"/>
+      <c r="L336" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M336" s="30" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="337" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A337" s="28" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B337" s="28" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C337" s="29" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D337" s="28" t="s">
+        <v>404</v>
+      </c>
+      <c r="E337" s="28" t="s">
+        <v>437</v>
+      </c>
+      <c r="F337" s="28" t="s">
+        <v>434</v>
+      </c>
+      <c r="G337" s="28" t="s">
+        <v>435</v>
+      </c>
+      <c r="H337" s="28">
+        <v>40</v>
+      </c>
+      <c r="I337" s="28"/>
+      <c r="J337" s="28"/>
+      <c r="K337" s="15"/>
+      <c r="L337" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M337" s="30" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="338" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A338" s="28" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B338" s="28" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C338" s="29" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D338" s="28" t="s">
+        <v>404</v>
+      </c>
+      <c r="E338" s="28" t="s">
+        <v>437</v>
+      </c>
+      <c r="F338" s="28" t="s">
+        <v>434</v>
+      </c>
+      <c r="G338" s="28" t="s">
+        <v>435</v>
+      </c>
+      <c r="H338" s="28">
+        <v>40</v>
+      </c>
+      <c r="I338" s="28"/>
+      <c r="J338" s="28"/>
+      <c r="K338" s="15"/>
+      <c r="L338" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M338" s="30" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="339" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A339" s="28" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B339" s="28" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C339" s="29" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D339" s="28" t="s">
+        <v>404</v>
+      </c>
+      <c r="E339" s="28" t="s">
+        <v>437</v>
+      </c>
+      <c r="F339" s="28" t="s">
+        <v>434</v>
+      </c>
+      <c r="G339" s="28" t="s">
+        <v>435</v>
+      </c>
+      <c r="H339" s="28">
+        <v>40</v>
+      </c>
+      <c r="I339" s="28"/>
+      <c r="J339" s="28"/>
+      <c r="K339" s="15"/>
+      <c r="L339" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M339" s="30" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="340" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A340" s="28" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B340" s="28" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C340" s="29" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D340" s="28" t="s">
+        <v>404</v>
+      </c>
+      <c r="E340" s="28" t="s">
+        <v>437</v>
+      </c>
+      <c r="F340" s="28" t="s">
+        <v>434</v>
+      </c>
+      <c r="G340" s="28" t="s">
+        <v>435</v>
+      </c>
+      <c r="H340" s="28">
+        <v>40</v>
+      </c>
+      <c r="I340" s="28"/>
+      <c r="J340" s="28"/>
+      <c r="K340" s="15"/>
+      <c r="L340" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M340" s="30" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="341" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A341" s="28" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B341" s="28" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C341" s="29" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D341" s="28" t="s">
+        <v>404</v>
+      </c>
+      <c r="E341" s="28" t="s">
+        <v>437</v>
+      </c>
+      <c r="F341" s="28" t="s">
+        <v>434</v>
+      </c>
+      <c r="G341" s="28" t="s">
+        <v>435</v>
+      </c>
+      <c r="H341" s="28">
+        <v>40</v>
+      </c>
+      <c r="I341" s="28"/>
+      <c r="J341" s="28"/>
+      <c r="K341" s="15"/>
+      <c r="L341" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M341" s="30" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="342" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A342" s="28" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B342" s="28" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C342" s="29" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D342" s="28" t="s">
+        <v>404</v>
+      </c>
+      <c r="E342" s="28" t="s">
+        <v>437</v>
+      </c>
+      <c r="F342" s="28" t="s">
+        <v>434</v>
+      </c>
+      <c r="G342" s="28" t="s">
+        <v>435</v>
+      </c>
+      <c r="H342" s="28">
+        <v>40</v>
+      </c>
+      <c r="I342" s="28"/>
+      <c r="J342" s="28"/>
+      <c r="K342" s="15"/>
+      <c r="L342" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M342" s="30" t="s">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="343" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A343" s="28" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B343" s="28" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C343" s="29" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D343" s="28" t="s">
+        <v>404</v>
+      </c>
+      <c r="E343" s="28" t="s">
+        <v>437</v>
+      </c>
+      <c r="F343" s="28" t="s">
+        <v>434</v>
+      </c>
+      <c r="G343" s="28" t="s">
+        <v>435</v>
+      </c>
+      <c r="H343" s="28">
+        <v>40</v>
+      </c>
+      <c r="I343" s="28"/>
+      <c r="J343" s="28"/>
+      <c r="K343" s="15"/>
+      <c r="L343" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M343" s="30" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="344" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A344" s="28" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B344" s="28" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C344" s="29" t="s">
+        <v>1183</v>
+      </c>
+      <c r="D344" s="28" t="s">
+        <v>404</v>
+      </c>
+      <c r="E344" s="28" t="s">
+        <v>437</v>
+      </c>
+      <c r="F344" s="28" t="s">
+        <v>434</v>
+      </c>
+      <c r="G344" s="28" t="s">
+        <v>435</v>
+      </c>
+      <c r="H344" s="28">
+        <v>40</v>
+      </c>
+      <c r="I344" s="28"/>
+      <c r="J344" s="28"/>
+      <c r="K344" s="15"/>
+      <c r="L344" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M344" s="30" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="345" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A345" s="28" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B345" s="28" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C345" s="29" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D345" s="28" t="s">
+        <v>404</v>
+      </c>
+      <c r="E345" s="28" t="s">
+        <v>437</v>
+      </c>
+      <c r="F345" s="28" t="s">
+        <v>434</v>
+      </c>
+      <c r="G345" s="28" t="s">
+        <v>441</v>
+      </c>
+      <c r="H345" s="28">
+        <v>30</v>
+      </c>
+      <c r="I345" s="28"/>
+      <c r="J345" s="28"/>
+      <c r="K345" s="15"/>
+      <c r="L345" s="29" t="s">
+        <v>1147</v>
+      </c>
+      <c r="M345" s="30" t="s">
+        <v>881</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N328" xr:uid="{E9848E97-FB23-44B1-9CE3-C616F78A0A8B}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -31796,7 +32629,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E795EE60-EBCD-4B19-B884-654D5F927670}">
-  <dimension ref="A1:S331"/>
+  <dimension ref="A1:S343"/>
   <sheetFormatPr defaultColWidth="16.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="44.88671875" bestFit="1" customWidth="1"/>
@@ -42654,6 +43487,426 @@
         <v>738</v>
       </c>
     </row>
+    <row r="332" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A332" s="28" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B332" s="28" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C332" s="29" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D332" s="28" t="s">
+        <v>478</v>
+      </c>
+      <c r="E332" s="28" t="s">
+        <v>486</v>
+      </c>
+      <c r="F332" s="28" t="s">
+        <v>480</v>
+      </c>
+      <c r="G332" s="28" t="s">
+        <v>483</v>
+      </c>
+      <c r="H332" s="28">
+        <v>20</v>
+      </c>
+      <c r="I332" s="28"/>
+      <c r="J332" s="28"/>
+      <c r="K332" s="15"/>
+      <c r="L332" s="29" t="s">
+        <v>1139</v>
+      </c>
+      <c r="M332" s="30" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="333" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A333" s="28" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B333" s="28" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C333" s="29" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D333" s="28" t="s">
+        <v>883</v>
+      </c>
+      <c r="E333" s="28" t="s">
+        <v>479</v>
+      </c>
+      <c r="F333" s="28" t="s">
+        <v>480</v>
+      </c>
+      <c r="G333" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="H333" s="28">
+        <v>30</v>
+      </c>
+      <c r="I333" s="28"/>
+      <c r="J333" s="28"/>
+      <c r="K333" s="15"/>
+      <c r="L333" s="29" t="s">
+        <v>1143</v>
+      </c>
+      <c r="M333" s="30" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="334" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A334" s="28" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B334" s="28" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C334" s="29" t="s">
+        <v>1188</v>
+      </c>
+      <c r="D334" s="28" t="s">
+        <v>883</v>
+      </c>
+      <c r="E334" s="28" t="s">
+        <v>479</v>
+      </c>
+      <c r="F334" s="28" t="s">
+        <v>480</v>
+      </c>
+      <c r="G334" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="H334" s="28">
+        <v>30</v>
+      </c>
+      <c r="I334" s="28"/>
+      <c r="J334" s="28"/>
+      <c r="K334" s="15"/>
+      <c r="L334" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M334" s="30" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="335" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A335" s="28" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B335" s="28" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C335" s="29" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D335" s="28" t="s">
+        <v>883</v>
+      </c>
+      <c r="E335" s="28" t="s">
+        <v>479</v>
+      </c>
+      <c r="F335" s="28" t="s">
+        <v>480</v>
+      </c>
+      <c r="G335" s="28" t="s">
+        <v>483</v>
+      </c>
+      <c r="H335" s="28">
+        <v>20</v>
+      </c>
+      <c r="I335" s="28"/>
+      <c r="J335" s="28"/>
+      <c r="K335" s="15"/>
+      <c r="L335" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M335" s="30" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="336" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A336" s="28" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B336" s="28" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C336" s="29" t="s">
+        <v>1191</v>
+      </c>
+      <c r="D336" s="28" t="s">
+        <v>883</v>
+      </c>
+      <c r="E336" s="28" t="s">
+        <v>479</v>
+      </c>
+      <c r="F336" s="28" t="s">
+        <v>480</v>
+      </c>
+      <c r="G336" s="28" t="s">
+        <v>483</v>
+      </c>
+      <c r="H336" s="28">
+        <v>20</v>
+      </c>
+      <c r="I336" s="28"/>
+      <c r="J336" s="28"/>
+      <c r="K336" s="15"/>
+      <c r="L336" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M336" s="30" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="337" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A337" s="28" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B337" s="28" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C337" s="29" t="s">
+        <v>1193</v>
+      </c>
+      <c r="D337" s="28" t="s">
+        <v>883</v>
+      </c>
+      <c r="E337" s="28" t="s">
+        <v>479</v>
+      </c>
+      <c r="F337" s="28" t="s">
+        <v>480</v>
+      </c>
+      <c r="G337" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="H337" s="28">
+        <v>30</v>
+      </c>
+      <c r="I337" s="28"/>
+      <c r="J337" s="28"/>
+      <c r="K337" s="15"/>
+      <c r="L337" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M337" s="30" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="338" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A338" s="28" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B338" s="28" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C338" s="29" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D338" s="28" t="s">
+        <v>883</v>
+      </c>
+      <c r="E338" s="28" t="s">
+        <v>479</v>
+      </c>
+      <c r="F338" s="28" t="s">
+        <v>480</v>
+      </c>
+      <c r="G338" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="H338" s="28">
+        <v>30</v>
+      </c>
+      <c r="I338" s="28"/>
+      <c r="J338" s="28"/>
+      <c r="K338" s="15"/>
+      <c r="L338" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M338" s="30" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="339" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A339" s="28" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B339" s="28" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C339" s="29" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D339" s="28" t="s">
+        <v>883</v>
+      </c>
+      <c r="E339" s="28" t="s">
+        <v>479</v>
+      </c>
+      <c r="F339" s="28" t="s">
+        <v>480</v>
+      </c>
+      <c r="G339" s="28" t="s">
+        <v>483</v>
+      </c>
+      <c r="H339" s="28">
+        <v>20</v>
+      </c>
+      <c r="I339" s="28"/>
+      <c r="J339" s="28"/>
+      <c r="K339" s="15"/>
+      <c r="L339" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M339" s="30" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="340" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A340" s="28" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B340" s="28" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C340" s="29" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D340" s="28" t="s">
+        <v>883</v>
+      </c>
+      <c r="E340" s="28" t="s">
+        <v>479</v>
+      </c>
+      <c r="F340" s="28" t="s">
+        <v>480</v>
+      </c>
+      <c r="G340" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="H340" s="28">
+        <v>30</v>
+      </c>
+      <c r="I340" s="28"/>
+      <c r="J340" s="28"/>
+      <c r="K340" s="15"/>
+      <c r="L340" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M340" s="30" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="341" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A341" s="28" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B341" s="28" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C341" s="29" t="s">
+        <v>1183</v>
+      </c>
+      <c r="D341" s="28" t="s">
+        <v>883</v>
+      </c>
+      <c r="E341" s="28" t="s">
+        <v>486</v>
+      </c>
+      <c r="F341" s="28" t="s">
+        <v>480</v>
+      </c>
+      <c r="G341" s="28" t="s">
+        <v>780</v>
+      </c>
+      <c r="H341" s="28">
+        <v>10</v>
+      </c>
+      <c r="I341" s="28"/>
+      <c r="J341" s="28"/>
+      <c r="K341" s="15"/>
+      <c r="L341" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M341" s="30" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="342" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A342" s="28" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B342" s="28" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C342" s="29" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D342" s="28" t="s">
+        <v>883</v>
+      </c>
+      <c r="E342" s="28" t="s">
+        <v>482</v>
+      </c>
+      <c r="F342" s="28" t="s">
+        <v>480</v>
+      </c>
+      <c r="G342" s="28" t="s">
+        <v>780</v>
+      </c>
+      <c r="H342" s="28">
+        <v>10</v>
+      </c>
+      <c r="I342" s="28"/>
+      <c r="J342" s="28"/>
+      <c r="K342" s="15"/>
+      <c r="L342" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M342" s="30" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="343" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A343" s="28" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B343" s="28" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C343" s="29" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D343" s="28" t="s">
+        <v>478</v>
+      </c>
+      <c r="E343" s="28" t="s">
+        <v>479</v>
+      </c>
+      <c r="F343" s="28" t="s">
+        <v>480</v>
+      </c>
+      <c r="G343" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="H343" s="28">
+        <v>40</v>
+      </c>
+      <c r="I343" s="28"/>
+      <c r="J343" s="28"/>
+      <c r="K343" s="15"/>
+      <c r="L343" s="29" t="s">
+        <v>1147</v>
+      </c>
+      <c r="M343" s="30" t="s">
+        <v>1201</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N325" xr:uid="{E795EE60-EBCD-4B19-B884-654D5F927670}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -42662,7 +43915,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41BB7886-C4B6-45DF-87F2-53652B8B0BB3}">
-  <dimension ref="A1:S330"/>
+  <dimension ref="A1:S343"/>
   <sheetFormatPr defaultColWidth="12.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="44.88671875" bestFit="1" customWidth="1"/>
@@ -53488,6 +54741,461 @@
         <v>1107</v>
       </c>
     </row>
+    <row r="331" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A331" s="28" t="s">
+        <v>839</v>
+      </c>
+      <c r="B331" s="28" t="s">
+        <v>873</v>
+      </c>
+      <c r="C331" s="29" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D331" s="28" t="s">
+        <v>518</v>
+      </c>
+      <c r="E331" s="28" t="s">
+        <v>523</v>
+      </c>
+      <c r="F331" s="28" t="s">
+        <v>658</v>
+      </c>
+      <c r="G331" s="28" t="s">
+        <v>522</v>
+      </c>
+      <c r="H331" s="28">
+        <v>0</v>
+      </c>
+      <c r="I331" s="28"/>
+      <c r="J331" s="28"/>
+      <c r="K331" s="15"/>
+      <c r="L331" s="29" t="s">
+        <v>1111</v>
+      </c>
+      <c r="M331" s="30" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="332" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A332" s="28" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B332" s="28" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C332" s="29" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D332" s="28" t="s">
+        <v>512</v>
+      </c>
+      <c r="E332" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="F332" s="28" t="s">
+        <v>517</v>
+      </c>
+      <c r="G332" s="28" t="s">
+        <v>515</v>
+      </c>
+      <c r="H332" s="28">
+        <v>40</v>
+      </c>
+      <c r="I332" s="28"/>
+      <c r="J332" s="28"/>
+      <c r="K332" s="15"/>
+      <c r="L332" s="29" t="s">
+        <v>1139</v>
+      </c>
+      <c r="M332" s="30" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="333" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A333" s="28" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B333" s="28" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C333" s="29" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D333" s="28" t="s">
+        <v>512</v>
+      </c>
+      <c r="E333" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="F333" s="28" t="s">
+        <v>517</v>
+      </c>
+      <c r="G333" s="28" t="s">
+        <v>522</v>
+      </c>
+      <c r="H333" s="28">
+        <v>30</v>
+      </c>
+      <c r="I333" s="28"/>
+      <c r="J333" s="28"/>
+      <c r="K333" s="15"/>
+      <c r="L333" s="29" t="s">
+        <v>1143</v>
+      </c>
+      <c r="M333" s="30" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="334" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A334" s="28" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B334" s="28" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C334" s="29" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D334" s="28" t="s">
+        <v>1105</v>
+      </c>
+      <c r="E334" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="F334" s="28" t="s">
+        <v>517</v>
+      </c>
+      <c r="G334" s="28" t="s">
+        <v>515</v>
+      </c>
+      <c r="H334" s="28">
+        <v>30</v>
+      </c>
+      <c r="I334" s="28"/>
+      <c r="J334" s="28"/>
+      <c r="K334" s="15"/>
+      <c r="L334" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M334" s="30" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="335" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A335" s="28" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B335" s="28" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C335" s="29" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D335" s="28" t="s">
+        <v>1105</v>
+      </c>
+      <c r="E335" s="28" t="s">
+        <v>516</v>
+      </c>
+      <c r="F335" s="28" t="s">
+        <v>517</v>
+      </c>
+      <c r="G335" s="28" t="s">
+        <v>660</v>
+      </c>
+      <c r="H335" s="28">
+        <v>10</v>
+      </c>
+      <c r="I335" s="28"/>
+      <c r="J335" s="28"/>
+      <c r="K335" s="15"/>
+      <c r="L335" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M335" s="30" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="336" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A336" s="28" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B336" s="28" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C336" s="29" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D336" s="28" t="s">
+        <v>1105</v>
+      </c>
+      <c r="E336" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="F336" s="28" t="s">
+        <v>517</v>
+      </c>
+      <c r="G336" s="28" t="s">
+        <v>515</v>
+      </c>
+      <c r="H336" s="28">
+        <v>30</v>
+      </c>
+      <c r="I336" s="28"/>
+      <c r="J336" s="28"/>
+      <c r="K336" s="15"/>
+      <c r="L336" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M336" s="30" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="337" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A337" s="28" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B337" s="28" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C337" s="29" t="s">
+        <v>1206</v>
+      </c>
+      <c r="D337" s="28" t="s">
+        <v>1105</v>
+      </c>
+      <c r="E337" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="F337" s="28" t="s">
+        <v>517</v>
+      </c>
+      <c r="G337" s="28" t="s">
+        <v>515</v>
+      </c>
+      <c r="H337" s="28">
+        <v>30</v>
+      </c>
+      <c r="I337" s="28"/>
+      <c r="J337" s="28"/>
+      <c r="K337" s="15"/>
+      <c r="L337" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M337" s="30" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="338" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A338" s="28" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B338" s="28" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C338" s="29" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D338" s="28" t="s">
+        <v>1105</v>
+      </c>
+      <c r="E338" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="F338" s="28" t="s">
+        <v>517</v>
+      </c>
+      <c r="G338" s="28" t="s">
+        <v>515</v>
+      </c>
+      <c r="H338" s="28">
+        <v>30</v>
+      </c>
+      <c r="I338" s="28"/>
+      <c r="J338" s="28"/>
+      <c r="K338" s="15"/>
+      <c r="L338" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M338" s="30" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="339" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A339" s="28" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B339" s="28" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C339" s="29" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D339" s="28" t="s">
+        <v>1105</v>
+      </c>
+      <c r="E339" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="F339" s="28" t="s">
+        <v>517</v>
+      </c>
+      <c r="G339" s="28" t="s">
+        <v>515</v>
+      </c>
+      <c r="H339" s="28">
+        <v>30</v>
+      </c>
+      <c r="I339" s="28"/>
+      <c r="J339" s="28"/>
+      <c r="K339" s="15"/>
+      <c r="L339" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M339" s="30" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="340" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A340" s="28" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B340" s="28" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C340" s="29" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D340" s="28" t="s">
+        <v>512</v>
+      </c>
+      <c r="E340" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="F340" s="28" t="s">
+        <v>517</v>
+      </c>
+      <c r="G340" s="28" t="s">
+        <v>522</v>
+      </c>
+      <c r="H340" s="28">
+        <v>30</v>
+      </c>
+      <c r="I340" s="28"/>
+      <c r="J340" s="28"/>
+      <c r="K340" s="15"/>
+      <c r="L340" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M340" s="30" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="341" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A341" s="28" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B341" s="28" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C341" s="29" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D341" s="28" t="s">
+        <v>1105</v>
+      </c>
+      <c r="E341" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="F341" s="28" t="s">
+        <v>517</v>
+      </c>
+      <c r="G341" s="28" t="s">
+        <v>515</v>
+      </c>
+      <c r="H341" s="28">
+        <v>30</v>
+      </c>
+      <c r="I341" s="28"/>
+      <c r="J341" s="28"/>
+      <c r="K341" s="15"/>
+      <c r="L341" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M341" s="30" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="342" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A342" s="28" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B342" s="28" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C342" s="29" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D342" s="28" t="s">
+        <v>512</v>
+      </c>
+      <c r="E342" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="F342" s="28" t="s">
+        <v>517</v>
+      </c>
+      <c r="G342" s="28" t="s">
+        <v>515</v>
+      </c>
+      <c r="H342" s="28">
+        <v>40</v>
+      </c>
+      <c r="I342" s="28"/>
+      <c r="J342" s="28"/>
+      <c r="K342" s="15"/>
+      <c r="L342" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M342" s="30" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="343" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A343" s="28" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B343" s="28" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C343" s="29" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D343" s="28" t="s">
+        <v>512</v>
+      </c>
+      <c r="E343" s="28" t="s">
+        <v>523</v>
+      </c>
+      <c r="F343" s="28" t="s">
+        <v>517</v>
+      </c>
+      <c r="G343" s="28" t="s">
+        <v>515</v>
+      </c>
+      <c r="H343" s="28">
+        <v>30</v>
+      </c>
+      <c r="I343" s="28"/>
+      <c r="J343" s="28"/>
+      <c r="K343" s="15"/>
+      <c r="L343" s="29" t="s">
+        <v>1147</v>
+      </c>
+      <c r="M343" s="30" t="s">
+        <v>980</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N330" xr:uid="{41BB7886-C4B6-45DF-87F2-53652B8B0BB3}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -53496,8 +55204,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{083B2BF1-723B-4775-8297-318920D3FD0C}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:S325"/>
+  <dimension ref="A1:S337"/>
   <sheetFormatPr defaultColWidth="13.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="44.88671875" bestFit="1" customWidth="1"/>
@@ -53553,7 +55260,7 @@
       <c r="R1" s="4"/>
       <c r="S1" s="4"/>
     </row>
-    <row r="2" spans="1:19" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -53585,7 +55292,7 @@
         <v>0.71180555555555547</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -53617,7 +55324,7 @@
         <v>0.71180555555555547</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -53649,7 +55356,7 @@
         <v>0.71180555555555547</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -53681,7 +55388,7 @@
         <v>0.8125</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>45</v>
       </c>
@@ -53713,7 +55420,7 @@
         <v>0.6875</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>46</v>
       </c>
@@ -53745,7 +55452,7 @@
         <v>0.68888888888888899</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>54</v>
       </c>
@@ -53777,7 +55484,7 @@
         <v>0.7104166666666667</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -53809,7 +55516,7 @@
         <v>0.7104166666666667</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>52</v>
       </c>
@@ -53841,7 +55548,7 @@
         <v>0.71111111111111114</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -53873,7 +55580,7 @@
         <v>0.71111111111111114</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>50</v>
       </c>
@@ -53905,7 +55612,7 @@
         <v>0.71111111111111114</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>49</v>
       </c>
@@ -53937,7 +55644,7 @@
         <v>0.71111111111111114</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>53</v>
       </c>
@@ -53969,7 +55676,7 @@
         <v>0.71180555555555547</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>59</v>
       </c>
@@ -54001,7 +55708,7 @@
         <v>0.60069444444444442</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -54033,7 +55740,7 @@
         <v>0.60138888888888886</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -54065,7 +55772,7 @@
         <v>0.60138888888888886</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -54097,7 +55804,7 @@
         <v>0.60138888888888886</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -54129,7 +55836,7 @@
         <v>0.6020833333333333</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>58</v>
       </c>
@@ -54161,7 +55868,7 @@
         <v>0.72569444444444453</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>61</v>
       </c>
@@ -54193,7 +55900,7 @@
         <v>0.45555555555555555</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>61</v>
       </c>
@@ -54225,7 +55932,7 @@
         <v>0.63888888888888895</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -54257,7 +55964,7 @@
         <v>0.42638888888888887</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>403</v>
       </c>
@@ -54289,7 +55996,7 @@
         <v>0.59861111111111109</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>405</v>
       </c>
@@ -54321,7 +56028,7 @@
         <v>0.60069444444444442</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>406</v>
       </c>
@@ -54353,7 +56060,7 @@
         <v>0.60069444444444442</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>72</v>
       </c>
@@ -54385,7 +56092,7 @@
         <v>0.60555555555555551</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>74</v>
       </c>
@@ -54417,7 +56124,7 @@
         <v>0.62083333333333335</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>76</v>
       </c>
@@ -54449,7 +56156,7 @@
         <v>0.63055555555555554</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>84</v>
       </c>
@@ -54481,7 +56188,7 @@
         <v>0.41388888888888892</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>86</v>
       </c>
@@ -54513,7 +56220,7 @@
         <v>0.42083333333333334</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>88</v>
       </c>
@@ -54545,7 +56252,7 @@
         <v>0.42569444444444443</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>81</v>
       </c>
@@ -54577,7 +56284,7 @@
         <v>0.70138888888888884</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>461</v>
       </c>
@@ -54609,7 +56316,7 @@
         <v>0.70208333333333339</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>463</v>
       </c>
@@ -54641,7 +56348,7 @@
         <v>0.20416666666666669</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>91</v>
       </c>
@@ -54673,7 +56380,7 @@
         <v>0.22361111111111109</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>92</v>
       </c>
@@ -54705,7 +56412,7 @@
         <v>0.23402777777777781</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>105</v>
       </c>
@@ -54737,7 +56444,7 @@
         <v>0.71458333333333324</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>101</v>
       </c>
@@ -54769,7 +56476,7 @@
         <v>0.71458333333333324</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>99</v>
       </c>
@@ -54801,7 +56508,7 @@
         <v>0.71458333333333324</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>106</v>
       </c>
@@ -54833,7 +56540,7 @@
         <v>0.71527777777777779</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>107</v>
       </c>
@@ -54865,7 +56572,7 @@
         <v>0.71527777777777779</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>411</v>
       </c>
@@ -54897,7 +56604,7 @@
         <v>0.71666666666666667</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>104</v>
       </c>
@@ -54929,7 +56636,7 @@
         <v>0.71666666666666667</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>412</v>
       </c>
@@ -54961,7 +56668,7 @@
         <v>0.71666666666666667</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>413</v>
       </c>
@@ -54993,7 +56700,7 @@
         <v>0.71666666666666667</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>108</v>
       </c>
@@ -55025,7 +56732,7 @@
         <v>0.71805555555555556</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>110</v>
       </c>
@@ -55057,7 +56764,7 @@
         <v>0.96250000000000002</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>111</v>
       </c>
@@ -55089,7 +56796,7 @@
         <v>0.96319444444444446</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>112</v>
       </c>
@@ -55121,7 +56828,7 @@
         <v>0.96319444444444446</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>113</v>
       </c>
@@ -55153,7 +56860,7 @@
         <v>0.96388888888888891</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>94</v>
       </c>
@@ -55185,7 +56892,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>96</v>
       </c>
@@ -55217,7 +56924,7 @@
         <v>0.6020833333333333</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>98</v>
       </c>
@@ -55249,7 +56956,7 @@
         <v>0.60416666666666663</v>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>114</v>
       </c>
@@ -55281,7 +56988,7 @@
         <v>9.0277777777777787E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>117</v>
       </c>
@@ -55313,7 +57020,7 @@
         <v>0.95347222222222217</v>
       </c>
     </row>
-    <row r="57" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>118</v>
       </c>
@@ -55345,7 +57052,7 @@
         <v>0.95347222222222217</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>116</v>
       </c>
@@ -55377,7 +57084,7 @@
         <v>0.95347222222222217</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>416</v>
       </c>
@@ -55409,7 +57116,7 @@
         <v>0.95347222222222217</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>120</v>
       </c>
@@ -55441,7 +57148,7 @@
         <v>0.14583333333333334</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>124</v>
       </c>
@@ -55473,7 +57180,7 @@
         <v>0.10555555555555556</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>123</v>
       </c>
@@ -55505,7 +57212,7 @@
         <v>0.10416666666666667</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>122</v>
       </c>
@@ -55537,7 +57244,7 @@
         <v>7.5694444444444439E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>120</v>
       </c>
@@ -55569,7 +57276,7 @@
         <v>0.97152777777777777</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>121</v>
       </c>
@@ -55601,7 +57308,7 @@
         <v>0.78402777777777777</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>127</v>
       </c>
@@ -55633,7 +57340,7 @@
         <v>0.11388888888888889</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>125</v>
       </c>
@@ -55665,7 +57372,7 @@
         <v>0.56388888888888888</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>130</v>
       </c>
@@ -55697,7 +57404,7 @@
         <v>0.99444444444444446</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>468</v>
       </c>
@@ -55729,7 +57436,7 @@
         <v>0.67708333333333337</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>132</v>
       </c>
@@ -55761,7 +57468,7 @@
         <v>0.6777777777777777</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>131</v>
       </c>
@@ -55793,7 +57500,7 @@
         <v>0.6777777777777777</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>136</v>
       </c>
@@ -55825,7 +57532,7 @@
         <v>0.4465277777777778</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>137</v>
       </c>
@@ -55857,7 +57564,7 @@
         <v>0.44791666666666669</v>
       </c>
     </row>
-    <row r="74" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>143</v>
       </c>
@@ -55889,7 +57596,7 @@
         <v>0.44861111111111113</v>
       </c>
     </row>
-    <row r="75" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>144</v>
       </c>
@@ -55921,7 +57628,7 @@
         <v>0.44861111111111113</v>
       </c>
     </row>
-    <row r="76" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>141</v>
       </c>
@@ -55953,7 +57660,7 @@
         <v>0.44861111111111113</v>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>142</v>
       </c>
@@ -55985,7 +57692,7 @@
         <v>0.44861111111111113</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>135</v>
       </c>
@@ -56017,7 +57724,7 @@
         <v>0.66180555555555554</v>
       </c>
     </row>
-    <row r="79" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>134</v>
       </c>
@@ -56049,7 +57756,7 @@
         <v>0.66180555555555554</v>
       </c>
     </row>
-    <row r="80" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>128</v>
       </c>
@@ -56081,7 +57788,7 @@
         <v>0.40277777777777773</v>
       </c>
     </row>
-    <row r="81" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>146</v>
       </c>
@@ -56113,7 +57820,7 @@
         <v>0.45902777777777781</v>
       </c>
     </row>
-    <row r="82" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>148</v>
       </c>
@@ -56145,7 +57852,7 @@
         <v>0.94027777777777777</v>
       </c>
     </row>
-    <row r="83" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>149</v>
       </c>
@@ -56177,7 +57884,7 @@
         <v>0.94166666666666676</v>
       </c>
     </row>
-    <row r="84" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>150</v>
       </c>
@@ -56209,7 +57916,7 @@
         <v>0.94166666666666676</v>
       </c>
     </row>
-    <row r="85" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>151</v>
       </c>
@@ -56241,7 +57948,7 @@
         <v>0.9784722222222223</v>
       </c>
     </row>
-    <row r="86" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>152</v>
       </c>
@@ -56273,7 +57980,7 @@
         <v>0.97916666666666663</v>
       </c>
     </row>
-    <row r="87" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>156</v>
       </c>
@@ -56305,7 +58012,7 @@
         <v>0.76666666666666661</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>165</v>
       </c>
@@ -56337,7 +58044,7 @@
         <v>2.2222222222222223E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>471</v>
       </c>
@@ -56369,7 +58076,7 @@
         <v>2.2222222222222223E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>163</v>
       </c>
@@ -56401,7 +58108,7 @@
         <v>0.86319444444444438</v>
       </c>
     </row>
-    <row r="91" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>157</v>
       </c>
@@ -56433,7 +58140,7 @@
         <v>0.86388888888888893</v>
       </c>
     </row>
-    <row r="92" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>160</v>
       </c>
@@ -56465,7 +58172,7 @@
         <v>0.86388888888888893</v>
       </c>
     </row>
-    <row r="93" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>159</v>
       </c>
@@ -56497,7 +58204,7 @@
         <v>0.86388888888888893</v>
       </c>
     </row>
-    <row r="94" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>161</v>
       </c>
@@ -56529,7 +58236,7 @@
         <v>0.86388888888888893</v>
       </c>
     </row>
-    <row r="95" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>162</v>
       </c>
@@ -56561,7 +58268,7 @@
         <v>0.86388888888888893</v>
       </c>
     </row>
-    <row r="96" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>164</v>
       </c>
@@ -56593,7 +58300,7 @@
         <v>0.95763888888888893</v>
       </c>
     </row>
-    <row r="97" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>170</v>
       </c>
@@ -56625,7 +58332,7 @@
         <v>0.46875</v>
       </c>
     </row>
-    <row r="98" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>174</v>
       </c>
@@ -56657,7 +58364,7 @@
         <v>0.4694444444444445</v>
       </c>
     </row>
-    <row r="99" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>421</v>
       </c>
@@ -56689,7 +58396,7 @@
         <v>0.4694444444444445</v>
       </c>
     </row>
-    <row r="100" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>175</v>
       </c>
@@ -56721,7 +58428,7 @@
         <v>0.4694444444444445</v>
       </c>
     </row>
-    <row r="101" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>176</v>
       </c>
@@ -56753,7 +58460,7 @@
         <v>0.7284722222222223</v>
       </c>
     </row>
-    <row r="102" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>178</v>
       </c>
@@ -56785,7 +58492,7 @@
         <v>0.72916666666666663</v>
       </c>
     </row>
-    <row r="103" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>180</v>
       </c>
@@ -56817,7 +58524,7 @@
         <v>0.75208333333333333</v>
       </c>
     </row>
-    <row r="104" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>182</v>
       </c>
@@ -56849,7 +58556,7 @@
         <v>0.46597222222222223</v>
       </c>
     </row>
-    <row r="105" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>183</v>
       </c>
@@ -56881,7 +58588,7 @@
         <v>0.46666666666666662</v>
       </c>
     </row>
-    <row r="106" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>185</v>
       </c>
@@ -56913,7 +58620,7 @@
         <v>0.46666666666666662</v>
       </c>
     </row>
-    <row r="107" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>186</v>
       </c>
@@ -56945,7 +58652,7 @@
         <v>0.46666666666666662</v>
       </c>
     </row>
-    <row r="108" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>188</v>
       </c>
@@ -56977,7 +58684,7 @@
         <v>0.42152777777777778</v>
       </c>
     </row>
-    <row r="109" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>189</v>
       </c>
@@ -57009,7 +58716,7 @@
         <v>0.42222222222222222</v>
       </c>
     </row>
-    <row r="110" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>190</v>
       </c>
@@ -57041,7 +58748,7 @@
         <v>0.42222222222222222</v>
       </c>
     </row>
-    <row r="111" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>192</v>
       </c>
@@ -57073,7 +58780,7 @@
         <v>0.42291666666666666</v>
       </c>
     </row>
-    <row r="112" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>194</v>
       </c>
@@ -57105,7 +58812,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="113" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>199</v>
       </c>
@@ -57137,7 +58844,7 @@
         <v>0.72152777777777777</v>
       </c>
     </row>
-    <row r="114" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>198</v>
       </c>
@@ -57169,7 +58876,7 @@
         <v>0.72152777777777777</v>
       </c>
     </row>
-    <row r="115" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>203</v>
       </c>
@@ -57201,7 +58908,7 @@
         <v>0.72152777777777777</v>
       </c>
     </row>
-    <row r="116" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>206</v>
       </c>
@@ -57233,7 +58940,7 @@
         <v>0.72152777777777777</v>
       </c>
     </row>
-    <row r="117" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>200</v>
       </c>
@@ -57265,7 +58972,7 @@
         <v>0.72152777777777777</v>
       </c>
     </row>
-    <row r="118" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>201</v>
       </c>
@@ -57297,7 +59004,7 @@
         <v>0.72152777777777777</v>
       </c>
     </row>
-    <row r="119" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>202</v>
       </c>
@@ -57329,7 +59036,7 @@
         <v>0.72291666666666676</v>
       </c>
     </row>
-    <row r="120" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>506</v>
       </c>
@@ -57361,7 +59068,7 @@
         <v>0.3972222222222222</v>
       </c>
     </row>
-    <row r="121" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>196</v>
       </c>
@@ -57393,7 +59100,7 @@
         <v>0.50416666666666665</v>
       </c>
     </row>
-    <row r="122" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>209</v>
       </c>
@@ -57425,7 +59132,7 @@
         <v>0.6743055555555556</v>
       </c>
     </row>
-    <row r="123" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>208</v>
       </c>
@@ -57457,7 +59164,7 @@
         <v>0.6743055555555556</v>
       </c>
     </row>
-    <row r="124" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>207</v>
       </c>
@@ -57489,7 +59196,7 @@
         <v>0.6743055555555556</v>
       </c>
     </row>
-    <row r="125" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>211</v>
       </c>
@@ -57521,7 +59228,7 @@
         <v>0.67638888888888893</v>
       </c>
     </row>
-    <row r="126" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>214</v>
       </c>
@@ -57553,7 +59260,7 @@
         <v>0.67708333333333337</v>
       </c>
     </row>
-    <row r="127" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>212</v>
       </c>
@@ -57585,7 +59292,7 @@
         <v>0.67708333333333337</v>
       </c>
     </row>
-    <row r="128" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>216</v>
       </c>
@@ -57617,7 +59324,7 @@
         <v>0.6777777777777777</v>
       </c>
     </row>
-    <row r="129" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>222</v>
       </c>
@@ -57649,7 +59356,7 @@
         <v>0.41180555555555554</v>
       </c>
     </row>
-    <row r="130" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>225</v>
       </c>
@@ -57681,7 +59388,7 @@
         <v>0.41111111111111115</v>
       </c>
     </row>
-    <row r="131" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>222</v>
       </c>
@@ -57713,7 +59420,7 @@
         <v>0.41180555555555554</v>
       </c>
     </row>
-    <row r="132" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>234</v>
       </c>
@@ -57745,7 +59452,7 @@
         <v>0.62847222222222221</v>
       </c>
     </row>
-    <row r="133" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>239</v>
       </c>
@@ -57777,7 +59484,7 @@
         <v>0.62986111111111109</v>
       </c>
     </row>
-    <row r="134" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>230</v>
       </c>
@@ -57809,7 +59516,7 @@
         <v>0.62986111111111109</v>
       </c>
     </row>
-    <row r="135" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>232</v>
       </c>
@@ -57841,7 +59548,7 @@
         <v>0.63055555555555554</v>
       </c>
     </row>
-    <row r="136" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>237</v>
       </c>
@@ -57873,7 +59580,7 @@
         <v>0.63124999999999998</v>
       </c>
     </row>
-    <row r="137" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>230</v>
       </c>
@@ -57905,7 +59612,7 @@
         <v>3.5416666666666666E-2</v>
       </c>
     </row>
-    <row r="138" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>238</v>
       </c>
@@ -57937,7 +59644,7 @@
         <v>3.5416666666666666E-2</v>
       </c>
     </row>
-    <row r="139" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>235</v>
       </c>
@@ -57969,7 +59676,7 @@
         <v>3.6805555555555557E-2</v>
       </c>
     </row>
-    <row r="140" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>231</v>
       </c>
@@ -58001,7 +59708,7 @@
         <v>3.888888888888889E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>229</v>
       </c>
@@ -58033,7 +59740,7 @@
         <v>0.89166666666666661</v>
       </c>
     </row>
-    <row r="142" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>243</v>
       </c>
@@ -58065,7 +59772,7 @@
         <v>0.42083333333333334</v>
       </c>
     </row>
-    <row r="143" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>241</v>
       </c>
@@ -58097,7 +59804,7 @@
         <v>0.42083333333333334</v>
       </c>
     </row>
-    <row r="144" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>247</v>
       </c>
@@ -58129,7 +59836,7 @@
         <v>0.73958333333333337</v>
       </c>
     </row>
-    <row r="145" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>252</v>
       </c>
@@ -58161,7 +59868,7 @@
         <v>0.61875000000000002</v>
       </c>
     </row>
-    <row r="146" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>250</v>
       </c>
@@ -58193,7 +59900,7 @@
         <v>0.61944444444444446</v>
       </c>
     </row>
-    <row r="147" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>425</v>
       </c>
@@ -58225,7 +59932,7 @@
         <v>0.61944444444444446</v>
       </c>
     </row>
-    <row r="148" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>251</v>
       </c>
@@ -58257,7 +59964,7 @@
         <v>0.61944444444444446</v>
       </c>
     </row>
-    <row r="149" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>257</v>
       </c>
@@ -58289,7 +59996,7 @@
         <v>0.48055555555555557</v>
       </c>
     </row>
-    <row r="150" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>254</v>
       </c>
@@ -58321,7 +60028,7 @@
         <v>0.48125000000000001</v>
       </c>
     </row>
-    <row r="151" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>256</v>
       </c>
@@ -58353,7 +60060,7 @@
         <v>0.48125000000000001</v>
       </c>
     </row>
-    <row r="152" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>266</v>
       </c>
@@ -58385,7 +60092,7 @@
         <v>0.59583333333333333</v>
       </c>
     </row>
-    <row r="153" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>265</v>
       </c>
@@ -58417,7 +60124,7 @@
         <v>0.59583333333333333</v>
       </c>
     </row>
-    <row r="154" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>263</v>
       </c>
@@ -58449,7 +60156,7 @@
         <v>0.59583333333333333</v>
       </c>
     </row>
-    <row r="155" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="20" t="s">
         <v>509</v>
       </c>
@@ -58481,7 +60188,7 @@
         <v>0.59930555555555554</v>
       </c>
     </row>
-    <row r="156" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>260</v>
       </c>
@@ -58513,7 +60220,7 @@
         <v>0.44027777777777777</v>
       </c>
     </row>
-    <row r="157" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>259</v>
       </c>
@@ -58545,7 +60252,7 @@
         <v>0.44027777777777777</v>
       </c>
     </row>
-    <row r="158" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>267</v>
       </c>
@@ -58577,7 +60284,7 @@
         <v>0.32361111111111113</v>
       </c>
     </row>
-    <row r="159" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>268</v>
       </c>
@@ -58609,7 +60316,7 @@
         <v>0.4236111111111111</v>
       </c>
     </row>
-    <row r="160" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>272</v>
       </c>
@@ -58641,7 +60348,7 @@
         <v>0.54305555555555551</v>
       </c>
     </row>
-    <row r="161" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>270</v>
       </c>
@@ -58673,7 +60380,7 @@
         <v>0.58958333333333335</v>
       </c>
     </row>
-    <row r="162" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>269</v>
       </c>
@@ -58705,7 +60412,7 @@
         <v>0.59027777777777779</v>
       </c>
     </row>
-    <row r="163" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>273</v>
       </c>
@@ -58737,7 +60444,7 @@
         <v>0.68611111111111101</v>
       </c>
     </row>
-    <row r="164" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>277</v>
       </c>
@@ -58769,7 +60476,7 @@
         <v>0.66875000000000007</v>
       </c>
     </row>
-    <row r="165" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>288</v>
       </c>
@@ -58801,7 +60508,7 @@
         <v>0.6694444444444444</v>
       </c>
     </row>
-    <row r="166" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>281</v>
       </c>
@@ -58833,7 +60540,7 @@
         <v>0.6694444444444444</v>
       </c>
     </row>
-    <row r="167" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>278</v>
       </c>
@@ -58865,7 +60572,7 @@
         <v>0.67013888888888884</v>
       </c>
     </row>
-    <row r="168" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>283</v>
       </c>
@@ -58897,7 +60604,7 @@
         <v>0.67222222222222217</v>
       </c>
     </row>
-    <row r="169" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>285</v>
       </c>
@@ -58929,7 +60636,7 @@
         <v>0.67222222222222217</v>
       </c>
     </row>
-    <row r="170" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>282</v>
       </c>
@@ -58961,7 +60668,7 @@
         <v>0.67222222222222217</v>
       </c>
     </row>
-    <row r="171" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>284</v>
       </c>
@@ -58993,7 +60700,7 @@
         <v>0.67291666666666661</v>
       </c>
     </row>
-    <row r="172" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>428</v>
       </c>
@@ -59025,7 +60732,7 @@
         <v>0.67291666666666661</v>
       </c>
     </row>
-    <row r="173" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>291</v>
       </c>
@@ -59057,7 +60764,7 @@
         <v>0.58958333333333335</v>
       </c>
     </row>
-    <row r="174" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>292</v>
       </c>
@@ -59089,7 +60796,7 @@
         <v>0.58958333333333335</v>
       </c>
     </row>
-    <row r="175" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>475</v>
       </c>
@@ -59121,7 +60828,7 @@
         <v>0.64027777777777783</v>
       </c>
     </row>
-    <row r="176" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>295</v>
       </c>
@@ -59153,7 +60860,7 @@
         <v>0.51527777777777783</v>
       </c>
     </row>
-    <row r="177" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>296</v>
       </c>
@@ -59185,7 +60892,7 @@
         <v>0.54027777777777775</v>
       </c>
     </row>
-    <row r="178" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>297</v>
       </c>
@@ -59217,7 +60924,7 @@
         <v>0.4152777777777778</v>
       </c>
     </row>
-    <row r="179" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>299</v>
       </c>
@@ -59249,7 +60956,7 @@
         <v>0.67569444444444438</v>
       </c>
     </row>
-    <row r="180" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>304</v>
       </c>
@@ -59281,7 +60988,7 @@
         <v>0.62847222222222221</v>
       </c>
     </row>
-    <row r="181" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>301</v>
       </c>
@@ -59313,7 +61020,7 @@
         <v>0.62847222222222221</v>
       </c>
     </row>
-    <row r="182" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>429</v>
       </c>
@@ -59345,7 +61052,7 @@
         <v>0.62986111111111109</v>
       </c>
     </row>
-    <row r="183" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>305</v>
       </c>
@@ -59377,7 +61084,7 @@
         <v>0.6333333333333333</v>
       </c>
     </row>
-    <row r="184" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>306</v>
       </c>
@@ -59409,7 +61116,7 @@
         <v>0.6333333333333333</v>
       </c>
     </row>
-    <row r="185" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>303</v>
       </c>
@@ -59441,7 +61148,7 @@
         <v>0.6333333333333333</v>
       </c>
     </row>
-    <row r="186" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>308</v>
       </c>
@@ -59473,7 +61180,7 @@
         <v>0.67361111111111116</v>
       </c>
     </row>
-    <row r="187" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>312</v>
       </c>
@@ -59505,7 +61212,7 @@
         <v>0.67361111111111116</v>
       </c>
     </row>
-    <row r="188" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>310</v>
       </c>
@@ -59537,7 +61244,7 @@
         <v>0.67361111111111116</v>
       </c>
     </row>
-    <row r="189" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>314</v>
       </c>
@@ -59569,7 +61276,7 @@
         <v>0.52708333333333335</v>
       </c>
     </row>
-    <row r="190" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>317</v>
       </c>
@@ -59601,7 +61308,7 @@
         <v>0.52708333333333335</v>
       </c>
     </row>
-    <row r="191" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>315</v>
       </c>
@@ -59633,7 +61340,7 @@
         <v>0.52708333333333335</v>
       </c>
     </row>
-    <row r="192" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>320</v>
       </c>
@@ -59665,7 +61372,7 @@
         <v>0.52708333333333335</v>
       </c>
     </row>
-    <row r="193" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>318</v>
       </c>
@@ -59697,7 +61404,7 @@
         <v>0.52708333333333335</v>
       </c>
     </row>
-    <row r="194" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>316</v>
       </c>
@@ -59729,7 +61436,7 @@
         <v>0.52708333333333335</v>
       </c>
     </row>
-    <row r="195" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>313</v>
       </c>
@@ -59761,7 +61468,7 @@
         <v>0.6118055555555556</v>
       </c>
     </row>
-    <row r="196" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>321</v>
       </c>
@@ -59793,7 +61500,7 @@
         <v>0.65347222222222223</v>
       </c>
     </row>
-    <row r="197" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>322</v>
       </c>
@@ -59825,7 +61532,7 @@
         <v>0.65347222222222223</v>
       </c>
     </row>
-    <row r="198" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>323</v>
       </c>
@@ -59857,7 +61564,7 @@
         <v>0.72499999999999998</v>
       </c>
     </row>
-    <row r="199" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>324</v>
       </c>
@@ -59889,7 +61596,7 @@
         <v>0.72499999999999998</v>
       </c>
     </row>
-    <row r="200" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>325</v>
       </c>
@@ -59921,7 +61628,7 @@
         <v>0.39930555555555558</v>
       </c>
     </row>
-    <row r="201" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>327</v>
       </c>
@@ -59953,7 +61660,7 @@
         <v>0.57916666666666672</v>
       </c>
     </row>
-    <row r="202" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>329</v>
       </c>
@@ -59985,7 +61692,7 @@
         <v>0.50416666666666665</v>
       </c>
     </row>
-    <row r="203" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>334</v>
       </c>
@@ -60017,7 +61724,7 @@
         <v>0.6069444444444444</v>
       </c>
     </row>
-    <row r="204" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>431</v>
       </c>
@@ -60049,7 +61756,7 @@
         <v>0.60972222222222217</v>
       </c>
     </row>
-    <row r="205" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>336</v>
       </c>
@@ -60081,7 +61788,7 @@
         <v>0.6118055555555556</v>
       </c>
     </row>
-    <row r="206" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>432</v>
       </c>
@@ -60113,7 +61820,7 @@
         <v>0.61249999999999993</v>
       </c>
     </row>
-    <row r="207" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>331</v>
       </c>
@@ -60145,7 +61852,7 @@
         <v>0.61249999999999993</v>
       </c>
     </row>
-    <row r="208" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>332</v>
       </c>
@@ -60177,7 +61884,7 @@
         <v>0.61319444444444449</v>
       </c>
     </row>
-    <row r="209" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>335</v>
       </c>
@@ -60209,7 +61916,7 @@
         <v>0.61319444444444449</v>
       </c>
     </row>
-    <row r="210" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>340</v>
       </c>
@@ -60241,7 +61948,7 @@
         <v>0.75347222222222221</v>
       </c>
     </row>
-    <row r="211" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>339</v>
       </c>
@@ -60273,7 +61980,7 @@
         <v>0.41319444444444442</v>
       </c>
     </row>
-    <row r="212" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>338</v>
       </c>
@@ -60305,7 +62012,7 @@
         <v>0.93888888888888899</v>
       </c>
     </row>
-    <row r="213" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>341</v>
       </c>
@@ -60337,7 +62044,7 @@
         <v>0.69513888888888886</v>
       </c>
     </row>
-    <row r="214" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>343</v>
       </c>
@@ -60369,7 +62076,7 @@
         <v>0.7006944444444444</v>
       </c>
     </row>
-    <row r="215" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>345</v>
       </c>
@@ -60401,7 +62108,7 @@
         <v>0.7006944444444444</v>
       </c>
     </row>
-    <row r="216" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>347</v>
       </c>
@@ -60433,7 +62140,7 @@
         <v>0.70138888888888884</v>
       </c>
     </row>
-    <row r="217" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>344</v>
       </c>
@@ -60465,7 +62172,7 @@
         <v>0.70138888888888884</v>
       </c>
     </row>
-    <row r="218" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>342</v>
       </c>
@@ -60497,7 +62204,7 @@
         <v>0.70208333333333339</v>
       </c>
     </row>
-    <row r="219" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>348</v>
       </c>
@@ -60529,7 +62236,7 @@
         <v>0.65347222222222223</v>
       </c>
     </row>
-    <row r="220" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>350</v>
       </c>
@@ -60593,7 +62300,7 @@
         <v>0.57847222222222217</v>
       </c>
     </row>
-    <row r="222" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>353</v>
       </c>
@@ -60625,7 +62332,7 @@
         <v>0.58611111111111114</v>
       </c>
     </row>
-    <row r="223" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>354</v>
       </c>
@@ -60657,7 +62364,7 @@
         <v>0.37916666666666665</v>
       </c>
     </row>
-    <row r="224" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>362</v>
       </c>
@@ -60689,7 +62396,7 @@
         <v>0.8979166666666667</v>
       </c>
     </row>
-    <row r="225" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>368</v>
       </c>
@@ -60721,7 +62428,7 @@
         <v>0.8979166666666667</v>
       </c>
     </row>
-    <row r="226" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>370</v>
       </c>
@@ -60753,7 +62460,7 @@
         <v>0.8979166666666667</v>
       </c>
     </row>
-    <row r="227" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>367</v>
       </c>
@@ -60785,7 +62492,7 @@
         <v>0.8979166666666667</v>
       </c>
     </row>
-    <row r="228" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>355</v>
       </c>
@@ -60817,7 +62524,7 @@
         <v>0.51736111111111105</v>
       </c>
     </row>
-    <row r="229" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>371</v>
       </c>
@@ -60849,7 +62556,7 @@
         <v>0.48888888888888887</v>
       </c>
     </row>
-    <row r="230" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>375</v>
       </c>
@@ -60881,7 +62588,7 @@
         <v>0.48472222222222222</v>
       </c>
     </row>
-    <row r="231" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>384</v>
       </c>
@@ -60913,7 +62620,7 @@
         <v>0.12916666666666668</v>
       </c>
     </row>
-    <row r="232" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>444</v>
       </c>
@@ -60945,7 +62652,7 @@
         <v>0.97361111111111109</v>
       </c>
     </row>
-    <row r="233" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>379</v>
       </c>
@@ -60977,7 +62684,7 @@
         <v>0.68194444444444446</v>
       </c>
     </row>
-    <row r="234" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>355</v>
       </c>
@@ -61009,7 +62716,7 @@
         <v>0.63541666666666663</v>
       </c>
     </row>
-    <row r="235" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>385</v>
       </c>
@@ -61041,7 +62748,7 @@
         <v>0.39999999999999997</v>
       </c>
     </row>
-    <row r="236" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>387</v>
       </c>
@@ -61073,7 +62780,7 @@
         <v>4.3055555555555562E-2</v>
       </c>
     </row>
-    <row r="237" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>389</v>
       </c>
@@ -61105,7 +62812,7 @@
         <v>4.2361111111111106E-2</v>
       </c>
     </row>
-    <row r="238" spans="1:13" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>388</v>
       </c>
@@ -61137,7 +62844,7 @@
         <v>4.2361111111111106E-2</v>
       </c>
     </row>
-    <row r="239" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A239" s="21" t="s">
         <v>565</v>
       </c>
@@ -61172,7 +62879,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="240" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A240" s="21" t="s">
         <v>571</v>
       </c>
@@ -61207,7 +62914,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="241" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A241" s="21" t="s">
         <v>588</v>
       </c>
@@ -61242,7 +62949,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="242" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A242" s="21" t="s">
         <v>578</v>
       </c>
@@ -61277,7 +62984,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="243" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A243" s="21" t="s">
         <v>584</v>
       </c>
@@ -61312,7 +63019,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="244" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A244" s="21" t="s">
         <v>582</v>
       </c>
@@ -61347,7 +63054,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="245" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A245" s="21" t="s">
         <v>607</v>
       </c>
@@ -61382,7 +63089,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="246" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A246" s="21" t="s">
         <v>642</v>
       </c>
@@ -61417,7 +63124,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="247" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A247" s="21" t="s">
         <v>621</v>
       </c>
@@ -61452,7 +63159,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="248" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A248" s="21" t="s">
         <v>616</v>
       </c>
@@ -61487,7 +63194,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="249" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A249" s="8" t="s">
         <v>621</v>
       </c>
@@ -61522,7 +63229,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="250" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A250" s="8" t="s">
         <v>637</v>
       </c>
@@ -61557,7 +63264,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="251" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A251" s="8" t="s">
         <v>634</v>
       </c>
@@ -61592,7 +63299,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="252" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A252" s="8" t="s">
         <v>624</v>
       </c>
@@ -61627,7 +63334,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="253" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A253" s="8" t="s">
         <v>709</v>
       </c>
@@ -61662,7 +63369,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="254" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A254" s="8" t="s">
         <v>729</v>
       </c>
@@ -61697,7 +63404,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="255" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A255" s="8" t="s">
         <v>730</v>
       </c>
@@ -61732,7 +63439,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="256" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A256" s="8" t="s">
         <v>732</v>
       </c>
@@ -61767,7 +63474,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="257" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A257" s="8" t="s">
         <v>734</v>
       </c>
@@ -61802,7 +63509,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="258" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A258" s="8" t="s">
         <v>692</v>
       </c>
@@ -61837,7 +63544,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="259" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A259" s="8" t="s">
         <v>679</v>
       </c>
@@ -61872,7 +63579,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="260" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A260" s="8" t="s">
         <v>687</v>
       </c>
@@ -61907,7 +63614,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="261" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A261" s="8" t="s">
         <v>689</v>
       </c>
@@ -61942,7 +63649,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="262" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A262" s="8" t="s">
         <v>684</v>
       </c>
@@ -61977,7 +63684,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="263" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A263" s="8" t="s">
         <v>671</v>
       </c>
@@ -62012,7 +63719,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="264" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A264" s="8" t="s">
         <v>676</v>
       </c>
@@ -62047,7 +63754,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="265" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A265" s="8" t="s">
         <v>756</v>
       </c>
@@ -62082,7 +63789,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="266" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A266" s="8" t="s">
         <v>758</v>
       </c>
@@ -62117,7 +63824,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="267" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A267" s="8" t="s">
         <v>772</v>
       </c>
@@ -62152,7 +63859,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="268" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A268" s="8" t="s">
         <v>760</v>
       </c>
@@ -62187,7 +63894,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="269" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A269" s="8" t="s">
         <v>790</v>
       </c>
@@ -62222,7 +63929,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="270" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A270" s="8" t="s">
         <v>810</v>
       </c>
@@ -62257,7 +63964,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="271" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A271" s="8" t="s">
         <v>813</v>
       </c>
@@ -62292,7 +63999,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="272" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A272" s="8" t="s">
         <v>818</v>
       </c>
@@ -62327,7 +64034,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="273" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A273" s="8" t="s">
         <v>821</v>
       </c>
@@ -62362,7 +64069,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="274" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A274" s="8" t="s">
         <v>867</v>
       </c>
@@ -62397,7 +64104,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="275" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A275" s="8" t="s">
         <v>864</v>
       </c>
@@ -62432,7 +64139,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="276" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A276" s="8" t="s">
         <v>816</v>
       </c>
@@ -62467,7 +64174,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="277" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A277" s="8" t="s">
         <v>832</v>
       </c>
@@ -62502,7 +64209,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="278" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A278" s="8" t="s">
         <v>795</v>
       </c>
@@ -62537,7 +64244,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="279" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A279" s="8" t="s">
         <v>807</v>
       </c>
@@ -62572,7 +64279,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="280" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A280" s="8" t="s">
         <v>802</v>
       </c>
@@ -62607,7 +64314,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="281" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A281" s="8" t="s">
         <v>827</v>
       </c>
@@ -62642,7 +64349,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="282" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A282" s="8" t="s">
         <v>825</v>
       </c>
@@ -62677,7 +64384,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="283" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A283" s="8" t="s">
         <v>804</v>
       </c>
@@ -62712,7 +64419,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="284" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A284" s="8" t="s">
         <v>837</v>
       </c>
@@ -62747,7 +64454,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="285" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A285" s="8" t="s">
         <v>830</v>
       </c>
@@ -62782,7 +64489,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="286" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A286" s="8" t="s">
         <v>869</v>
       </c>
@@ -62817,7 +64524,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="287" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A287" s="8" t="s">
         <v>905</v>
       </c>
@@ -62852,7 +64559,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="288" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A288" s="8" t="s">
         <v>945</v>
       </c>
@@ -62887,7 +64594,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="289" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A289" s="8" t="s">
         <v>907</v>
       </c>
@@ -62922,7 +64629,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="290" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A290" s="8" t="s">
         <v>947</v>
       </c>
@@ -62957,7 +64664,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="291" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A291" s="8" t="s">
         <v>949</v>
       </c>
@@ -62992,7 +64699,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="292" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A292" s="8" t="s">
         <v>915</v>
       </c>
@@ -63027,7 +64734,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="293" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A293" s="8" t="s">
         <v>853</v>
       </c>
@@ -63062,7 +64769,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="294" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A294" s="8" t="s">
         <v>859</v>
       </c>
@@ -63097,7 +64804,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="295" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A295" s="8" t="s">
         <v>857</v>
       </c>
@@ -63132,7 +64839,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="296" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A296" s="8" t="s">
         <v>959</v>
       </c>
@@ -63167,7 +64874,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="297" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A297" s="8" t="s">
         <v>943</v>
       </c>
@@ -63202,7 +64909,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="298" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A298" s="8" t="s">
         <v>966</v>
       </c>
@@ -63237,7 +64944,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="299" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A299" s="8" t="s">
         <v>919</v>
       </c>
@@ -63272,7 +64979,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="300" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A300" s="8" t="s">
         <v>969</v>
       </c>
@@ -63307,7 +65014,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="301" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A301" s="8" t="s">
         <v>859</v>
       </c>
@@ -63342,7 +65049,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="302" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A302" s="8" t="s">
         <v>853</v>
       </c>
@@ -63377,7 +65084,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="303" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A303" s="8" t="s">
         <v>934</v>
       </c>
@@ -63412,7 +65119,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="304" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A304" s="17" t="s">
         <v>1002</v>
       </c>
@@ -63447,7 +65154,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="305" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A305" s="21" t="s">
         <v>1013</v>
       </c>
@@ -63482,7 +65189,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="306" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A306" s="21" t="s">
         <v>1049</v>
       </c>
@@ -63517,7 +65224,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="307" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A307" s="21" t="s">
         <v>1026</v>
       </c>
@@ -63552,7 +65259,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="308" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A308" s="21" t="s">
         <v>1060</v>
       </c>
@@ -63587,7 +65294,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="309" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A309" s="20" t="s">
         <v>1063</v>
       </c>
@@ -63622,7 +65329,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="310" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A310" s="20" t="s">
         <v>1065</v>
       </c>
@@ -63657,7 +65364,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="311" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A311" s="20" t="s">
         <v>1067</v>
       </c>
@@ -63692,7 +65399,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="312" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A312" s="21" t="s">
         <v>926</v>
       </c>
@@ -63727,7 +65434,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="313" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A313" s="21" t="s">
         <v>997</v>
       </c>
@@ -63762,7 +65469,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="314" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A314" s="20" t="s">
         <v>1070</v>
       </c>
@@ -63797,7 +65504,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="315" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A315" s="20" t="s">
         <v>1072</v>
       </c>
@@ -63832,7 +65539,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="316" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A316" s="20" t="s">
         <v>1074</v>
       </c>
@@ -63867,7 +65574,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="317" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A317" s="20" t="s">
         <v>1076</v>
       </c>
@@ -63902,7 +65609,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="318" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A318" s="20" t="s">
         <v>219</v>
       </c>
@@ -63937,7 +65644,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="319" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A319" s="20" t="s">
         <v>218</v>
       </c>
@@ -63972,7 +65679,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="320" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A320" s="21" t="s">
         <v>1078</v>
       </c>
@@ -64007,7 +65714,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="321" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A321" s="21" t="s">
         <v>1103</v>
       </c>
@@ -64042,7 +65749,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="322" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A322" s="21" t="s">
         <v>1082</v>
       </c>
@@ -64077,7 +65784,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="323" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A323" s="21" t="s">
         <v>1089</v>
       </c>
@@ -64112,7 +65819,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="324" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A324" s="21" t="s">
         <v>1086</v>
       </c>
@@ -64147,49 +65854,463 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="325" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A325" s="29" t="s">
+    <row r="325" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A325" s="28" t="s">
         <v>839</v>
       </c>
-      <c r="B325" s="29" t="s">
+      <c r="B325" s="28" t="s">
         <v>873</v>
       </c>
-      <c r="C325" s="30" t="s">
+      <c r="C325" s="29" t="s">
         <v>1134</v>
       </c>
-      <c r="D325" s="29" t="s">
+      <c r="D325" s="28" t="s">
         <v>545</v>
       </c>
-      <c r="E325" s="29" t="s">
+      <c r="E325" s="28" t="s">
         <v>550</v>
       </c>
-      <c r="F325" s="29" t="s">
+      <c r="F325" s="28" t="s">
         <v>551</v>
       </c>
-      <c r="G325" s="29" t="s">
+      <c r="G325" s="28" t="s">
         <v>897</v>
       </c>
-      <c r="H325" s="29">
+      <c r="H325" s="28">
         <v>10</v>
       </c>
       <c r="I325" s="28"/>
       <c r="J325" s="28"/>
-      <c r="K325" s="28"/>
-      <c r="L325" s="30" t="s">
+      <c r="K325" s="15"/>
+      <c r="L325" s="29" t="s">
         <v>1111</v>
       </c>
-      <c r="M325" s="31" t="s">
+      <c r="M325" s="30" t="s">
         <v>1135</v>
       </c>
     </row>
+    <row r="326" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A326" s="28" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B326" s="28" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C326" s="29" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D326" s="28" t="s">
+        <v>441</v>
+      </c>
+      <c r="E326" s="28" t="s">
+        <v>550</v>
+      </c>
+      <c r="F326" s="28" t="s">
+        <v>554</v>
+      </c>
+      <c r="G326" s="28" t="s">
+        <v>556</v>
+      </c>
+      <c r="H326" s="28">
+        <v>10</v>
+      </c>
+      <c r="I326" s="28"/>
+      <c r="J326" s="28"/>
+      <c r="K326" s="15"/>
+      <c r="L326" s="29" t="s">
+        <v>1139</v>
+      </c>
+      <c r="M326" s="30" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="327" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A327" s="28" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B327" s="28" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C327" s="29" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D327" s="28" t="s">
+        <v>549</v>
+      </c>
+      <c r="E327" s="28" t="s">
+        <v>550</v>
+      </c>
+      <c r="F327" s="28" t="s">
+        <v>547</v>
+      </c>
+      <c r="G327" s="28" t="s">
+        <v>552</v>
+      </c>
+      <c r="H327" s="28">
+        <v>40</v>
+      </c>
+      <c r="I327" s="28"/>
+      <c r="J327" s="28"/>
+      <c r="K327" s="15"/>
+      <c r="L327" s="29" t="s">
+        <v>1143</v>
+      </c>
+      <c r="M327" s="30" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="328" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A328" s="28" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B328" s="28" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C328" s="29" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D328" s="28" t="s">
+        <v>549</v>
+      </c>
+      <c r="E328" s="28" t="s">
+        <v>550</v>
+      </c>
+      <c r="F328" s="28" t="s">
+        <v>902</v>
+      </c>
+      <c r="G328" s="28" t="s">
+        <v>552</v>
+      </c>
+      <c r="H328" s="28">
+        <v>30</v>
+      </c>
+      <c r="I328" s="28"/>
+      <c r="J328" s="28"/>
+      <c r="K328" s="15"/>
+      <c r="L328" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M328" s="30" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="329" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A329" s="28" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B329" s="28" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C329" s="29" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D329" s="28" t="s">
+        <v>549</v>
+      </c>
+      <c r="E329" s="28" t="s">
+        <v>550</v>
+      </c>
+      <c r="F329" s="28" t="s">
+        <v>902</v>
+      </c>
+      <c r="G329" s="28" t="s">
+        <v>552</v>
+      </c>
+      <c r="H329" s="28">
+        <v>30</v>
+      </c>
+      <c r="I329" s="28"/>
+      <c r="J329" s="28"/>
+      <c r="K329" s="15"/>
+      <c r="L329" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M329" s="30" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="330" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A330" s="28" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B330" s="28" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C330" s="29" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D330" s="28" t="s">
+        <v>549</v>
+      </c>
+      <c r="E330" s="28" t="s">
+        <v>550</v>
+      </c>
+      <c r="F330" s="28" t="s">
+        <v>902</v>
+      </c>
+      <c r="G330" s="28" t="s">
+        <v>552</v>
+      </c>
+      <c r="H330" s="28">
+        <v>30</v>
+      </c>
+      <c r="I330" s="28"/>
+      <c r="J330" s="28"/>
+      <c r="K330" s="15"/>
+      <c r="L330" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M330" s="30" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="331" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A331" s="28" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B331" s="28" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C331" s="29" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D331" s="28" t="s">
+        <v>549</v>
+      </c>
+      <c r="E331" s="28" t="s">
+        <v>550</v>
+      </c>
+      <c r="F331" s="28" t="s">
+        <v>902</v>
+      </c>
+      <c r="G331" s="28" t="s">
+        <v>552</v>
+      </c>
+      <c r="H331" s="28">
+        <v>30</v>
+      </c>
+      <c r="I331" s="28"/>
+      <c r="J331" s="28"/>
+      <c r="K331" s="15"/>
+      <c r="L331" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M331" s="30" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="332" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A332" s="28" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B332" s="28" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C332" s="29" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D332" s="28" t="s">
+        <v>549</v>
+      </c>
+      <c r="E332" s="28" t="s">
+        <v>550</v>
+      </c>
+      <c r="F332" s="28" t="s">
+        <v>902</v>
+      </c>
+      <c r="G332" s="28" t="s">
+        <v>552</v>
+      </c>
+      <c r="H332" s="28">
+        <v>30</v>
+      </c>
+      <c r="I332" s="28"/>
+      <c r="J332" s="28"/>
+      <c r="K332" s="15"/>
+      <c r="L332" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M332" s="30" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="333" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A333" s="28" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B333" s="28" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C333" s="29" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D333" s="28" t="s">
+        <v>549</v>
+      </c>
+      <c r="E333" s="28" t="s">
+        <v>550</v>
+      </c>
+      <c r="F333" s="28" t="s">
+        <v>902</v>
+      </c>
+      <c r="G333" s="28" t="s">
+        <v>552</v>
+      </c>
+      <c r="H333" s="28">
+        <v>30</v>
+      </c>
+      <c r="I333" s="28"/>
+      <c r="J333" s="28"/>
+      <c r="K333" s="15"/>
+      <c r="L333" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M333" s="30" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="334" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A334" s="28" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B334" s="28" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C334" s="29" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D334" s="28" t="s">
+        <v>549</v>
+      </c>
+      <c r="E334" s="28" t="s">
+        <v>550</v>
+      </c>
+      <c r="F334" s="28" t="s">
+        <v>902</v>
+      </c>
+      <c r="G334" s="28" t="s">
+        <v>552</v>
+      </c>
+      <c r="H334" s="28">
+        <v>30</v>
+      </c>
+      <c r="I334" s="28"/>
+      <c r="J334" s="28"/>
+      <c r="K334" s="15"/>
+      <c r="L334" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M334" s="30" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="335" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A335" s="28" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B335" s="28" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C335" s="29" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D335" s="28" t="s">
+        <v>549</v>
+      </c>
+      <c r="E335" s="28" t="s">
+        <v>550</v>
+      </c>
+      <c r="F335" s="28" t="s">
+        <v>902</v>
+      </c>
+      <c r="G335" s="28" t="s">
+        <v>552</v>
+      </c>
+      <c r="H335" s="28">
+        <v>30</v>
+      </c>
+      <c r="I335" s="28"/>
+      <c r="J335" s="28"/>
+      <c r="K335" s="15"/>
+      <c r="L335" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M335" s="30" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="336" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A336" s="28" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B336" s="28" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C336" s="29" t="s">
+        <v>1183</v>
+      </c>
+      <c r="D336" s="28" t="s">
+        <v>549</v>
+      </c>
+      <c r="E336" s="28" t="s">
+        <v>550</v>
+      </c>
+      <c r="F336" s="28" t="s">
+        <v>902</v>
+      </c>
+      <c r="G336" s="28" t="s">
+        <v>897</v>
+      </c>
+      <c r="H336" s="28">
+        <v>20</v>
+      </c>
+      <c r="I336" s="28"/>
+      <c r="J336" s="28"/>
+      <c r="K336" s="15"/>
+      <c r="L336" s="29" t="s">
+        <v>1154</v>
+      </c>
+      <c r="M336" s="30" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="337" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A337" s="28" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B337" s="28" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C337" s="29" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D337" s="28" t="s">
+        <v>549</v>
+      </c>
+      <c r="E337" s="28" t="s">
+        <v>550</v>
+      </c>
+      <c r="F337" s="28" t="s">
+        <v>547</v>
+      </c>
+      <c r="G337" s="28" t="s">
+        <v>552</v>
+      </c>
+      <c r="H337" s="28">
+        <v>40</v>
+      </c>
+      <c r="I337" s="28"/>
+      <c r="J337" s="28"/>
+      <c r="K337" s="15"/>
+      <c r="L337" s="29" t="s">
+        <v>1147</v>
+      </c>
+      <c r="M337" s="30" t="s">
+        <v>1081</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N325" xr:uid="{083B2BF1-723B-4775-8297-318920D3FD0C}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="LUIZ ROGERIO DA SILVA SEUANES"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:N325" xr:uid="{083B2BF1-723B-4775-8297-318920D3FD0C}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>